--- a/Audit/JJ_PD_IP_M06_통합테스트결과서_v1.0_이노팸.xlsx
+++ b/Audit/JJ_PD_IP_M06_통합테스트결과서_v1.0_이노팸.xlsx
@@ -9120,7 +9120,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:S44"/>
+  <dimension ref="A1:S44"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col width="5.125" customWidth="1" style="2" min="1" max="1"/>
@@ -9141,6 +9141,7 @@
     <col width="9" customWidth="1" style="4" min="19" max="16384"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2" ht="41.25" customFormat="1" customHeight="1" s="83">
       <c r="A2" s="72" t="inlineStr">
         <is>
@@ -11476,13 +11477,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:O897"/>
+  <dimension ref="A1:O897"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.875" defaultRowHeight="17.1"/>
   <cols>
     <col width="10" customWidth="1" style="48" min="1" max="3"/>
     <col width="12" customWidth="1" style="48" min="4" max="15"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2" ht="24" customHeight="1" s="48">
       <c r="A2" s="43" t="inlineStr">
         <is>
@@ -11685,6 +11687,7 @@
       <c r="N23" s="51" t="n"/>
       <c r="O23" s="52" t="n"/>
     </row>
+    <row r="24"/>
     <row r="25" ht="24" customHeight="1" s="48">
       <c r="A25" s="43" t="inlineStr">
         <is>
@@ -11887,6 +11890,7 @@
       <c r="N46" s="51" t="n"/>
       <c r="O46" s="52" t="n"/>
     </row>
+    <row r="47"/>
     <row r="48" ht="24" customHeight="1" s="48">
       <c r="A48" s="43" t="inlineStr">
         <is>
@@ -12089,6 +12093,7 @@
       <c r="N69" s="51" t="n"/>
       <c r="O69" s="52" t="n"/>
     </row>
+    <row r="70"/>
     <row r="71" ht="24" customHeight="1" s="48">
       <c r="A71" s="43" t="inlineStr">
         <is>
@@ -12291,6 +12296,7 @@
       <c r="N92" s="51" t="n"/>
       <c r="O92" s="52" t="n"/>
     </row>
+    <row r="93"/>
     <row r="94" ht="24" customHeight="1" s="48">
       <c r="A94" s="43" t="inlineStr">
         <is>
@@ -12493,6 +12499,7 @@
       <c r="N115" s="51" t="n"/>
       <c r="O115" s="52" t="n"/>
     </row>
+    <row r="116"/>
     <row r="117" ht="24" customHeight="1" s="48">
       <c r="A117" s="43" t="inlineStr">
         <is>
@@ -12695,6 +12702,7 @@
       <c r="N138" s="51" t="n"/>
       <c r="O138" s="52" t="n"/>
     </row>
+    <row r="139"/>
     <row r="140" ht="24" customHeight="1" s="48">
       <c r="A140" s="43" t="inlineStr">
         <is>
@@ -12897,6 +12905,7 @@
       <c r="N161" s="51" t="n"/>
       <c r="O161" s="52" t="n"/>
     </row>
+    <row r="162"/>
     <row r="163" ht="24" customHeight="1" s="48">
       <c r="A163" s="43" t="inlineStr">
         <is>
@@ -13099,6 +13108,7 @@
       <c r="N184" s="51" t="n"/>
       <c r="O184" s="52" t="n"/>
     </row>
+    <row r="185"/>
     <row r="186" ht="24" customHeight="1" s="48">
       <c r="A186" s="43" t="inlineStr">
         <is>
@@ -13301,6 +13311,7 @@
       <c r="N207" s="51" t="n"/>
       <c r="O207" s="52" t="n"/>
     </row>
+    <row r="208"/>
     <row r="209" ht="24" customHeight="1" s="48">
       <c r="A209" s="43" t="inlineStr">
         <is>
@@ -13503,6 +13514,7 @@
       <c r="N230" s="51" t="n"/>
       <c r="O230" s="52" t="n"/>
     </row>
+    <row r="231"/>
     <row r="232" ht="24" customHeight="1" s="48">
       <c r="A232" s="43" t="inlineStr">
         <is>
@@ -13705,6 +13717,7 @@
       <c r="N253" s="51" t="n"/>
       <c r="O253" s="52" t="n"/>
     </row>
+    <row r="254"/>
     <row r="255" ht="24" customHeight="1" s="48">
       <c r="A255" s="43" t="inlineStr">
         <is>
@@ -13907,6 +13920,7 @@
       <c r="N276" s="51" t="n"/>
       <c r="O276" s="52" t="n"/>
     </row>
+    <row r="277"/>
     <row r="278" ht="24" customHeight="1" s="48">
       <c r="A278" s="43" t="inlineStr">
         <is>
@@ -14109,6 +14123,7 @@
       <c r="N299" s="51" t="n"/>
       <c r="O299" s="52" t="n"/>
     </row>
+    <row r="300"/>
     <row r="301" ht="24" customHeight="1" s="48">
       <c r="A301" s="43" t="inlineStr">
         <is>
@@ -14311,6 +14326,7 @@
       <c r="N322" s="51" t="n"/>
       <c r="O322" s="52" t="n"/>
     </row>
+    <row r="323"/>
     <row r="324" ht="24" customHeight="1" s="48">
       <c r="A324" s="43" t="inlineStr">
         <is>
@@ -14513,6 +14529,7 @@
       <c r="N345" s="51" t="n"/>
       <c r="O345" s="52" t="n"/>
     </row>
+    <row r="346"/>
     <row r="347" ht="24" customHeight="1" s="48">
       <c r="A347" s="43" t="inlineStr">
         <is>
@@ -14715,6 +14732,7 @@
       <c r="N368" s="51" t="n"/>
       <c r="O368" s="52" t="n"/>
     </row>
+    <row r="369"/>
     <row r="370" ht="24" customHeight="1" s="48">
       <c r="A370" s="43" t="inlineStr">
         <is>
@@ -14917,6 +14935,7 @@
       <c r="N391" s="51" t="n"/>
       <c r="O391" s="52" t="n"/>
     </row>
+    <row r="392"/>
     <row r="393" ht="24" customHeight="1" s="48">
       <c r="A393" s="43" t="inlineStr">
         <is>
@@ -15119,6 +15138,7 @@
       <c r="N414" s="51" t="n"/>
       <c r="O414" s="52" t="n"/>
     </row>
+    <row r="415"/>
     <row r="416" ht="24" customHeight="1" s="48">
       <c r="A416" s="43" t="inlineStr">
         <is>
@@ -15321,6 +15341,7 @@
       <c r="N437" s="51" t="n"/>
       <c r="O437" s="52" t="n"/>
     </row>
+    <row r="438"/>
     <row r="439" ht="24" customHeight="1" s="48">
       <c r="A439" s="43" t="inlineStr">
         <is>
@@ -15523,6 +15544,7 @@
       <c r="N460" s="51" t="n"/>
       <c r="O460" s="52" t="n"/>
     </row>
+    <row r="461"/>
     <row r="462" ht="24" customHeight="1" s="48">
       <c r="A462" s="43" t="inlineStr">
         <is>
@@ -15725,6 +15747,7 @@
       <c r="N483" s="51" t="n"/>
       <c r="O483" s="52" t="n"/>
     </row>
+    <row r="484"/>
     <row r="485" ht="24" customHeight="1" s="48">
       <c r="A485" s="43" t="inlineStr">
         <is>
@@ -15927,6 +15950,7 @@
       <c r="N506" s="51" t="n"/>
       <c r="O506" s="52" t="n"/>
     </row>
+    <row r="507"/>
     <row r="508" ht="24" customHeight="1" s="48">
       <c r="A508" s="43" t="inlineStr">
         <is>
@@ -16129,6 +16153,7 @@
       <c r="N529" s="51" t="n"/>
       <c r="O529" s="52" t="n"/>
     </row>
+    <row r="530"/>
     <row r="531" ht="24" customHeight="1" s="48">
       <c r="A531" s="43" t="inlineStr">
         <is>
@@ -16331,6 +16356,7 @@
       <c r="N552" s="51" t="n"/>
       <c r="O552" s="52" t="n"/>
     </row>
+    <row r="553"/>
     <row r="554" ht="24" customHeight="1" s="48">
       <c r="A554" s="43" t="inlineStr">
         <is>
@@ -16533,6 +16559,7 @@
       <c r="N575" s="51" t="n"/>
       <c r="O575" s="52" t="n"/>
     </row>
+    <row r="576"/>
     <row r="577" ht="24" customHeight="1" s="48">
       <c r="A577" s="43" t="inlineStr">
         <is>
@@ -16735,6 +16762,7 @@
       <c r="N598" s="51" t="n"/>
       <c r="O598" s="52" t="n"/>
     </row>
+    <row r="599"/>
     <row r="600" ht="24" customHeight="1" s="48">
       <c r="A600" s="43" t="inlineStr">
         <is>
@@ -16937,6 +16965,7 @@
       <c r="N621" s="51" t="n"/>
       <c r="O621" s="52" t="n"/>
     </row>
+    <row r="622"/>
     <row r="623" ht="24" customHeight="1" s="48">
       <c r="A623" s="43" t="inlineStr">
         <is>
@@ -17139,6 +17168,7 @@
       <c r="N644" s="51" t="n"/>
       <c r="O644" s="52" t="n"/>
     </row>
+    <row r="645"/>
     <row r="646" ht="24" customHeight="1" s="48">
       <c r="A646" s="43" t="inlineStr">
         <is>
@@ -17341,6 +17371,7 @@
       <c r="N667" s="51" t="n"/>
       <c r="O667" s="52" t="n"/>
     </row>
+    <row r="668"/>
     <row r="669" ht="24" customHeight="1" s="48">
       <c r="A669" s="43" t="inlineStr">
         <is>
@@ -17426,7 +17457,7 @@
       <c r="C672" s="42" t="n"/>
       <c r="D672" s="40" t="inlineStr">
         <is>
-          <t>임계값 초과 시 알림 자동 발생</t>
+          <t>기준 충족 시 알림 자동 발생</t>
         </is>
       </c>
       <c r="E672" s="41" t="n"/>
@@ -17543,6 +17574,7 @@
       <c r="N690" s="51" t="n"/>
       <c r="O690" s="52" t="n"/>
     </row>
+    <row r="691"/>
     <row r="692" ht="24" customHeight="1" s="48">
       <c r="A692" s="43" t="inlineStr">
         <is>
@@ -17745,6 +17777,7 @@
       <c r="N713" s="51" t="n"/>
       <c r="O713" s="52" t="n"/>
     </row>
+    <row r="714"/>
     <row r="715" ht="24" customHeight="1" s="48">
       <c r="A715" s="43" t="inlineStr">
         <is>
@@ -17947,6 +17980,7 @@
       <c r="N736" s="51" t="n"/>
       <c r="O736" s="52" t="n"/>
     </row>
+    <row r="737"/>
     <row r="738" ht="24" customHeight="1" s="48">
       <c r="A738" s="43" t="inlineStr">
         <is>
@@ -18149,6 +18183,7 @@
       <c r="N759" s="51" t="n"/>
       <c r="O759" s="52" t="n"/>
     </row>
+    <row r="760"/>
     <row r="761" ht="24" customHeight="1" s="48">
       <c r="A761" s="43" t="inlineStr">
         <is>
@@ -18351,6 +18386,7 @@
       <c r="N782" s="51" t="n"/>
       <c r="O782" s="52" t="n"/>
     </row>
+    <row r="783"/>
     <row r="784" ht="24" customHeight="1" s="48">
       <c r="A784" s="43" t="inlineStr">
         <is>
@@ -18553,6 +18589,7 @@
       <c r="N805" s="51" t="n"/>
       <c r="O805" s="52" t="n"/>
     </row>
+    <row r="806"/>
     <row r="807" ht="24" customHeight="1" s="48">
       <c r="A807" s="43" t="inlineStr">
         <is>
@@ -18755,6 +18792,7 @@
       <c r="N828" s="51" t="n"/>
       <c r="O828" s="52" t="n"/>
     </row>
+    <row r="829"/>
     <row r="830" ht="24" customHeight="1" s="48">
       <c r="A830" s="43" t="inlineStr">
         <is>
@@ -18957,6 +18995,7 @@
       <c r="N851" s="51" t="n"/>
       <c r="O851" s="52" t="n"/>
     </row>
+    <row r="852"/>
     <row r="853" ht="24" customHeight="1" s="48">
       <c r="A853" s="43" t="inlineStr">
         <is>
@@ -19159,6 +19198,7 @@
       <c r="N874" s="51" t="n"/>
       <c r="O874" s="52" t="n"/>
     </row>
+    <row r="875"/>
     <row r="876" ht="24" customHeight="1" s="48">
       <c r="A876" s="43" t="inlineStr">
         <is>
@@ -19744,6 +19784,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="28" t="inlineStr">
         <is>

--- a/Audit/JJ_PD_IP_M06_통합테스트결과서_v1.0_이노팸.xlsx
+++ b/Audit/JJ_PD_IP_M06_통합테스트결과서_v1.0_이노팸.xlsx
@@ -9120,7 +9120,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:S44"/>
+  <dimension ref="A2:S39"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col width="5.125" customWidth="1" style="2" min="1" max="1"/>
@@ -9141,7 +9141,6 @@
     <col width="9" customWidth="1" style="4" min="19" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2" ht="41.25" customFormat="1" customHeight="1" s="83">
       <c r="A2" s="72" t="inlineStr">
         <is>
@@ -9441,19 +9440,19 @@
       <c r="A9" s="32" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="76" t="inlineStr">
+      <c r="B9" s="0" t="inlineStr">
         <is>
           <t>TT-PAR-A01-02</t>
         </is>
       </c>
-      <c r="C9" s="76" t="inlineStr">
-        <is>
-          <t>민원 데이터 연계·수집</t>
+      <c r="C9" s="0" t="inlineStr">
+        <is>
+          <t>민원 데이터 수집 반영</t>
         </is>
       </c>
       <c r="D9" s="22" t="inlineStr">
         <is>
-          <t>PR-PAR-A01-04</t>
+          <t>PR-PAR-A01-07</t>
         </is>
       </c>
       <c r="E9" s="22" t="inlineStr">
@@ -9463,7 +9462,7 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>민원 원천 데이터 Open API 수집</t>
+          <t>수집 결과 대시보드 반영</t>
         </is>
       </c>
       <c r="G9" s="3" t="n">
@@ -9471,8 +9470,8 @@
       </c>
       <c r="H9" s="1" t="inlineStr">
         <is>
-          <t>- 120만덕콜센터·국민신문고·안전신문고 연계 배치 수행
-- 수집 로그 및 적재 건수 확인</t>
+          <t>- 배치 완료 후 대시보드 재진입
+- 최근 갱신 일시 및 KPI 수치 확인</t>
         </is>
       </c>
       <c r="I9" s="5" t="inlineStr">
@@ -9482,7 +9481,7 @@
       </c>
       <c r="J9" s="1" t="inlineStr">
         <is>
-          <t>- 민원 3종 데이터가 오류 없이 수집·정제되어 적재</t>
+          <t>- 최근 갱신 일시이 갱신되고 KPI 수치가 수집 결과와 일치</t>
         </is>
       </c>
       <c r="K9" s="3" t="n"/>
@@ -9493,7 +9492,8 @@
       <c r="P9" s="31" t="n"/>
       <c r="Q9" s="34" t="inlineStr">
         <is>
-          <t>REQ-SFR-005-02</t>
+          <t>REQ-SFR-003-07
+REQ-SFR-005-02</t>
         </is>
       </c>
     </row>
@@ -9501,11 +9501,19 @@
       <c r="A10" s="32" t="n">
         <v>5</v>
       </c>
-      <c r="B10" s="68" t="n"/>
-      <c r="C10" s="68" t="n"/>
+      <c r="B10" s="76" t="inlineStr">
+        <is>
+          <t>TT-PAR-A01-03</t>
+        </is>
+      </c>
+      <c r="C10" s="76" t="inlineStr">
+        <is>
+          <t>민원현황 GIS 조회</t>
+        </is>
+      </c>
       <c r="D10" s="22" t="inlineStr">
         <is>
-          <t>PR-PAR-A01-05</t>
+          <t>PR-PAR-A01-08</t>
         </is>
       </c>
       <c r="E10" s="22" t="inlineStr">
@@ -9513,18 +9521,18 @@
           <t>UI-PAR-002</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>불법주정차 민원·단속 데이터 연계</t>
+      <c r="F10" s="73" t="inlineStr">
+        <is>
+          <t>자세히 보기 이동 및 조회조건 승계</t>
         </is>
       </c>
       <c r="G10" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H10" s="1" t="inlineStr">
         <is>
-          <t>- 민원처리시스템 / 단속관리시스템 Open API 호출
-- 수집 건수 및 좌표 매핑 확인</t>
+          <t>- 대시보드 '불법주차 집중구역 순위' 영역의 [자세히 보기] 클릭
+- 민원현황 화면 진입 확인</t>
         </is>
       </c>
       <c r="I10" s="5" t="inlineStr">
@@ -9534,7 +9542,7 @@
       </c>
       <c r="J10" s="1" t="inlineStr">
         <is>
-          <t>- 민원·단속 데이터가 읍·면·동 및 좌표 기준으로 정상 매핑</t>
+          <t>- 민원현황 화면으로 이동하고 직전 조회 단위·기간 조건이 승계</t>
         </is>
       </c>
       <c r="K10" s="3" t="n"/>
@@ -9545,7 +9553,8 @@
       <c r="P10" s="31" t="n"/>
       <c r="Q10" s="34" t="inlineStr">
         <is>
-          <t>REQ-SFR-005-02</t>
+          <t>REQ-SFR-003-03
+REQ-SFR-003-07</t>
         </is>
       </c>
     </row>
@@ -9557,7 +9566,7 @@
       <c r="C11" s="68" t="n"/>
       <c r="D11" s="22" t="inlineStr">
         <is>
-          <t>PR-PAR-A01-06</t>
+          <t>PR-PAR-A01-09</t>
         </is>
       </c>
       <c r="E11" s="22" t="inlineStr">
@@ -9567,16 +9576,16 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>공영주차장 운영 데이터 연계</t>
+          <t>분석 레이어 전환</t>
         </is>
       </c>
       <c r="G11" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H11" s="1" t="inlineStr">
         <is>
-          <t>- 주차관제시스템 Open API 호출
-- 공영주차장 시설물 현황 적재 확인</t>
+          <t>- 레이어 설정에서 민원 다발 지역 / 단속 집중 지역 / 수요 부족 지역을 순차 선택
+- 민원 다발·단속 집중 레이어에서 [히트맵] 전환</t>
         </is>
       </c>
       <c r="I11" s="5" t="inlineStr">
@@ -9586,7 +9595,7 @@
       </c>
       <c r="J11" s="1" t="inlineStr">
         <is>
-          <t>- 공영주차장 운영·시설물 데이터가 적재되고 지도에 P 마커로 표출</t>
+          <t>- 선택한 레이어 1개만 활성화되고, 히트맵 전환 시 밀도 히트맵·그라데이션 범례로 표시</t>
         </is>
       </c>
       <c r="K11" s="3" t="n"/>
@@ -9597,7 +9606,7 @@
       <c r="P11" s="31" t="n"/>
       <c r="Q11" s="34" t="inlineStr">
         <is>
-          <t>REQ-SFR-005-02</t>
+          <t>REQ-SFR-003-09</t>
         </is>
       </c>
     </row>
@@ -9605,30 +9614,30 @@
       <c r="A12" s="32" t="n">
         <v>7</v>
       </c>
-      <c r="B12" s="69" t="n"/>
-      <c r="C12" s="69" t="n"/>
+      <c r="B12" s="68" t="n"/>
+      <c r="C12" s="68" t="n"/>
       <c r="D12" s="22" t="inlineStr">
         <is>
-          <t>PR-PAR-A01-07</t>
+          <t>PR-PAR-A01-10</t>
         </is>
       </c>
       <c r="E12" s="22" t="inlineStr">
         <is>
-          <t>UI-PAR-001</t>
+          <t>UI-PAR-002</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>수집 결과 대시보드 반영</t>
+          <t>공영주차장·행정동 경계 토글</t>
         </is>
       </c>
       <c r="G12" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H12" s="1" t="inlineStr">
         <is>
-          <t>- 배치 완료 후 대시보드 재진입
-- 최근 갱신 일시 및 KPI 수치 확인</t>
+          <t>- 공영주차장 토글 ON/OFF
+- 행정동 경계 토글 ON/OFF</t>
         </is>
       </c>
       <c r="I12" s="5" t="inlineStr">
@@ -9638,7 +9647,7 @@
       </c>
       <c r="J12" s="1" t="inlineStr">
         <is>
-          <t>- 최근 갱신 일시이 갱신되고 KPI 수치가 수집 결과와 일치</t>
+          <t>- 공영주차장 P 마커와 행정동 경계가 각각 표시/숨김 전환</t>
         </is>
       </c>
       <c r="K12" s="3" t="n"/>
@@ -9649,8 +9658,7 @@
       <c r="P12" s="31" t="n"/>
       <c r="Q12" s="34" t="inlineStr">
         <is>
-          <t>REQ-SFR-003-07
-REQ-SFR-005-02</t>
+          <t>REQ-SFR-003-09</t>
         </is>
       </c>
     </row>
@@ -9658,19 +9666,11 @@
       <c r="A13" s="32" t="n">
         <v>8</v>
       </c>
-      <c r="B13" s="76" t="inlineStr">
-        <is>
-          <t>TT-PAR-A01-03</t>
-        </is>
-      </c>
-      <c r="C13" s="76" t="inlineStr">
-        <is>
-          <t>민원현황 GIS 조회</t>
-        </is>
-      </c>
+      <c r="B13" s="69" t="n"/>
+      <c r="C13" s="69" t="n"/>
       <c r="D13" s="22" t="inlineStr">
         <is>
-          <t>PR-PAR-A01-08</t>
+          <t>PR-PAR-A01-11</t>
         </is>
       </c>
       <c r="E13" s="22" t="inlineStr">
@@ -9678,18 +9678,18 @@
           <t>UI-PAR-002</t>
         </is>
       </c>
-      <c r="F13" s="73" t="inlineStr">
-        <is>
-          <t>자세히 보기 이동 및 조회조건 승계</t>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>지역별 민원현황·집중구역 순위 동기화</t>
         </is>
       </c>
       <c r="G13" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H13" s="1" t="inlineStr">
         <is>
-          <t>- 대시보드 '불법주차 집중구역 순위' 영역의 [자세히 보기] 클릭
-- 민원현황 화면 진입 확인</t>
+          <t>- 조회 필터(행정구역/민원유형/위험단계) 변경
+- 우측 지역별 민원현황 및 불법주차 집중구역 순위 확인</t>
         </is>
       </c>
       <c r="I13" s="5" t="inlineStr">
@@ -9699,7 +9699,7 @@
       </c>
       <c r="J13" s="1" t="inlineStr">
         <is>
-          <t>- 민원현황 화면으로 이동하고 직전 조회 단위·기간 조건이 승계</t>
+          <t>- 지도·지역별 순위·집중구역 순위가 동일 조건 기준으로 동시 갱신</t>
         </is>
       </c>
       <c r="K13" s="3" t="n"/>
@@ -9710,8 +9710,7 @@
       <c r="P13" s="31" t="n"/>
       <c r="Q13" s="34" t="inlineStr">
         <is>
-          <t>REQ-SFR-003-03
-REQ-SFR-003-07</t>
+          <t>REQ-SFR-003-03</t>
         </is>
       </c>
     </row>
@@ -9719,30 +9718,39 @@
       <c r="A14" s="32" t="n">
         <v>9</v>
       </c>
-      <c r="B14" s="68" t="n"/>
-      <c r="C14" s="68" t="n"/>
+      <c r="B14" s="76" t="inlineStr">
+        <is>
+          <t>TT-PAR-A01-04</t>
+        </is>
+      </c>
+      <c r="C14" s="76" t="inlineStr">
+        <is>
+          <t>불법주차 집중구역 분석</t>
+        </is>
+      </c>
       <c r="D14" s="22" t="inlineStr">
         <is>
-          <t>PR-PAR-A01-09</t>
+          <t>PR-PAR-A01-12</t>
         </is>
       </c>
       <c r="E14" s="22" t="inlineStr">
         <is>
-          <t>UI-PAR-002</t>
-        </is>
-      </c>
-      <c r="F14" s="3" t="inlineStr">
-        <is>
-          <t>분석 레이어 전환</t>
+          <t>UI-PAR-003-01</t>
+        </is>
+      </c>
+      <c r="F14" s="73" t="inlineStr">
+        <is>
+          <t>집중구역 자동 도출 실행</t>
         </is>
       </c>
       <c r="G14" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H14" s="1" t="inlineStr">
         <is>
-          <t>- 레이어 설정에서 민원 다발 지역 / 단속 집중 지역 / 수요 부족 지역을 순차 선택
-- 민원 다발·단속 집중 레이어에서 [히트맵] 전환</t>
+          <t>- 분석·시뮬레이션 &gt; 불법 주차 불법 주차 집중 구역 분석 진입
+- 분석 지역(제주시), 분석 기간(최근3개월) 설정
+- [분석 실행] 클릭</t>
         </is>
       </c>
       <c r="I14" s="5" t="inlineStr">
@@ -9752,7 +9760,7 @@
       </c>
       <c r="J14" s="1" t="inlineStr">
         <is>
-          <t>- 선택한 레이어 1개만 활성화되고, 히트맵 전환 시 밀도 히트맵·그라데이션 범례로 표시</t>
+          <t>- 종합점수 기준으로 집중구역이 자동 도출되어 지도·순위가 갱신</t>
         </is>
       </c>
       <c r="K14" s="3" t="n"/>
@@ -9763,7 +9771,7 @@
       <c r="P14" s="31" t="n"/>
       <c r="Q14" s="34" t="inlineStr">
         <is>
-          <t>REQ-SFR-003-09</t>
+          <t>REQ-SFR-003-02</t>
         </is>
       </c>
     </row>
@@ -9775,26 +9783,25 @@
       <c r="C15" s="68" t="n"/>
       <c r="D15" s="22" t="inlineStr">
         <is>
-          <t>PR-PAR-A01-10</t>
-        </is>
-      </c>
-      <c r="E15" s="22" t="inlineStr">
-        <is>
-          <t>UI-PAR-002</t>
+          <t>PR-PAR-A01-13</t>
+        </is>
+      </c>
+      <c r="E15" s="67" t="inlineStr">
+        <is>
+          <t>UI-PAR-003-01</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>공영주차장·행정동 경계 토글</t>
+          <t>지도 마커 상세 팝업</t>
         </is>
       </c>
       <c r="G15" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H15" s="1" t="inlineStr">
         <is>
-          <t>- 공영주차장 토글 ON/OFF
-- 행정동 경계 토글 ON/OFF</t>
+          <t>- 지도상 집중구역 마커 클릭</t>
         </is>
       </c>
       <c r="I15" s="5" t="inlineStr">
@@ -9804,7 +9811,7 @@
       </c>
       <c r="J15" s="1" t="inlineStr">
         <is>
-          <t>- 공영주차장 P 마커와 행정동 경계가 각각 표시/숨김 전환</t>
+          <t>- 순위·구역명·민원 건수·단속 건수 팝업이 표출</t>
         </is>
       </c>
       <c r="K15" s="3" t="n"/>
@@ -9813,9 +9820,9 @@
       <c r="N15" s="3" t="n"/>
       <c r="O15" s="3" t="n"/>
       <c r="P15" s="31" t="n"/>
-      <c r="Q15" s="34" t="inlineStr">
-        <is>
-          <t>REQ-SFR-003-09</t>
+      <c r="Q15" s="67" t="inlineStr">
+        <is>
+          <t>REQ-SFR-003-02</t>
         </is>
       </c>
     </row>
@@ -9827,26 +9834,26 @@
       <c r="C16" s="69" t="n"/>
       <c r="D16" s="22" t="inlineStr">
         <is>
-          <t>PR-PAR-A01-11</t>
-        </is>
-      </c>
-      <c r="E16" s="22" t="inlineStr">
-        <is>
-          <t>UI-PAR-002</t>
+          <t>PR-PAR-A01-14</t>
+        </is>
+      </c>
+      <c r="E16" s="67" t="inlineStr">
+        <is>
+          <t>UI-PAR-004-01</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>지역별 민원현황·집중구역 순위 동기화</t>
+          <t>분석 결과 보고서 내보내기</t>
         </is>
       </c>
       <c r="G16" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H16" s="1" t="inlineStr">
         <is>
-          <t>- 조회 필터(행정구역/민원유형/위험단계) 변경
-- 우측 지역별 민원현황 및 불법주차 집중구역 순위 확인</t>
+          <t>- [내보내기] 클릭
+- 보고서·알림 &gt; 보고서 관리 진입</t>
         </is>
       </c>
       <c r="I16" s="5" t="inlineStr">
@@ -9856,7 +9863,7 @@
       </c>
       <c r="J16" s="1" t="inlineStr">
         <is>
-          <t>- 지도·지역별 순위·집중구역 순위가 동일 조건 기준으로 동시 갱신</t>
+          <t>- 직접 생성 보고서 목록에 보고서명·분석기간·생성일·생성자가 등록되고 PDF 다운로드 가능</t>
         </is>
       </c>
       <c r="K16" s="3" t="n"/>
@@ -9865,9 +9872,9 @@
       <c r="N16" s="3" t="n"/>
       <c r="O16" s="3" t="n"/>
       <c r="P16" s="31" t="n"/>
-      <c r="Q16" s="34" t="inlineStr">
-        <is>
-          <t>REQ-SFR-003-03</t>
+      <c r="Q16" s="67" t="inlineStr">
+        <is>
+          <t>REQ-SFR-003-10</t>
         </is>
       </c>
     </row>
@@ -9877,27 +9884,27 @@
       </c>
       <c r="B17" s="76" t="inlineStr">
         <is>
-          <t>TT-PAR-A01-04</t>
+          <t>TT-PAR-A01-05</t>
         </is>
       </c>
       <c r="C17" s="76" t="inlineStr">
         <is>
-          <t>불법주차 집중구역 분석</t>
+          <t>정책 효과 시뮬레이션</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
         <is>
-          <t>PR-PAR-A01-12</t>
-        </is>
-      </c>
-      <c r="E17" s="22" t="inlineStr">
-        <is>
-          <t>UI-PAR-003-01</t>
-        </is>
-      </c>
-      <c r="F17" s="73" t="inlineStr">
-        <is>
-          <t>집중구역 자동 도출 실행</t>
+          <t>PR-PAR-A01-15</t>
+        </is>
+      </c>
+      <c r="E17" s="67" t="inlineStr">
+        <is>
+          <t>UI-PAR-003-02</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>주차장 확충 시뮬레이션 실행</t>
         </is>
       </c>
       <c r="G17" s="3" t="n">
@@ -9905,19 +9912,19 @@
       </c>
       <c r="H17" s="1" t="inlineStr">
         <is>
-          <t>- 분석·시뮬레이션 &gt; 불법 주차 불법 주차 집중 구역 분석 진입
-- 분석 지역(제주시), 분석 기간(최근3개월) 설정
-- [분석 실행] 클릭</t>
+          <t>- 정책 유형 [주차장 확충] 선택
+- 대상 지역(제주 전체), 확충 방식(공한지 조성), 주차면 증설 수 입력
+- [시뮬레이션 실행] 클릭</t>
         </is>
       </c>
       <c r="I17" s="5" t="inlineStr">
         <is>
-          <t>교통행정과 담당자 권한 계정</t>
+          <t>차량관리과 담당자 권한 계정</t>
         </is>
       </c>
       <c r="J17" s="1" t="inlineStr">
         <is>
-          <t>- 종합점수 기준으로 집중구역이 자동 도출되어 지도·순위가 갱신</t>
+          <t>- 효과 예측 차트와 민원 감소 예측·혼잡도 개선 수치가 표출</t>
         </is>
       </c>
       <c r="K17" s="3" t="n"/>
@@ -9926,9 +9933,9 @@
       <c r="N17" s="3" t="n"/>
       <c r="O17" s="3" t="n"/>
       <c r="P17" s="31" t="n"/>
-      <c r="Q17" s="34" t="inlineStr">
-        <is>
-          <t>REQ-SFR-003-02</t>
+      <c r="Q17" s="67" t="inlineStr">
+        <is>
+          <t>REQ-SFR-003-05</t>
         </is>
       </c>
     </row>
@@ -9940,17 +9947,17 @@
       <c r="C18" s="68" t="n"/>
       <c r="D18" s="22" t="inlineStr">
         <is>
-          <t>PR-PAR-A01-13</t>
+          <t>PR-PAR-A01-16</t>
         </is>
       </c>
       <c r="E18" s="67" t="inlineStr">
         <is>
-          <t>UI-PAR-003-01</t>
-        </is>
-      </c>
-      <c r="F18" s="3" t="inlineStr">
-        <is>
-          <t>지도 마커 상세 팝업</t>
+          <t>UI-PAR-003-02-1</t>
+        </is>
+      </c>
+      <c r="F18" s="73" t="inlineStr">
+        <is>
+          <t>정책 유형 전환 및 변수 입력</t>
         </is>
       </c>
       <c r="G18" s="3" t="n">
@@ -9958,17 +9965,18 @@
       </c>
       <c r="H18" s="1" t="inlineStr">
         <is>
-          <t>- 지도상 집중구역 마커 클릭</t>
+          <t>- 정책 유형을 [이면도로 정비] / [요금제 적용]으로 전환
+- 정비유형 및 요금 인상율 선택 후 실행</t>
         </is>
       </c>
       <c r="I18" s="5" t="inlineStr">
         <is>
-          <t>교통행정과 담당자 권한 계정</t>
+          <t>차량관리과 담당자 권한 계정</t>
         </is>
       </c>
       <c r="J18" s="1" t="inlineStr">
         <is>
-          <t>- 순위·구역명·민원 건수·단속 건수 팝업이 표출</t>
+          <t>- 정책 유형별 입력 항목이 전환되고 각 조건 기준의 예측 결과가 산출</t>
         </is>
       </c>
       <c r="K18" s="3" t="n"/>
@@ -9979,7 +9987,7 @@
       <c r="P18" s="31" t="n"/>
       <c r="Q18" s="67" t="inlineStr">
         <is>
-          <t>REQ-SFR-003-02</t>
+          <t>REQ-SFR-003-05</t>
         </is>
       </c>
     </row>
@@ -9987,21 +9995,21 @@
       <c r="A19" s="32" t="n">
         <v>14</v>
       </c>
-      <c r="B19" s="69" t="n"/>
-      <c r="C19" s="69" t="n"/>
-      <c r="D19" s="22" t="inlineStr">
-        <is>
-          <t>PR-PAR-A01-14</t>
+      <c r="B19" s="68" t="n"/>
+      <c r="C19" s="68" t="n"/>
+      <c r="D19" s="67" t="inlineStr">
+        <is>
+          <t>PR-PAR-A01-17</t>
         </is>
       </c>
       <c r="E19" s="67" t="inlineStr">
         <is>
-          <t>UI-PAR-004-01</t>
+          <t>UI-PAR-003-02</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>분석 결과 보고서 내보내기</t>
+          <t>시나리오 비교</t>
         </is>
       </c>
       <c r="G19" s="3" t="n">
@@ -10009,18 +10017,17 @@
       </c>
       <c r="H19" s="1" t="inlineStr">
         <is>
-          <t>- [내보내기] 클릭
-- 보고서·알림 &gt; 보고서 관리 진입</t>
+          <t>- 하단 시나리오 비교 테이블 확인</t>
         </is>
       </c>
       <c r="I19" s="5" t="inlineStr">
         <is>
-          <t>교통행정과 담당자 권한 계정</t>
+          <t>차량관리과 담당자 권한 계정</t>
         </is>
       </c>
       <c r="J19" s="1" t="inlineStr">
         <is>
-          <t>- 직접 생성 보고서 목록에 보고서명·분석기간·생성일·생성자가 등록되고 PDF 다운로드 가능</t>
+          <t>- 시나리오별 민원 감소율·혼잡도 개선·비용 수준이 비교 표출되고 추천 배지가 부여</t>
         </is>
       </c>
       <c r="K19" s="3" t="n"/>
@@ -10031,7 +10038,8 @@
       <c r="P19" s="31" t="n"/>
       <c r="Q19" s="67" t="inlineStr">
         <is>
-          <t>REQ-SFR-003-10</t>
+          <t>REQ-SFR-003-12
+REQ-SFR-003-13</t>
         </is>
       </c>
     </row>
@@ -10039,39 +10047,29 @@
       <c r="A20" s="32" t="n">
         <v>15</v>
       </c>
-      <c r="B20" s="76" t="inlineStr">
-        <is>
-          <t>TT-PAR-A01-05</t>
-        </is>
-      </c>
-      <c r="C20" s="76" t="inlineStr">
-        <is>
-          <t>정책 효과 시뮬레이션</t>
-        </is>
-      </c>
-      <c r="D20" s="22" t="inlineStr">
-        <is>
-          <t>PR-PAR-A01-15</t>
+      <c r="B20" s="69" t="n"/>
+      <c r="C20" s="69" t="n"/>
+      <c r="D20" s="67" t="inlineStr">
+        <is>
+          <t>PR-PAR-A01-18</t>
         </is>
       </c>
       <c r="E20" s="67" t="inlineStr">
         <is>
-          <t>UI-PAR-003-02</t>
+          <t>UI-PAR-004-01</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>주차장 확충 시뮬레이션 실행</t>
+          <t>시뮬레이션 결과 보고서 내보내기</t>
         </is>
       </c>
       <c r="G20" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H20" s="1" t="inlineStr">
         <is>
-          <t>- 정책 유형 [주차장 확충] 선택
-- 대상 지역(제주 전체), 확충 방식(공한지 조성), 주차면 증설 수 입력
-- [시뮬레이션 실행] 클릭</t>
+          <t>- [내보내기] 클릭 후 보고서 관리 진입</t>
         </is>
       </c>
       <c r="I20" s="5" t="inlineStr">
@@ -10081,7 +10079,7 @@
       </c>
       <c r="J20" s="1" t="inlineStr">
         <is>
-          <t>- 효과 예측 차트와 민원 감소 예측·혼잡도 개선 수치가 표출</t>
+          <t>- 직접 생성 보고서 목록에 시뮬레이션 보고서가 등록되고 미리보기·다운로드 동작</t>
         </is>
       </c>
       <c r="K20" s="3" t="n"/>
@@ -10092,7 +10090,8 @@
       <c r="P20" s="31" t="n"/>
       <c r="Q20" s="67" t="inlineStr">
         <is>
-          <t>REQ-SFR-003-05</t>
+          <t>REQ-SFR-003-10
+REQ-SFR-003-12</t>
         </is>
       </c>
     </row>
@@ -10100,30 +10099,38 @@
       <c r="A21" s="32" t="n">
         <v>16</v>
       </c>
-      <c r="B21" s="68" t="n"/>
-      <c r="C21" s="68" t="n"/>
-      <c r="D21" s="22" t="inlineStr">
-        <is>
-          <t>PR-PAR-A01-16</t>
+      <c r="B21" s="76" t="inlineStr">
+        <is>
+          <t>TT-PAR-A01-06</t>
+        </is>
+      </c>
+      <c r="C21" s="76" t="inlineStr">
+        <is>
+          <t>생활권 시뮬레이션</t>
+        </is>
+      </c>
+      <c r="D21" s="67" t="inlineStr">
+        <is>
+          <t>PR-PAR-A01-19</t>
         </is>
       </c>
       <c r="E21" s="67" t="inlineStr">
         <is>
-          <t>UI-PAR-003-02-1</t>
-        </is>
-      </c>
-      <c r="F21" s="73" t="inlineStr">
-        <is>
-          <t>정책 유형 전환 및 변수 입력</t>
+          <t>UI-PAR-003-03</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>격자 기반 분석 실행</t>
         </is>
       </c>
       <c r="G21" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H21" s="1" t="inlineStr">
         <is>
-          <t>- 정책 유형을 [이면도로 정비] / [요금제 적용]으로 전환
-- 정비유형 및 요금 인상율 선택 후 실행</t>
+          <t>- 분석 내용(민원건수/수급/혼잡도), 분석 지역, 분석 기간, 격자 크기(500m) 설정
+- [생활권 분석 실행] 클릭</t>
         </is>
       </c>
       <c r="I21" s="5" t="inlineStr">
@@ -10133,7 +10140,7 @@
       </c>
       <c r="J21" s="1" t="inlineStr">
         <is>
-          <t>- 정책 유형별 입력 항목이 전환되고 각 조건 기준의 예측 결과가 산출</t>
+          <t>- 제주 전역 격자 기반 히트맵이 표출</t>
         </is>
       </c>
       <c r="K21" s="3" t="n"/>
@@ -10144,7 +10151,7 @@
       <c r="P21" s="31" t="n"/>
       <c r="Q21" s="67" t="inlineStr">
         <is>
-          <t>REQ-SFR-003-05</t>
+          <t>REQ-SFR-003-04</t>
         </is>
       </c>
     </row>
@@ -10156,25 +10163,25 @@
       <c r="C22" s="68" t="n"/>
       <c r="D22" s="67" t="inlineStr">
         <is>
-          <t>PR-PAR-A01-17</t>
+          <t>PR-PAR-A01-20</t>
         </is>
       </c>
       <c r="E22" s="67" t="inlineStr">
         <is>
-          <t>UI-PAR-003-02</t>
+          <t>UI-PAR-003-03</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>시나리오 비교</t>
+          <t>격자 클릭 상세 팝업</t>
         </is>
       </c>
       <c r="G22" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H22" s="1" t="inlineStr">
         <is>
-          <t>- 하단 시나리오 비교 테이블 확인</t>
+          <t>- 히트맵상 격자 클릭</t>
         </is>
       </c>
       <c r="I22" s="5" t="inlineStr">
@@ -10184,7 +10191,7 @@
       </c>
       <c r="J22" s="1" t="inlineStr">
         <is>
-          <t>- 시나리오별 민원 감소율·혼잡도 개선·비용 수준이 비교 표출되고 추천 배지가 부여</t>
+          <t>- 위험단계·구역명·민원 건수·유형별 세부 건수 팝업이 표출</t>
         </is>
       </c>
       <c r="K22" s="3" t="n"/>
@@ -10195,8 +10202,7 @@
       <c r="P22" s="31" t="n"/>
       <c r="Q22" s="67" t="inlineStr">
         <is>
-          <t>REQ-SFR-003-12
-REQ-SFR-003-13</t>
+          <t>REQ-SFR-003-04</t>
         </is>
       </c>
     </row>
@@ -10206,27 +10212,27 @@
       </c>
       <c r="B23" s="69" t="n"/>
       <c r="C23" s="69" t="n"/>
-      <c r="D23" s="67" t="inlineStr">
-        <is>
-          <t>PR-PAR-A01-18</t>
-        </is>
-      </c>
-      <c r="E23" s="67" t="inlineStr">
-        <is>
-          <t>UI-PAR-004-01</t>
-        </is>
-      </c>
-      <c r="F23" s="3" t="inlineStr">
-        <is>
-          <t>시뮬레이션 결과 보고서 내보내기</t>
+      <c r="D23" s="22" t="inlineStr">
+        <is>
+          <t>PR-PAR-A01-21</t>
+        </is>
+      </c>
+      <c r="E23" s="22" t="inlineStr">
+        <is>
+          <t>UI-PAR-003-03</t>
+        </is>
+      </c>
+      <c r="F23" s="73" t="inlineStr">
+        <is>
+          <t>분석결과요약·민원집중구역 표출</t>
         </is>
       </c>
       <c r="G23" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H23" s="1" t="inlineStr">
         <is>
-          <t>- [내보내기] 클릭 후 보고서 관리 진입</t>
+          <t>- 우측 분석 결과 요약 및 민원 집중 구역 목록 확인</t>
         </is>
       </c>
       <c r="I23" s="5" t="inlineStr">
@@ -10236,7 +10242,7 @@
       </c>
       <c r="J23" s="1" t="inlineStr">
         <is>
-          <t>- 직접 생성 보고서 목록에 시뮬레이션 보고서가 등록되고 미리보기·다운로드 동작</t>
+          <t>- 전체/유형별 격자 수가 집계되고 집중구역이 '동 + 격자 중심 POI' 명칭으로 표출</t>
         </is>
       </c>
       <c r="K23" s="3" t="n"/>
@@ -10245,10 +10251,9 @@
       <c r="N23" s="3" t="n"/>
       <c r="O23" s="3" t="n"/>
       <c r="P23" s="31" t="n"/>
-      <c r="Q23" s="67" t="inlineStr">
-        <is>
-          <t>REQ-SFR-003-10
-REQ-SFR-003-12</t>
+      <c r="Q23" s="34" t="inlineStr">
+        <is>
+          <t>REQ-SFR-003-04</t>
         </is>
       </c>
     </row>
@@ -10256,29 +10261,29 @@
       <c r="A24" s="32" t="n">
         <v>19</v>
       </c>
-      <c r="B24" s="76" t="inlineStr">
-        <is>
-          <t>TT-PAR-A01-06</t>
-        </is>
-      </c>
-      <c r="C24" s="76" t="inlineStr">
-        <is>
-          <t>생활권 시뮬레이션</t>
+      <c r="B24" s="67" t="inlineStr">
+        <is>
+          <t>TT-PAR-A01-07</t>
+        </is>
+      </c>
+      <c r="C24" s="73" t="inlineStr">
+        <is>
+          <t>구역 추천</t>
         </is>
       </c>
       <c r="D24" s="67" t="inlineStr">
         <is>
-          <t>PR-PAR-A01-19</t>
+          <t>PR-PAR-A01-22</t>
         </is>
       </c>
       <c r="E24" s="67" t="inlineStr">
         <is>
-          <t>UI-PAR-003-03</t>
+          <t>UI-PAR-003-04</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>격자 기반 분석 실행</t>
+          <t>구역 추천 실행</t>
         </is>
       </c>
       <c r="G24" s="3" t="n">
@@ -10286,8 +10291,8 @@
       </c>
       <c r="H24" s="1" t="inlineStr">
         <is>
-          <t>- 분석 내용(민원건수/수급/혼잡도), 분석 지역, 분석 기간, 격자 크기(500m) 설정
-- [생활권 분석 실행] 클릭</t>
+          <t>- 분석 내용(요금제 적용/공유주차제), 분석 지역, 분석 기간 설정
+- [구역 추천 실행] 클릭</t>
         </is>
       </c>
       <c r="I24" s="5" t="inlineStr">
@@ -10297,7 +10302,7 @@
       </c>
       <c r="J24" s="1" t="inlineStr">
         <is>
-          <t>- 제주 전역 격자 기반 히트맵이 표출</t>
+          <t>- 민원 증가 추세를 반영한 추천 구역이 자동 도출</t>
         </is>
       </c>
       <c r="K24" s="3" t="n"/>
@@ -10308,7 +10313,7 @@
       <c r="P24" s="31" t="n"/>
       <c r="Q24" s="67" t="inlineStr">
         <is>
-          <t>REQ-SFR-003-04</t>
+          <t>REQ-SFR-003-06</t>
         </is>
       </c>
     </row>
@@ -10317,20 +10322,20 @@
         <v>20</v>
       </c>
       <c r="B25" s="68" t="n"/>
-      <c r="C25" s="68" t="n"/>
-      <c r="D25" s="67" t="inlineStr">
-        <is>
-          <t>PR-PAR-A01-20</t>
-        </is>
-      </c>
-      <c r="E25" s="67" t="inlineStr">
-        <is>
-          <t>UI-PAR-003-03</t>
-        </is>
-      </c>
-      <c r="F25" s="3" t="inlineStr">
-        <is>
-          <t>격자 클릭 상세 팝업</t>
+      <c r="C25" s="74" t="n"/>
+      <c r="D25" s="22" t="inlineStr">
+        <is>
+          <t>PR-PAR-A01-23</t>
+        </is>
+      </c>
+      <c r="E25" s="22" t="inlineStr">
+        <is>
+          <t>UI-PAR-003-04</t>
+        </is>
+      </c>
+      <c r="F25" s="67" t="inlineStr">
+        <is>
+          <t>추천 구역 마커 표출</t>
         </is>
       </c>
       <c r="G25" s="3" t="n">
@@ -10338,7 +10343,7 @@
       </c>
       <c r="H25" s="1" t="inlineStr">
         <is>
-          <t>- 히트맵상 격자 클릭</t>
+          <t>- 지도상 추천 구역 핀 마커 확인 후 클릭</t>
         </is>
       </c>
       <c r="I25" s="5" t="inlineStr">
@@ -10348,7 +10353,7 @@
       </c>
       <c r="J25" s="1" t="inlineStr">
         <is>
-          <t>- 위험단계·구역명·민원 건수·유형별 세부 건수 팝업이 표출</t>
+          <t>- 요금제/공유주차제 유형별 마커가 구분 표시되고 구역명·민원 증가율·최근 건수 팝업이 표출</t>
         </is>
       </c>
       <c r="K25" s="3" t="n"/>
@@ -10357,9 +10362,9 @@
       <c r="N25" s="3" t="n"/>
       <c r="O25" s="3" t="n"/>
       <c r="P25" s="31" t="n"/>
-      <c r="Q25" s="67" t="inlineStr">
-        <is>
-          <t>REQ-SFR-003-04</t>
+      <c r="Q25" s="34" t="inlineStr">
+        <is>
+          <t>REQ-SFR-003-06</t>
         </is>
       </c>
     </row>
@@ -10368,20 +10373,20 @@
         <v>21</v>
       </c>
       <c r="B26" s="69" t="n"/>
-      <c r="C26" s="69" t="n"/>
+      <c r="C26" s="71" t="n"/>
       <c r="D26" s="22" t="inlineStr">
         <is>
-          <t>PR-PAR-A01-21</t>
+          <t>PR-PAR-A01-24</t>
         </is>
       </c>
       <c r="E26" s="22" t="inlineStr">
         <is>
-          <t>UI-PAR-003-03</t>
-        </is>
-      </c>
-      <c r="F26" s="73" t="inlineStr">
-        <is>
-          <t>분석결과요약·민원집중구역 표출</t>
+          <t>UI-PAR-003-04</t>
+        </is>
+      </c>
+      <c r="F26" s="67" t="inlineStr">
+        <is>
+          <t>추천 구역 순위 산정</t>
         </is>
       </c>
       <c r="G26" s="3" t="n">
@@ -10389,7 +10394,7 @@
       </c>
       <c r="H26" s="1" t="inlineStr">
         <is>
-          <t>- 우측 분석 결과 요약 및 민원 집중 구역 목록 확인</t>
+          <t>- 우측 추천 구역 순위 목록 확인</t>
         </is>
       </c>
       <c r="I26" s="5" t="inlineStr">
@@ -10399,7 +10404,7 @@
       </c>
       <c r="J26" s="1" t="inlineStr">
         <is>
-          <t>- 전체/유형별 격자 수가 집계되고 집중구역이 '동 + 격자 중심 POI' 명칭으로 표출</t>
+          <t>- 민원 증가 추세를 반영한 순위 기준으로 상위 구역이 표출</t>
         </is>
       </c>
       <c r="K26" s="3" t="n"/>
@@ -10410,7 +10415,7 @@
       <c r="P26" s="31" t="n"/>
       <c r="Q26" s="34" t="inlineStr">
         <is>
-          <t>REQ-SFR-003-04</t>
+          <t>REQ-SFR-003-06</t>
         </is>
       </c>
     </row>
@@ -10418,29 +10423,29 @@
       <c r="A27" s="32" t="n">
         <v>22</v>
       </c>
-      <c r="B27" s="67" t="inlineStr">
-        <is>
-          <t>TT-PAR-A01-07</t>
-        </is>
-      </c>
-      <c r="C27" s="73" t="inlineStr">
-        <is>
-          <t>구역 추천</t>
-        </is>
-      </c>
-      <c r="D27" s="67" t="inlineStr">
-        <is>
-          <t>PR-PAR-A01-22</t>
-        </is>
-      </c>
-      <c r="E27" s="67" t="inlineStr">
-        <is>
-          <t>UI-PAR-003-04</t>
-        </is>
-      </c>
-      <c r="F27" s="3" t="inlineStr">
-        <is>
-          <t>구역 추천 실행</t>
+      <c r="B27" s="76" t="inlineStr">
+        <is>
+          <t>TT-PAR-A01-08</t>
+        </is>
+      </c>
+      <c r="C27" s="76" t="inlineStr">
+        <is>
+          <t>투자우선순위 산정</t>
+        </is>
+      </c>
+      <c r="D27" s="22" t="inlineStr">
+        <is>
+          <t>PR-PAR-A01-25</t>
+        </is>
+      </c>
+      <c r="E27" s="22" t="inlineStr">
+        <is>
+          <t>UI-PAR-003-05</t>
+        </is>
+      </c>
+      <c r="F27" s="67" t="inlineStr">
+        <is>
+          <t>종합 지표 기반 우선순위 자동 산정</t>
         </is>
       </c>
       <c r="G27" s="3" t="n">
@@ -10448,8 +10453,7 @@
       </c>
       <c r="H27" s="1" t="inlineStr">
         <is>
-          <t>- 분석 내용(요금제 적용/공유주차제), 분석 지역, 분석 기간 설정
-- [구역 추천 실행] 클릭</t>
+          <t>- 분석·시뮬레이션 &gt; 투자우선순위 보드 진입</t>
         </is>
       </c>
       <c r="I27" s="5" t="inlineStr">
@@ -10459,7 +10463,7 @@
       </c>
       <c r="J27" s="1" t="inlineStr">
         <is>
-          <t>- 민원 증가 추세를 반영한 추천 구역이 자동 도출</t>
+          <t>- 설정된 가중치(안전위험도·민원빈도·이용패턴·사고이력)로 종합점수가 자동 산정</t>
         </is>
       </c>
       <c r="K27" s="3" t="n"/>
@@ -10468,9 +10472,9 @@
       <c r="N27" s="3" t="n"/>
       <c r="O27" s="3" t="n"/>
       <c r="P27" s="31" t="n"/>
-      <c r="Q27" s="67" t="inlineStr">
-        <is>
-          <t>REQ-SFR-003-06</t>
+      <c r="Q27" s="34" t="inlineStr">
+        <is>
+          <t>REQ-SFR-005-04</t>
         </is>
       </c>
     </row>
@@ -10479,20 +10483,20 @@
         <v>23</v>
       </c>
       <c r="B28" s="68" t="n"/>
-      <c r="C28" s="74" t="n"/>
+      <c r="C28" s="68" t="n"/>
       <c r="D28" s="22" t="inlineStr">
         <is>
-          <t>PR-PAR-A01-23</t>
+          <t>PR-PAR-A01-26</t>
         </is>
       </c>
       <c r="E28" s="22" t="inlineStr">
         <is>
-          <t>UI-PAR-003-04</t>
-        </is>
-      </c>
-      <c r="F28" s="67" t="inlineStr">
-        <is>
-          <t>추천 구역 마커 표출</t>
+          <t>UI-PAR-003-05</t>
+        </is>
+      </c>
+      <c r="F28" s="73" t="inlineStr">
+        <is>
+          <t>지도 마커 표출 및 상세 팝업</t>
         </is>
       </c>
       <c r="G28" s="3" t="n">
@@ -10500,7 +10504,7 @@
       </c>
       <c r="H28" s="1" t="inlineStr">
         <is>
-          <t>- 지도상 추천 구역 핀 마커 확인 후 클릭</t>
+          <t>- 공영주차장 P 핀 마커 확인 후 클릭</t>
         </is>
       </c>
       <c r="I28" s="5" t="inlineStr">
@@ -10510,7 +10514,7 @@
       </c>
       <c r="J28" s="1" t="inlineStr">
         <is>
-          <t>- 요금제/공유주차제 유형별 마커가 구분 표시되고 구역명·민원 증가율·최근 건수 팝업이 표출</t>
+          <t>- 우선순위(높음·중간·낮음)가 컬러로 구분되고 주차장명·종합점수·4개 지표 점수 팝업이 표출</t>
         </is>
       </c>
       <c r="K28" s="3" t="n"/>
@@ -10521,7 +10525,7 @@
       <c r="P28" s="31" t="n"/>
       <c r="Q28" s="34" t="inlineStr">
         <is>
-          <t>REQ-SFR-003-06</t>
+          <t>REQ-SFR-005-04</t>
         </is>
       </c>
     </row>
@@ -10530,20 +10534,20 @@
         <v>24</v>
       </c>
       <c r="B29" s="69" t="n"/>
-      <c r="C29" s="71" t="n"/>
+      <c r="C29" s="69" t="n"/>
       <c r="D29" s="22" t="inlineStr">
         <is>
-          <t>PR-PAR-A01-24</t>
+          <t>PR-PAR-A01-27</t>
         </is>
       </c>
       <c r="E29" s="22" t="inlineStr">
         <is>
-          <t>UI-PAR-003-04</t>
+          <t>UI-PAR-003-05</t>
         </is>
       </c>
       <c r="F29" s="67" t="inlineStr">
         <is>
-          <t>추천 구역 순위 산정</t>
+          <t>요약 카드·순위 리스트 정합성</t>
         </is>
       </c>
       <c r="G29" s="3" t="n">
@@ -10551,7 +10555,7 @@
       </c>
       <c r="H29" s="1" t="inlineStr">
         <is>
-          <t>- 우측 추천 구역 순위 목록 확인</t>
+          <t>- 상단 요약 카드와 우측 우선순위 리스트 대조</t>
         </is>
       </c>
       <c r="I29" s="5" t="inlineStr">
@@ -10561,7 +10565,7 @@
       </c>
       <c r="J29" s="1" t="inlineStr">
         <is>
-          <t>- 민원 증가 추세를 반영한 순위 기준으로 상위 구역이 표출</t>
+          <t>- 분석 대상 주차장 수·높음 우선순위 개소·최근 3개월 사고 건수가 리스트 집계와 일치</t>
         </is>
       </c>
       <c r="K29" s="3" t="n"/>
@@ -10572,7 +10576,7 @@
       <c r="P29" s="31" t="n"/>
       <c r="Q29" s="34" t="inlineStr">
         <is>
-          <t>REQ-SFR-003-06</t>
+          <t>REQ-SFR-005-04</t>
         </is>
       </c>
     </row>
@@ -10582,27 +10586,27 @@
       </c>
       <c r="B30" s="76" t="inlineStr">
         <is>
-          <t>TT-PAR-A01-08</t>
+          <t>TT-PAR-A01-09</t>
         </is>
       </c>
       <c r="C30" s="76" t="inlineStr">
         <is>
-          <t>투자우선순위 산정</t>
+          <t>위험단계 알림 관리</t>
         </is>
       </c>
       <c r="D30" s="22" t="inlineStr">
         <is>
-          <t>PR-PAR-A01-25</t>
+          <t>PR-PAR-A01-28</t>
         </is>
       </c>
       <c r="E30" s="22" t="inlineStr">
         <is>
-          <t>UI-PAR-003-05</t>
+          <t>UI-PAR-004-03</t>
         </is>
       </c>
       <c r="F30" s="67" t="inlineStr">
         <is>
-          <t>종합 지표 기반 우선순위 자동 산정</t>
+          <t>알림 기준 설정 저장</t>
         </is>
       </c>
       <c r="G30" s="3" t="n">
@@ -10610,17 +10614,18 @@
       </c>
       <c r="H30" s="1" t="inlineStr">
         <is>
-          <t>- 분석·시뮬레이션 &gt; 투자우선순위 보드 진입</t>
+          <t>- 보고서·알림 &gt; 위험단계 알림 관리 진입
+- 심각/경고/주의 기준 건수 입력 후 [저장] 클릭</t>
         </is>
       </c>
       <c r="I30" s="5" t="inlineStr">
         <is>
-          <t>차량관리과 담당자 권한 계정</t>
+          <t>시스템관리자 권한 계정</t>
         </is>
       </c>
       <c r="J30" s="1" t="inlineStr">
         <is>
-          <t>- 설정된 가중치(안전위험도·민원빈도·이용패턴·사고이력)로 종합점수가 자동 산정</t>
+          <t>- 설정한 위험단계 기준이 저장되고 재진입 시 유지</t>
         </is>
       </c>
       <c r="K30" s="3" t="n"/>
@@ -10631,7 +10636,7 @@
       <c r="P30" s="31" t="n"/>
       <c r="Q30" s="34" t="inlineStr">
         <is>
-          <t>REQ-SFR-005-04</t>
+          <t>REQ-SFR-003-08</t>
         </is>
       </c>
     </row>
@@ -10643,17 +10648,17 @@
       <c r="C31" s="68" t="n"/>
       <c r="D31" s="22" t="inlineStr">
         <is>
-          <t>PR-PAR-A01-26</t>
+          <t>PR-PAR-A01-29</t>
         </is>
       </c>
       <c r="E31" s="22" t="inlineStr">
         <is>
-          <t>UI-PAR-003-05</t>
-        </is>
-      </c>
-      <c r="F31" s="73" t="inlineStr">
-        <is>
-          <t>지도 마커 표출 및 상세 팝업</t>
+          <t>UI-PAR-004-03</t>
+        </is>
+      </c>
+      <c r="F31" s="67" t="inlineStr">
+        <is>
+          <t>수신자 등록 및 활성화 관리</t>
         </is>
       </c>
       <c r="G31" s="3" t="n">
@@ -10661,17 +10666,18 @@
       </c>
       <c r="H31" s="1" t="inlineStr">
         <is>
-          <t>- 공영주차장 P 핀 마커 확인 후 클릭</t>
+          <t>- [수신자 추가] 클릭 후 소속·이름·이메일·단계 그룹 입력
+- 활성화 토글 전환</t>
         </is>
       </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
-          <t>차량관리과 담당자 권한 계정</t>
+          <t>시스템관리자 권한 계정</t>
         </is>
       </c>
       <c r="J31" s="1" t="inlineStr">
         <is>
-          <t>- 우선순위(높음·중간·낮음)가 컬러로 구분되고 주차장명·종합점수·4개 지표 점수 팝업이 표출</t>
+          <t>- 수신자가 등록되고 활성화 여부에 따라 알림 발송 대상이 결정</t>
         </is>
       </c>
       <c r="K31" s="3" t="n"/>
@@ -10682,7 +10688,7 @@
       <c r="P31" s="31" t="n"/>
       <c r="Q31" s="34" t="inlineStr">
         <is>
-          <t>REQ-SFR-005-04</t>
+          <t>REQ-SFR-003-08</t>
         </is>
       </c>
     </row>
@@ -10690,21 +10696,21 @@
       <c r="A32" s="32" t="n">
         <v>27</v>
       </c>
-      <c r="B32" s="69" t="n"/>
-      <c r="C32" s="69" t="n"/>
+      <c r="B32" s="68" t="n"/>
+      <c r="C32" s="68" t="n"/>
       <c r="D32" s="22" t="inlineStr">
         <is>
-          <t>PR-PAR-A01-27</t>
+          <t>PR-PAR-A01-30</t>
         </is>
       </c>
       <c r="E32" s="22" t="inlineStr">
         <is>
-          <t>UI-PAR-003-05</t>
+          <t>UI-PAR-004-02</t>
         </is>
       </c>
       <c r="F32" s="67" t="inlineStr">
         <is>
-          <t>요약 카드·순위 리스트 정합성</t>
+          <t>기준 충족 시 알림 자동 발생</t>
         </is>
       </c>
       <c r="G32" s="3" t="n">
@@ -10712,17 +10718,18 @@
       </c>
       <c r="H32" s="1" t="inlineStr">
         <is>
-          <t>- 상단 요약 카드와 우측 우선순위 리스트 대조</t>
+          <t>- 기준 초과 민원 데이터 수집
+- 알림 발생 및 수신자 메일 통보 확인</t>
         </is>
       </c>
       <c r="I32" s="5" t="inlineStr">
         <is>
-          <t>차량관리과 담당자 권한 계정</t>
+          <t>시스템관리자 권한 계정</t>
         </is>
       </c>
       <c r="J32" s="1" t="inlineStr">
         <is>
-          <t>- 분석 대상 주차장 수·높음 우선순위 개소·최근 3개월 사고 건수가 리스트 집계와 일치</t>
+          <t>- 위험 단계별 알림이 자동 발생하고 활성화된 수신자에게 통보</t>
         </is>
       </c>
       <c r="K32" s="3" t="n"/>
@@ -10733,7 +10740,7 @@
       <c r="P32" s="31" t="n"/>
       <c r="Q32" s="34" t="inlineStr">
         <is>
-          <t>REQ-SFR-005-04</t>
+          <t>REQ-SFR-003-08</t>
         </is>
       </c>
     </row>
@@ -10741,38 +10748,30 @@
       <c r="A33" s="32" t="n">
         <v>28</v>
       </c>
-      <c r="B33" s="76" t="inlineStr">
-        <is>
-          <t>TT-PAR-A01-09</t>
-        </is>
-      </c>
-      <c r="C33" s="76" t="inlineStr">
-        <is>
-          <t>위험단계 알림 관리</t>
-        </is>
-      </c>
+      <c r="B33" s="69" t="n"/>
+      <c r="C33" s="69" t="n"/>
       <c r="D33" s="22" t="inlineStr">
         <is>
-          <t>PR-PAR-A01-28</t>
+          <t>PR-PAR-A01-31</t>
         </is>
       </c>
       <c r="E33" s="22" t="inlineStr">
         <is>
-          <t>UI-PAR-004-03</t>
+          <t>UI-PAR-004-02</t>
         </is>
       </c>
       <c r="F33" s="67" t="inlineStr">
         <is>
-          <t>알림 기준 설정 저장</t>
+          <t>알림 이력 조회</t>
         </is>
       </c>
       <c r="G33" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H33" s="1" t="inlineStr">
         <is>
-          <t>- 보고서·알림 &gt; 위험단계 알림 관리 진입
-- 심각/경고/주의 기준 건수 입력 후 [저장] 클릭</t>
+          <t>- 보고서·알림 &gt; 위험단계 알림 조회 진입
+- 단계/지역/기간 필터 적용</t>
         </is>
       </c>
       <c r="I33" s="5" t="inlineStr">
@@ -10782,7 +10781,7 @@
       </c>
       <c r="J33" s="1" t="inlineStr">
         <is>
-          <t>- 설정한 위험단계 기준이 저장되고 재진입 시 유지</t>
+          <t>- 필터 조건에 맞는 알림 이력이 단계 뱃지와 함께 목록으로 표출</t>
         </is>
       </c>
       <c r="K33" s="3" t="n"/>
@@ -10801,30 +10800,38 @@
       <c r="A34" s="32" t="n">
         <v>29</v>
       </c>
-      <c r="B34" s="68" t="n"/>
-      <c r="C34" s="68" t="n"/>
+      <c r="B34" s="76" t="inlineStr">
+        <is>
+          <t>TT-PAR-A01-10</t>
+        </is>
+      </c>
+      <c r="C34" s="76" t="inlineStr">
+        <is>
+          <t>보고서 자동 생성</t>
+        </is>
+      </c>
       <c r="D34" s="22" t="inlineStr">
         <is>
-          <t>PR-PAR-A01-29</t>
+          <t>PR-PAR-A01-32</t>
         </is>
       </c>
       <c r="E34" s="22" t="inlineStr">
         <is>
-          <t>UI-PAR-004-03</t>
+          <t>UI-PAR-004-01</t>
         </is>
       </c>
       <c r="F34" s="67" t="inlineStr">
         <is>
-          <t>수신자 등록 및 활성화 관리</t>
+          <t>배포주기·배포일자 설정</t>
         </is>
       </c>
       <c r="G34" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H34" s="1" t="inlineStr">
         <is>
-          <t>- [수신자 추가] 클릭 후 소속·이름·이메일·단계 그룹 입력
-- 활성화 토글 전환</t>
+          <t>- 보고서·알림 &gt; 보고서 관리 진입
+- 배포 주기, 배포 일자 선택 후 [보고서 자동 생성] 클릭</t>
         </is>
       </c>
       <c r="I34" s="5" t="inlineStr">
@@ -10834,7 +10841,7 @@
       </c>
       <c r="J34" s="1" t="inlineStr">
         <is>
-          <t>- 수신자가 등록되고 활성화 여부에 따라 알림 발송 대상이 결정</t>
+          <t>- 자동 생성 설정이 저장되고 자동 생성 보고서 목록에 항목이 추가</t>
         </is>
       </c>
       <c r="K34" s="3" t="n"/>
@@ -10845,7 +10852,9 @@
       <c r="P34" s="31" t="n"/>
       <c r="Q34" s="34" t="inlineStr">
         <is>
-          <t>REQ-SFR-003-08</t>
+          <t>REQ-SFR-003-11
+REQ-SFR-005-05
+REQ-SFR-005-06</t>
         </is>
       </c>
     </row>
@@ -10857,26 +10866,25 @@
       <c r="C35" s="68" t="n"/>
       <c r="D35" s="22" t="inlineStr">
         <is>
-          <t>PR-PAR-A01-30</t>
+          <t>PR-PAR-A01-33</t>
         </is>
       </c>
       <c r="E35" s="22" t="inlineStr">
         <is>
-          <t>UI-PAR-004-02</t>
+          <t>UI-PAR-004-01</t>
         </is>
       </c>
       <c r="F35" s="67" t="inlineStr">
         <is>
-          <t>기준 충족 시 알림 자동 발생</t>
+          <t>배포일자 도래 시 자동 생성</t>
         </is>
       </c>
       <c r="G35" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H35" s="1" t="inlineStr">
         <is>
-          <t>- 기준 초과 민원 데이터 수집
-- 알림 발생 및 수신자 메일 통보 확인</t>
+          <t>- 배포 일자 도래 후 목록 상태 확인</t>
         </is>
       </c>
       <c r="I35" s="5" t="inlineStr">
@@ -10886,7 +10894,7 @@
       </c>
       <c r="J35" s="1" t="inlineStr">
         <is>
-          <t>- 위험 단계별 알림이 자동 발생하고 활성화된 수신자에게 통보</t>
+          <t>- 보고서명(당해년도+배포주기+민원보고서)으로 생성되고 상태가 '대기'에서 '완료'로 전환</t>
         </is>
       </c>
       <c r="K35" s="3" t="n"/>
@@ -10897,7 +10905,7 @@
       <c r="P35" s="31" t="n"/>
       <c r="Q35" s="34" t="inlineStr">
         <is>
-          <t>REQ-SFR-003-08</t>
+          <t>REQ-SFR-005-05</t>
         </is>
       </c>
     </row>
@@ -10909,26 +10917,25 @@
       <c r="C36" s="69" t="n"/>
       <c r="D36" s="22" t="inlineStr">
         <is>
-          <t>PR-PAR-A01-31</t>
+          <t>PR-PAR-A01-34</t>
         </is>
       </c>
       <c r="E36" s="22" t="inlineStr">
         <is>
-          <t>UI-PAR-004-02</t>
-        </is>
-      </c>
-      <c r="F36" s="67" t="inlineStr">
-        <is>
-          <t>알림 이력 조회</t>
+          <t>UI-PAR-004-01</t>
+        </is>
+      </c>
+      <c r="F36" s="73" t="inlineStr">
+        <is>
+          <t>미리보기 및 다운로드</t>
         </is>
       </c>
       <c r="G36" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H36" s="1" t="inlineStr">
         <is>
-          <t>- 보고서·알림 &gt; 위험단계 알림 조회 진입
-- 단계/지역/기간 필터 적용</t>
+          <t>- [미리보기] 클릭 후 [PDF] 클릭</t>
         </is>
       </c>
       <c r="I36" s="5" t="inlineStr">
@@ -10938,7 +10945,7 @@
       </c>
       <c r="J36" s="1" t="inlineStr">
         <is>
-          <t>- 필터 조건에 맞는 알림 이력이 단계 뱃지와 함께 목록으로 표출</t>
+          <t>- 보고서 미리보기 팝업이 표출되고 PDF 형식으로 다운로드</t>
         </is>
       </c>
       <c r="K36" s="3" t="n"/>
@@ -10949,7 +10956,8 @@
       <c r="P36" s="31" t="n"/>
       <c r="Q36" s="34" t="inlineStr">
         <is>
-          <t>REQ-SFR-003-08</t>
+          <t>REQ-SFR-003-11
+REQ-SFR-005-05</t>
         </is>
       </c>
     </row>
@@ -10957,29 +10965,29 @@
       <c r="A37" s="32" t="n">
         <v>32</v>
       </c>
-      <c r="B37" s="76" t="inlineStr">
-        <is>
-          <t>TT-PAR-A01-10</t>
-        </is>
-      </c>
-      <c r="C37" s="76" t="inlineStr">
-        <is>
-          <t>보고서 자동 생성</t>
+      <c r="B37" s="67" t="inlineStr">
+        <is>
+          <t>TT-PAR-A01-11</t>
+        </is>
+      </c>
+      <c r="C37" s="67" t="inlineStr">
+        <is>
+          <t>AI 어시스턴트</t>
         </is>
       </c>
       <c r="D37" s="22" t="inlineStr">
         <is>
-          <t>PR-PAR-A01-32</t>
-        </is>
-      </c>
-      <c r="E37" s="22" t="inlineStr">
-        <is>
-          <t>UI-PAR-004-01</t>
-        </is>
-      </c>
-      <c r="F37" s="67" t="inlineStr">
-        <is>
-          <t>배포주기·배포일자 설정</t>
+          <t>PR-PAR-A01-35</t>
+        </is>
+      </c>
+      <c r="E37" s="67" t="inlineStr">
+        <is>
+          <t>UI-PAR-005</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>AI 어시스턴트 행정 지원(자연어 검색·조례 인용·민원 요약)</t>
         </is>
       </c>
       <c r="G37" s="3" t="n">
@@ -10987,18 +10995,18 @@
       </c>
       <c r="H37" s="1" t="inlineStr">
         <is>
-          <t>- 보고서·알림 &gt; 보고서 관리 진입
-- 배포 주기, 배포 일자 선택 후 [보고서 자동 생성] 클릭</t>
+          <t>- 자연어 질의로 sLLM 응답 및 RAG 조례 인용 카드 확인
+- 대량 민원 내용 보고용 요약 실행</t>
         </is>
       </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
-          <t>시스템관리자 권한 계정</t>
+          <t>교통행정과 담당자 권한 계정</t>
         </is>
       </c>
       <c r="J37" s="1" t="inlineStr">
         <is>
-          <t>- 자동 생성 설정이 저장되고 자동 생성 보고서 목록에 항목이 추가</t>
+          <t>- sLLM 자연어 응답·조례명·관련 조문 발췌 인용·민원 보고용 요약이 정상 표출</t>
         </is>
       </c>
       <c r="K37" s="3" t="n"/>
@@ -11007,11 +11015,11 @@
       <c r="N37" s="3" t="n"/>
       <c r="O37" s="3" t="n"/>
       <c r="P37" s="31" t="n"/>
-      <c r="Q37" s="34" t="inlineStr">
-        <is>
-          <t>REQ-SFR-003-11
-REQ-SFR-005-05
-REQ-SFR-005-06</t>
+      <c r="Q37" s="67" t="inlineStr">
+        <is>
+          <t>REQ-SFR-005-07
+REQ-SFR-005-08
+REQ-SFR-005-09</t>
         </is>
       </c>
     </row>
@@ -11019,29 +11027,37 @@
       <c r="A38" s="32" t="n">
         <v>33</v>
       </c>
-      <c r="B38" s="68" t="n"/>
-      <c r="C38" s="68" t="n"/>
+      <c r="B38" s="67" t="inlineStr">
+        <is>
+          <t>TT-PAR-A01-12</t>
+        </is>
+      </c>
+      <c r="C38" s="67" t="inlineStr">
+        <is>
+          <t>데이터 융합 통합분석</t>
+        </is>
+      </c>
       <c r="D38" s="22" t="inlineStr">
         <is>
-          <t>PR-PAR-A01-33</t>
-        </is>
-      </c>
-      <c r="E38" s="22" t="inlineStr">
-        <is>
-          <t>UI-PAR-004-01</t>
-        </is>
-      </c>
-      <c r="F38" s="67" t="inlineStr">
-        <is>
-          <t>배포일자 도래 시 자동 생성</t>
+          <t>PR-PAR-A01-37</t>
+        </is>
+      </c>
+      <c r="E38" s="67" t="inlineStr">
+        <is>
+          <t>UI-PAR-005</t>
+        </is>
+      </c>
+      <c r="F38" s="33" t="inlineStr">
+        <is>
+          <t>데이터 융합 통합분석</t>
         </is>
       </c>
       <c r="G38" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H38" s="1" t="inlineStr">
         <is>
-          <t>- 배포 일자 도래 후 목록 상태 확인</t>
+          <t>- 상관관계 분석 및 종합 인사이트 도출·보고서 반영 확인</t>
         </is>
       </c>
       <c r="I38" s="5" t="inlineStr">
@@ -11051,7 +11067,7 @@
       </c>
       <c r="J38" s="1" t="inlineStr">
         <is>
-          <t>- 보고서명(당해년도+배포주기+민원보고서)으로 생성되고 상태가 '대기'에서 '완료'로 전환</t>
+          <t>- 두 솔루션 데이터가 결합되어 상관관계·종합 인사이트가 시각화·보고서에 반영</t>
         </is>
       </c>
       <c r="K38" s="3" t="n"/>
@@ -11060,9 +11076,9 @@
       <c r="N38" s="3" t="n"/>
       <c r="O38" s="3" t="n"/>
       <c r="P38" s="31" t="n"/>
-      <c r="Q38" s="34" t="inlineStr">
-        <is>
-          <t>REQ-SFR-005-05</t>
+      <c r="Q38" s="67" t="inlineStr">
+        <is>
+          <t>REQ-SFR-005-01</t>
         </is>
       </c>
     </row>
@@ -11070,29 +11086,38 @@
       <c r="A39" s="32" t="n">
         <v>34</v>
       </c>
-      <c r="B39" s="69" t="n"/>
-      <c r="C39" s="69" t="n"/>
+      <c r="B39" s="67" t="inlineStr">
+        <is>
+          <t>TT-PAR-A01-13</t>
+        </is>
+      </c>
+      <c r="C39" s="67" t="inlineStr">
+        <is>
+          <t>타 지자체 확산 적용 구조</t>
+        </is>
+      </c>
       <c r="D39" s="22" t="inlineStr">
         <is>
-          <t>PR-PAR-A01-34</t>
-        </is>
-      </c>
-      <c r="E39" s="22" t="inlineStr">
-        <is>
-          <t>UI-PAR-004-01</t>
-        </is>
-      </c>
-      <c r="F39" s="73" t="inlineStr">
-        <is>
-          <t>미리보기 및 다운로드</t>
+          <t>PR-PAR-A01-39</t>
+        </is>
+      </c>
+      <c r="E39" s="67" t="inlineStr">
+        <is>
+          <t>공통(설정)</t>
+        </is>
+      </c>
+      <c r="F39" s="33" t="inlineStr">
+        <is>
+          <t>타 지자체 확산 적용 구조 검증</t>
         </is>
       </c>
       <c r="G39" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H39" s="1" t="inlineStr">
         <is>
-          <t>- [미리보기] 클릭 후 [PDF] 클릭</t>
+          <t>- 대상 지역·데이터 구조·분석 지표(가중치)를 타 지자체 기준으로 설정 변경
+- 변경 설정으로 주요 분석 기능 동작 확인</t>
         </is>
       </c>
       <c r="I39" s="5" t="inlineStr">
@@ -11102,7 +11127,7 @@
       </c>
       <c r="J39" s="1" t="inlineStr">
         <is>
-          <t>- 보고서 미리보기 팝업이 표출되고 PDF 형식으로 다운로드</t>
+          <t>- 지역 여건에 맞게 설정·조정되어 기능이 오류 없이 정상 동작</t>
         </is>
       </c>
       <c r="K39" s="3" t="n"/>
@@ -11111,351 +11136,51 @@
       <c r="N39" s="3" t="n"/>
       <c r="O39" s="3" t="n"/>
       <c r="P39" s="31" t="n"/>
-      <c r="Q39" s="34" t="inlineStr">
-        <is>
-          <t>REQ-SFR-003-11
-REQ-SFR-005-05</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="48" customHeight="1" s="48">
-      <c r="A40" s="32" t="n">
-        <v>35</v>
-      </c>
-      <c r="B40" s="67" t="inlineStr">
-        <is>
-          <t>TT-PAR-A01-11</t>
-        </is>
-      </c>
-      <c r="C40" s="67" t="inlineStr">
-        <is>
-          <t>AI 어시스턴트</t>
-        </is>
-      </c>
-      <c r="D40" s="22" t="inlineStr">
-        <is>
-          <t>PR-PAR-A01-35</t>
-        </is>
-      </c>
-      <c r="E40" s="67" t="inlineStr">
-        <is>
-          <t>UI-PAR-005</t>
-        </is>
-      </c>
-      <c r="F40" s="3" t="inlineStr">
-        <is>
-          <t>AI 어시스턴트 행정 지원(자연어 검색·조례 인용·민원 요약)</t>
-        </is>
-      </c>
-      <c r="G40" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H40" s="1" t="inlineStr">
-        <is>
-          <t>- 자연어 질의로 sLLM 응답 및 RAG 조례 인용 카드 확인
-- 대량 민원 내용 보고용 요약 실행</t>
-        </is>
-      </c>
-      <c r="I40" s="5" t="inlineStr">
-        <is>
-          <t>교통행정과 담당자 권한 계정</t>
-        </is>
-      </c>
-      <c r="J40" s="1" t="inlineStr">
-        <is>
-          <t>- sLLM 자연어 응답·조례명·관련 조문 발췌 인용·민원 보고용 요약이 정상 표출</t>
-        </is>
-      </c>
-      <c r="K40" s="3" t="n"/>
-      <c r="L40" s="3" t="n"/>
-      <c r="M40" s="21" t="n"/>
-      <c r="N40" s="3" t="n"/>
-      <c r="O40" s="3" t="n"/>
-      <c r="P40" s="31" t="n"/>
-      <c r="Q40" s="67" t="inlineStr">
-        <is>
-          <t>REQ-SFR-005-07
-REQ-SFR-005-08
-REQ-SFR-005-09</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="48" customHeight="1" s="48">
-      <c r="A41" s="32" t="n">
-        <v>36</v>
-      </c>
-      <c r="B41" s="67" t="inlineStr">
-        <is>
-          <t>TT-PAR-A01-12</t>
-        </is>
-      </c>
-      <c r="C41" s="67" t="inlineStr">
-        <is>
-          <t>비정형 행정문서 자동 수집·정형화</t>
-        </is>
-      </c>
-      <c r="D41" s="22" t="inlineStr">
-        <is>
-          <t>PR-PAR-A01-36</t>
-        </is>
-      </c>
-      <c r="E41" s="67" t="inlineStr">
-        <is>
-          <t>UI-PAR-005</t>
-        </is>
-      </c>
-      <c r="F41" s="33" t="inlineStr">
-        <is>
-          <t>비정형 행정문서 자동 수집·정형화(AI RPA/OCR)</t>
-        </is>
-      </c>
-      <c r="G41" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H41" s="1" t="inlineStr">
-        <is>
-          <t>- AI RPA/OCR로 비정형·스캔 문서 자동 수집·텍스트 추출
-- 정형화·구조화 적재 후 RAG 검색 연계 확인</t>
-        </is>
-      </c>
-      <c r="I41" s="5" t="inlineStr">
-        <is>
-          <t>시스템관리자 권한 계정</t>
-        </is>
-      </c>
-      <c r="J41" s="1" t="inlineStr">
-        <is>
-          <t>- 비정형 문서가 정형화 적재되고 RAG 검색 대상에 포함됨</t>
-        </is>
-      </c>
-      <c r="K41" s="3" t="n"/>
-      <c r="L41" s="3" t="n"/>
-      <c r="M41" s="21" t="n"/>
-      <c r="N41" s="3" t="n"/>
-      <c r="O41" s="3" t="n"/>
-      <c r="P41" s="31" t="n"/>
-      <c r="Q41" s="67" t="inlineStr">
-        <is>
-          <t>REQ-SFR-005-03
-REQ-SFR-005-08</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="32.1" customHeight="1" s="48">
-      <c r="A42" s="32" t="n">
-        <v>37</v>
-      </c>
-      <c r="B42" s="67" t="inlineStr">
-        <is>
-          <t>TT-PAR-A01-13</t>
-        </is>
-      </c>
-      <c r="C42" s="67" t="inlineStr">
-        <is>
-          <t>데이터 융합 통합분석</t>
-        </is>
-      </c>
-      <c r="D42" s="22" t="inlineStr">
-        <is>
-          <t>PR-PAR-A01-37</t>
-        </is>
-      </c>
-      <c r="E42" s="67" t="inlineStr">
-        <is>
-          <t>UI-PAR-005</t>
-        </is>
-      </c>
-      <c r="F42" s="33" t="inlineStr">
-        <is>
-          <t>데이터 융합 통합분석</t>
-        </is>
-      </c>
-      <c r="G42" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H42" s="1" t="inlineStr">
-        <is>
-          <t>- 상관관계 분석 및 종합 인사이트 도출·보고서 반영 확인</t>
-        </is>
-      </c>
-      <c r="I42" s="5" t="inlineStr">
-        <is>
-          <t>시스템관리자 권한 계정</t>
-        </is>
-      </c>
-      <c r="J42" s="1" t="inlineStr">
-        <is>
-          <t>- 두 솔루션 데이터가 결합되어 상관관계·종합 인사이트가 시각화·보고서에 반영</t>
-        </is>
-      </c>
-      <c r="K42" s="3" t="n"/>
-      <c r="L42" s="3" t="n"/>
-      <c r="M42" s="21" t="n"/>
-      <c r="N42" s="3" t="n"/>
-      <c r="O42" s="3" t="n"/>
-      <c r="P42" s="31" t="n"/>
-      <c r="Q42" s="67" t="inlineStr">
-        <is>
-          <t>REQ-SFR-005-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="32.1" customHeight="1" s="48">
-      <c r="A43" s="32" t="n">
-        <v>38</v>
-      </c>
-      <c r="B43" s="67" t="inlineStr">
-        <is>
-          <t>TT-PAR-A01-14</t>
-        </is>
-      </c>
-      <c r="C43" s="67" t="inlineStr">
-        <is>
-          <t>분석 모델 고도화·재학습</t>
-        </is>
-      </c>
-      <c r="D43" s="22" t="inlineStr">
-        <is>
-          <t>PR-PAR-A01-38</t>
-        </is>
-      </c>
-      <c r="E43" s="67" t="inlineStr">
-        <is>
-          <t>공통(배치)</t>
-        </is>
-      </c>
-      <c r="F43" s="33" t="inlineStr">
-        <is>
-          <t>분석 모델 재학습 및 고도화</t>
-        </is>
-      </c>
-      <c r="G43" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H43" s="1" t="inlineStr">
-        <is>
-          <t>- 신규 민원 유형·정책 변화 데이터 반영 후 재학습 배치 실행
-- 재학습 전후 성능 지표 및 개선 이력 확인</t>
-        </is>
-      </c>
-      <c r="I43" s="5" t="inlineStr">
-        <is>
-          <t>시스템관리자 권한 계정</t>
-        </is>
-      </c>
-      <c r="J43" s="1" t="inlineStr">
-        <is>
-          <t>- 재학습이 정상 완료되고 신규 유형이 분석에 반영되며 개선 이력이 관리됨</t>
-        </is>
-      </c>
-      <c r="K43" s="3" t="n"/>
-      <c r="L43" s="3" t="n"/>
-      <c r="M43" s="21" t="n"/>
-      <c r="N43" s="3" t="n"/>
-      <c r="O43" s="3" t="n"/>
-      <c r="P43" s="31" t="n"/>
-      <c r="Q43" s="67" t="inlineStr">
-        <is>
-          <t>REQ-SFR-003-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="32.1" customHeight="1" s="48">
-      <c r="A44" s="32" t="n">
-        <v>39</v>
-      </c>
-      <c r="B44" s="67" t="inlineStr">
-        <is>
-          <t>TT-PAR-A01-15</t>
-        </is>
-      </c>
-      <c r="C44" s="67" t="inlineStr">
-        <is>
-          <t>타 지자체 확산 적용 구조</t>
-        </is>
-      </c>
-      <c r="D44" s="22" t="inlineStr">
-        <is>
-          <t>PR-PAR-A01-39</t>
-        </is>
-      </c>
-      <c r="E44" s="67" t="inlineStr">
-        <is>
-          <t>공통(설정)</t>
-        </is>
-      </c>
-      <c r="F44" s="33" t="inlineStr">
-        <is>
-          <t>타 지자체 확산 적용 구조 검증</t>
-        </is>
-      </c>
-      <c r="G44" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H44" s="1" t="inlineStr">
-        <is>
-          <t>- 대상 지역·데이터 구조·분석 지표(가중치)를 타 지자체 기준으로 설정 변경
-- 변경 설정으로 주요 분석 기능 동작 확인</t>
-        </is>
-      </c>
-      <c r="I44" s="5" t="inlineStr">
-        <is>
-          <t>시스템관리자 권한 계정</t>
-        </is>
-      </c>
-      <c r="J44" s="1" t="inlineStr">
-        <is>
-          <t>- 지역 여건에 맞게 설정·조정되어 기능이 오류 없이 정상 동작</t>
-        </is>
-      </c>
-      <c r="K44" s="3" t="n"/>
-      <c r="L44" s="3" t="n"/>
-      <c r="M44" s="21" t="n"/>
-      <c r="N44" s="3" t="n"/>
-      <c r="O44" s="3" t="n"/>
-      <c r="P44" s="31" t="n"/>
-      <c r="Q44" s="67" t="inlineStr">
+      <c r="Q39" s="67" t="inlineStr">
         <is>
           <t>REQ-SFR-005-10</t>
         </is>
       </c>
     </row>
+    <row r="40" ht="48" customHeight="1" s="48"/>
+    <row r="41" ht="48" customHeight="1" s="48"/>
+    <row r="42" ht="32.1" customHeight="1" s="48"/>
+    <row r="43" ht="32.1" customHeight="1" s="48"/>
+    <row r="44" ht="32.1" customHeight="1" s="48"/>
   </sheetData>
-  <mergeCells count="34">
+  <mergeCells count="32">
     <mergeCell ref="C27:C29"/>
+    <mergeCell ref="C21:C23"/>
     <mergeCell ref="C4:C5"/>
-    <mergeCell ref="C33:C36"/>
+    <mergeCell ref="B34:B36"/>
     <mergeCell ref="E4:E5"/>
-    <mergeCell ref="C17:C19"/>
-    <mergeCell ref="B30:B32"/>
-    <mergeCell ref="C20:C23"/>
     <mergeCell ref="B24:B26"/>
-    <mergeCell ref="C9:C12"/>
+    <mergeCell ref="C30:C33"/>
+    <mergeCell ref="C10:C13"/>
+    <mergeCell ref="B17:B20"/>
     <mergeCell ref="Q4:Q5"/>
     <mergeCell ref="D4:D5"/>
     <mergeCell ref="J4:J5"/>
-    <mergeCell ref="C37:C39"/>
+    <mergeCell ref="C34:C36"/>
     <mergeCell ref="C6:C8"/>
     <mergeCell ref="C24:C26"/>
-    <mergeCell ref="B13:B16"/>
-    <mergeCell ref="C30:C32"/>
-    <mergeCell ref="B9:B12"/>
+    <mergeCell ref="B10:B13"/>
+    <mergeCell ref="C17:C20"/>
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="K4:M4"/>
     <mergeCell ref="G4:G5"/>
     <mergeCell ref="I4:I5"/>
+    <mergeCell ref="B21:B23"/>
+    <mergeCell ref="C14:C16"/>
     <mergeCell ref="A2:Q2"/>
-    <mergeCell ref="B33:B36"/>
+    <mergeCell ref="B30:B33"/>
     <mergeCell ref="N4:P4"/>
     <mergeCell ref="B27:B29"/>
-    <mergeCell ref="B17:B19"/>
-    <mergeCell ref="C13:C16"/>
     <mergeCell ref="B4:B5"/>
     <mergeCell ref="F4:F5"/>
-    <mergeCell ref="B20:B23"/>
     <mergeCell ref="H4:H5"/>
+    <mergeCell ref="B14:B16"/>
     <mergeCell ref="B6:B8"/>
-    <mergeCell ref="B37:B39"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.3937007874015748" right="0.3937007874015748" top="0.5905511811023623" bottom="0.5905511811023623" header="0.3149606299212598" footer="0.3149606299212598"/>
@@ -11477,14 +11202,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O897"/>
+  <dimension ref="A2:O782"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.875" defaultRowHeight="17.1"/>
   <cols>
     <col width="10" customWidth="1" style="48" min="1" max="3"/>
     <col width="12" customWidth="1" style="48" min="4" max="15"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2" ht="24" customHeight="1" s="48">
       <c r="A2" s="43" t="inlineStr">
         <is>
@@ -11687,7 +11411,6 @@
       <c r="N23" s="51" t="n"/>
       <c r="O23" s="52" t="n"/>
     </row>
-    <row r="24"/>
     <row r="25" ht="24" customHeight="1" s="48">
       <c r="A25" s="43" t="inlineStr">
         <is>
@@ -11890,7 +11613,6 @@
       <c r="N46" s="51" t="n"/>
       <c r="O46" s="52" t="n"/>
     </row>
-    <row r="47"/>
     <row r="48" ht="24" customHeight="1" s="48">
       <c r="A48" s="43" t="inlineStr">
         <is>
@@ -12093,7 +11815,6 @@
       <c r="N69" s="51" t="n"/>
       <c r="O69" s="52" t="n"/>
     </row>
-    <row r="70"/>
     <row r="71" ht="24" customHeight="1" s="48">
       <c r="A71" s="43" t="inlineStr">
         <is>
@@ -12129,7 +11850,7 @@
       <c r="C72" s="42" t="n"/>
       <c r="D72" s="40" t="inlineStr">
         <is>
-          <t>PR-PAR-A01-04</t>
+          <t>PR-PAR-A01-07</t>
         </is>
       </c>
       <c r="E72" s="41" t="n"/>
@@ -12179,7 +11900,7 @@
       <c r="C74" s="42" t="n"/>
       <c r="D74" s="40" t="inlineStr">
         <is>
-          <t>민원 원천 데이터 Open API 수집</t>
+          <t>수집 결과 대시보드 반영</t>
         </is>
       </c>
       <c r="E74" s="41" t="n"/>
@@ -12296,7 +12017,6 @@
       <c r="N92" s="51" t="n"/>
       <c r="O92" s="52" t="n"/>
     </row>
-    <row r="93"/>
     <row r="94" ht="24" customHeight="1" s="48">
       <c r="A94" s="43" t="inlineStr">
         <is>
@@ -12307,7 +12027,7 @@
       <c r="C94" s="42" t="n"/>
       <c r="D94" s="40" t="inlineStr">
         <is>
-          <t>TT-PAR-A01-02</t>
+          <t>TT-PAR-A01-03</t>
         </is>
       </c>
       <c r="E94" s="41" t="n"/>
@@ -12332,7 +12052,7 @@
       <c r="C95" s="42" t="n"/>
       <c r="D95" s="40" t="inlineStr">
         <is>
-          <t>PR-PAR-A01-05</t>
+          <t>PR-PAR-A01-08</t>
         </is>
       </c>
       <c r="E95" s="41" t="n"/>
@@ -12382,7 +12102,7 @@
       <c r="C97" s="42" t="n"/>
       <c r="D97" s="40" t="inlineStr">
         <is>
-          <t>불법주정차 민원·단속 데이터 연계</t>
+          <t>자세히 보기 이동 및 조회조건 승계</t>
         </is>
       </c>
       <c r="E97" s="41" t="n"/>
@@ -12499,7 +12219,6 @@
       <c r="N115" s="51" t="n"/>
       <c r="O115" s="52" t="n"/>
     </row>
-    <row r="116"/>
     <row r="117" ht="24" customHeight="1" s="48">
       <c r="A117" s="43" t="inlineStr">
         <is>
@@ -12510,7 +12229,7 @@
       <c r="C117" s="42" t="n"/>
       <c r="D117" s="40" t="inlineStr">
         <is>
-          <t>TT-PAR-A01-02</t>
+          <t>TT-PAR-A01-03</t>
         </is>
       </c>
       <c r="E117" s="41" t="n"/>
@@ -12535,7 +12254,7 @@
       <c r="C118" s="42" t="n"/>
       <c r="D118" s="40" t="inlineStr">
         <is>
-          <t>PR-PAR-A01-06</t>
+          <t>PR-PAR-A01-09</t>
         </is>
       </c>
       <c r="E118" s="41" t="n"/>
@@ -12585,7 +12304,7 @@
       <c r="C120" s="42" t="n"/>
       <c r="D120" s="40" t="inlineStr">
         <is>
-          <t>공영주차장 운영 데이터 연계</t>
+          <t>분석 레이어 전환</t>
         </is>
       </c>
       <c r="E120" s="41" t="n"/>
@@ -12702,7 +12421,6 @@
       <c r="N138" s="51" t="n"/>
       <c r="O138" s="52" t="n"/>
     </row>
-    <row r="139"/>
     <row r="140" ht="24" customHeight="1" s="48">
       <c r="A140" s="43" t="inlineStr">
         <is>
@@ -12713,7 +12431,7 @@
       <c r="C140" s="42" t="n"/>
       <c r="D140" s="40" t="inlineStr">
         <is>
-          <t>TT-PAR-A01-02</t>
+          <t>TT-PAR-A01-03</t>
         </is>
       </c>
       <c r="E140" s="41" t="n"/>
@@ -12738,7 +12456,7 @@
       <c r="C141" s="42" t="n"/>
       <c r="D141" s="40" t="inlineStr">
         <is>
-          <t>PR-PAR-A01-07</t>
+          <t>PR-PAR-A01-10</t>
         </is>
       </c>
       <c r="E141" s="41" t="n"/>
@@ -12763,7 +12481,7 @@
       <c r="C142" s="42" t="n"/>
       <c r="D142" s="40" t="inlineStr">
         <is>
-          <t>UI-PAR-001</t>
+          <t>UI-PAR-002</t>
         </is>
       </c>
       <c r="E142" s="41" t="n"/>
@@ -12788,7 +12506,7 @@
       <c r="C143" s="42" t="n"/>
       <c r="D143" s="40" t="inlineStr">
         <is>
-          <t>수집 결과 대시보드 반영</t>
+          <t>공영주차장·행정동 경계 토글</t>
         </is>
       </c>
       <c r="E143" s="41" t="n"/>
@@ -12905,7 +12623,6 @@
       <c r="N161" s="51" t="n"/>
       <c r="O161" s="52" t="n"/>
     </row>
-    <row r="162"/>
     <row r="163" ht="24" customHeight="1" s="48">
       <c r="A163" s="43" t="inlineStr">
         <is>
@@ -12941,7 +12658,7 @@
       <c r="C164" s="42" t="n"/>
       <c r="D164" s="40" t="inlineStr">
         <is>
-          <t>PR-PAR-A01-08</t>
+          <t>PR-PAR-A01-11</t>
         </is>
       </c>
       <c r="E164" s="41" t="n"/>
@@ -12991,7 +12708,7 @@
       <c r="C166" s="42" t="n"/>
       <c r="D166" s="40" t="inlineStr">
         <is>
-          <t>자세히 보기 이동 및 조회조건 승계</t>
+          <t>지역별 민원현황·집중구역 순위 동기화</t>
         </is>
       </c>
       <c r="E166" s="41" t="n"/>
@@ -13108,7 +12825,6 @@
       <c r="N184" s="51" t="n"/>
       <c r="O184" s="52" t="n"/>
     </row>
-    <row r="185"/>
     <row r="186" ht="24" customHeight="1" s="48">
       <c r="A186" s="43" t="inlineStr">
         <is>
@@ -13119,7 +12835,7 @@
       <c r="C186" s="42" t="n"/>
       <c r="D186" s="40" t="inlineStr">
         <is>
-          <t>TT-PAR-A01-03</t>
+          <t>TT-PAR-A01-04</t>
         </is>
       </c>
       <c r="E186" s="41" t="n"/>
@@ -13144,7 +12860,7 @@
       <c r="C187" s="42" t="n"/>
       <c r="D187" s="40" t="inlineStr">
         <is>
-          <t>PR-PAR-A01-09</t>
+          <t>PR-PAR-A01-12</t>
         </is>
       </c>
       <c r="E187" s="41" t="n"/>
@@ -13169,7 +12885,7 @@
       <c r="C188" s="42" t="n"/>
       <c r="D188" s="40" t="inlineStr">
         <is>
-          <t>UI-PAR-002</t>
+          <t>UI-PAR-003-01</t>
         </is>
       </c>
       <c r="E188" s="41" t="n"/>
@@ -13194,7 +12910,7 @@
       <c r="C189" s="42" t="n"/>
       <c r="D189" s="40" t="inlineStr">
         <is>
-          <t>분석 레이어 전환</t>
+          <t>집중구역 자동 도출 실행</t>
         </is>
       </c>
       <c r="E189" s="41" t="n"/>
@@ -13311,7 +13027,6 @@
       <c r="N207" s="51" t="n"/>
       <c r="O207" s="52" t="n"/>
     </row>
-    <row r="208"/>
     <row r="209" ht="24" customHeight="1" s="48">
       <c r="A209" s="43" t="inlineStr">
         <is>
@@ -13322,7 +13037,7 @@
       <c r="C209" s="42" t="n"/>
       <c r="D209" s="40" t="inlineStr">
         <is>
-          <t>TT-PAR-A01-03</t>
+          <t>TT-PAR-A01-04</t>
         </is>
       </c>
       <c r="E209" s="41" t="n"/>
@@ -13347,7 +13062,7 @@
       <c r="C210" s="42" t="n"/>
       <c r="D210" s="40" t="inlineStr">
         <is>
-          <t>PR-PAR-A01-10</t>
+          <t>PR-PAR-A01-13</t>
         </is>
       </c>
       <c r="E210" s="41" t="n"/>
@@ -13372,7 +13087,7 @@
       <c r="C211" s="42" t="n"/>
       <c r="D211" s="40" t="inlineStr">
         <is>
-          <t>UI-PAR-002</t>
+          <t>UI-PAR-003-01</t>
         </is>
       </c>
       <c r="E211" s="41" t="n"/>
@@ -13397,7 +13112,7 @@
       <c r="C212" s="42" t="n"/>
       <c r="D212" s="40" t="inlineStr">
         <is>
-          <t>공영주차장·행정동 경계 토글</t>
+          <t>지도 마커 상세 팝업</t>
         </is>
       </c>
       <c r="E212" s="41" t="n"/>
@@ -13514,7 +13229,6 @@
       <c r="N230" s="51" t="n"/>
       <c r="O230" s="52" t="n"/>
     </row>
-    <row r="231"/>
     <row r="232" ht="24" customHeight="1" s="48">
       <c r="A232" s="43" t="inlineStr">
         <is>
@@ -13525,7 +13239,7 @@
       <c r="C232" s="42" t="n"/>
       <c r="D232" s="40" t="inlineStr">
         <is>
-          <t>TT-PAR-A01-03</t>
+          <t>TT-PAR-A01-04</t>
         </is>
       </c>
       <c r="E232" s="41" t="n"/>
@@ -13550,7 +13264,7 @@
       <c r="C233" s="42" t="n"/>
       <c r="D233" s="40" t="inlineStr">
         <is>
-          <t>PR-PAR-A01-11</t>
+          <t>PR-PAR-A01-14</t>
         </is>
       </c>
       <c r="E233" s="41" t="n"/>
@@ -13575,7 +13289,7 @@
       <c r="C234" s="42" t="n"/>
       <c r="D234" s="40" t="inlineStr">
         <is>
-          <t>UI-PAR-002</t>
+          <t>UI-PAR-004-01</t>
         </is>
       </c>
       <c r="E234" s="41" t="n"/>
@@ -13600,7 +13314,7 @@
       <c r="C235" s="42" t="n"/>
       <c r="D235" s="40" t="inlineStr">
         <is>
-          <t>지역별 민원현황·집중구역 순위 동기화</t>
+          <t>분석 결과 보고서 내보내기</t>
         </is>
       </c>
       <c r="E235" s="41" t="n"/>
@@ -13717,7 +13431,6 @@
       <c r="N253" s="51" t="n"/>
       <c r="O253" s="52" t="n"/>
     </row>
-    <row r="254"/>
     <row r="255" ht="24" customHeight="1" s="48">
       <c r="A255" s="43" t="inlineStr">
         <is>
@@ -13728,7 +13441,7 @@
       <c r="C255" s="42" t="n"/>
       <c r="D255" s="40" t="inlineStr">
         <is>
-          <t>TT-PAR-A01-04</t>
+          <t>TT-PAR-A01-05</t>
         </is>
       </c>
       <c r="E255" s="41" t="n"/>
@@ -13753,7 +13466,7 @@
       <c r="C256" s="42" t="n"/>
       <c r="D256" s="40" t="inlineStr">
         <is>
-          <t>PR-PAR-A01-12</t>
+          <t>PR-PAR-A01-15</t>
         </is>
       </c>
       <c r="E256" s="41" t="n"/>
@@ -13778,7 +13491,7 @@
       <c r="C257" s="42" t="n"/>
       <c r="D257" s="40" t="inlineStr">
         <is>
-          <t>UI-PAR-003-01</t>
+          <t>UI-PAR-003-02</t>
         </is>
       </c>
       <c r="E257" s="41" t="n"/>
@@ -13803,7 +13516,7 @@
       <c r="C258" s="42" t="n"/>
       <c r="D258" s="40" t="inlineStr">
         <is>
-          <t>집중구역 자동 도출 실행</t>
+          <t>주차장 확충 시뮬레이션 실행</t>
         </is>
       </c>
       <c r="E258" s="41" t="n"/>
@@ -13920,7 +13633,6 @@
       <c r="N276" s="51" t="n"/>
       <c r="O276" s="52" t="n"/>
     </row>
-    <row r="277"/>
     <row r="278" ht="24" customHeight="1" s="48">
       <c r="A278" s="43" t="inlineStr">
         <is>
@@ -13931,7 +13643,7 @@
       <c r="C278" s="42" t="n"/>
       <c r="D278" s="40" t="inlineStr">
         <is>
-          <t>TT-PAR-A01-04</t>
+          <t>TT-PAR-A01-05</t>
         </is>
       </c>
       <c r="E278" s="41" t="n"/>
@@ -13956,7 +13668,7 @@
       <c r="C279" s="42" t="n"/>
       <c r="D279" s="40" t="inlineStr">
         <is>
-          <t>PR-PAR-A01-13</t>
+          <t>PR-PAR-A01-16</t>
         </is>
       </c>
       <c r="E279" s="41" t="n"/>
@@ -13981,7 +13693,7 @@
       <c r="C280" s="42" t="n"/>
       <c r="D280" s="40" t="inlineStr">
         <is>
-          <t>UI-PAR-003-01</t>
+          <t>UI-PAR-003-02-1</t>
         </is>
       </c>
       <c r="E280" s="41" t="n"/>
@@ -14006,7 +13718,7 @@
       <c r="C281" s="42" t="n"/>
       <c r="D281" s="40" t="inlineStr">
         <is>
-          <t>지도 마커 상세 팝업</t>
+          <t>정책 유형 전환 및 변수 입력</t>
         </is>
       </c>
       <c r="E281" s="41" t="n"/>
@@ -14123,7 +13835,6 @@
       <c r="N299" s="51" t="n"/>
       <c r="O299" s="52" t="n"/>
     </row>
-    <row r="300"/>
     <row r="301" ht="24" customHeight="1" s="48">
       <c r="A301" s="43" t="inlineStr">
         <is>
@@ -14134,7 +13845,7 @@
       <c r="C301" s="42" t="n"/>
       <c r="D301" s="40" t="inlineStr">
         <is>
-          <t>TT-PAR-A01-04</t>
+          <t>TT-PAR-A01-05</t>
         </is>
       </c>
       <c r="E301" s="41" t="n"/>
@@ -14159,7 +13870,7 @@
       <c r="C302" s="42" t="n"/>
       <c r="D302" s="40" t="inlineStr">
         <is>
-          <t>PR-PAR-A01-14</t>
+          <t>PR-PAR-A01-17</t>
         </is>
       </c>
       <c r="E302" s="41" t="n"/>
@@ -14184,7 +13895,7 @@
       <c r="C303" s="42" t="n"/>
       <c r="D303" s="40" t="inlineStr">
         <is>
-          <t>UI-PAR-004-01</t>
+          <t>UI-PAR-003-02</t>
         </is>
       </c>
       <c r="E303" s="41" t="n"/>
@@ -14209,7 +13920,7 @@
       <c r="C304" s="42" t="n"/>
       <c r="D304" s="40" t="inlineStr">
         <is>
-          <t>분석 결과 보고서 내보내기</t>
+          <t>시나리오 비교</t>
         </is>
       </c>
       <c r="E304" s="41" t="n"/>
@@ -14326,7 +14037,6 @@
       <c r="N322" s="51" t="n"/>
       <c r="O322" s="52" t="n"/>
     </row>
-    <row r="323"/>
     <row r="324" ht="24" customHeight="1" s="48">
       <c r="A324" s="43" t="inlineStr">
         <is>
@@ -14362,7 +14072,7 @@
       <c r="C325" s="42" t="n"/>
       <c r="D325" s="40" t="inlineStr">
         <is>
-          <t>PR-PAR-A01-15</t>
+          <t>PR-PAR-A01-18</t>
         </is>
       </c>
       <c r="E325" s="41" t="n"/>
@@ -14387,7 +14097,7 @@
       <c r="C326" s="42" t="n"/>
       <c r="D326" s="40" t="inlineStr">
         <is>
-          <t>UI-PAR-003-02</t>
+          <t>UI-PAR-004-01</t>
         </is>
       </c>
       <c r="E326" s="41" t="n"/>
@@ -14412,7 +14122,7 @@
       <c r="C327" s="42" t="n"/>
       <c r="D327" s="40" t="inlineStr">
         <is>
-          <t>주차장 확충 시뮬레이션 실행</t>
+          <t>시뮬레이션 결과 보고서 내보내기</t>
         </is>
       </c>
       <c r="E327" s="41" t="n"/>
@@ -14529,7 +14239,6 @@
       <c r="N345" s="51" t="n"/>
       <c r="O345" s="52" t="n"/>
     </row>
-    <row r="346"/>
     <row r="347" ht="24" customHeight="1" s="48">
       <c r="A347" s="43" t="inlineStr">
         <is>
@@ -14540,7 +14249,7 @@
       <c r="C347" s="42" t="n"/>
       <c r="D347" s="40" t="inlineStr">
         <is>
-          <t>TT-PAR-A01-05</t>
+          <t>TT-PAR-A01-06</t>
         </is>
       </c>
       <c r="E347" s="41" t="n"/>
@@ -14565,7 +14274,7 @@
       <c r="C348" s="42" t="n"/>
       <c r="D348" s="40" t="inlineStr">
         <is>
-          <t>PR-PAR-A01-16</t>
+          <t>PR-PAR-A01-19</t>
         </is>
       </c>
       <c r="E348" s="41" t="n"/>
@@ -14590,7 +14299,7 @@
       <c r="C349" s="42" t="n"/>
       <c r="D349" s="40" t="inlineStr">
         <is>
-          <t>UI-PAR-003-02-1</t>
+          <t>UI-PAR-003-03</t>
         </is>
       </c>
       <c r="E349" s="41" t="n"/>
@@ -14615,7 +14324,7 @@
       <c r="C350" s="42" t="n"/>
       <c r="D350" s="40" t="inlineStr">
         <is>
-          <t>정책 유형 전환 및 변수 입력</t>
+          <t>격자 기반 분석 실행</t>
         </is>
       </c>
       <c r="E350" s="41" t="n"/>
@@ -14732,7 +14441,6 @@
       <c r="N368" s="51" t="n"/>
       <c r="O368" s="52" t="n"/>
     </row>
-    <row r="369"/>
     <row r="370" ht="24" customHeight="1" s="48">
       <c r="A370" s="43" t="inlineStr">
         <is>
@@ -14743,7 +14451,7 @@
       <c r="C370" s="42" t="n"/>
       <c r="D370" s="40" t="inlineStr">
         <is>
-          <t>TT-PAR-A01-05</t>
+          <t>TT-PAR-A01-06</t>
         </is>
       </c>
       <c r="E370" s="41" t="n"/>
@@ -14768,7 +14476,7 @@
       <c r="C371" s="42" t="n"/>
       <c r="D371" s="40" t="inlineStr">
         <is>
-          <t>PR-PAR-A01-17</t>
+          <t>PR-PAR-A01-20</t>
         </is>
       </c>
       <c r="E371" s="41" t="n"/>
@@ -14793,7 +14501,7 @@
       <c r="C372" s="42" t="n"/>
       <c r="D372" s="40" t="inlineStr">
         <is>
-          <t>UI-PAR-003-02</t>
+          <t>UI-PAR-003-03</t>
         </is>
       </c>
       <c r="E372" s="41" t="n"/>
@@ -14818,7 +14526,7 @@
       <c r="C373" s="42" t="n"/>
       <c r="D373" s="40" t="inlineStr">
         <is>
-          <t>시나리오 비교</t>
+          <t>격자 클릭 상세 팝업</t>
         </is>
       </c>
       <c r="E373" s="41" t="n"/>
@@ -14935,7 +14643,6 @@
       <c r="N391" s="51" t="n"/>
       <c r="O391" s="52" t="n"/>
     </row>
-    <row r="392"/>
     <row r="393" ht="24" customHeight="1" s="48">
       <c r="A393" s="43" t="inlineStr">
         <is>
@@ -14946,7 +14653,7 @@
       <c r="C393" s="42" t="n"/>
       <c r="D393" s="40" t="inlineStr">
         <is>
-          <t>TT-PAR-A01-05</t>
+          <t>TT-PAR-A01-06</t>
         </is>
       </c>
       <c r="E393" s="41" t="n"/>
@@ -14971,7 +14678,7 @@
       <c r="C394" s="42" t="n"/>
       <c r="D394" s="40" t="inlineStr">
         <is>
-          <t>PR-PAR-A01-18</t>
+          <t>PR-PAR-A01-21</t>
         </is>
       </c>
       <c r="E394" s="41" t="n"/>
@@ -14996,7 +14703,7 @@
       <c r="C395" s="42" t="n"/>
       <c r="D395" s="40" t="inlineStr">
         <is>
-          <t>UI-PAR-004-01</t>
+          <t>UI-PAR-003-03</t>
         </is>
       </c>
       <c r="E395" s="41" t="n"/>
@@ -15021,7 +14728,7 @@
       <c r="C396" s="42" t="n"/>
       <c r="D396" s="40" t="inlineStr">
         <is>
-          <t>시뮬레이션 결과 보고서 내보내기</t>
+          <t>분석결과요약·민원집중구역 표출</t>
         </is>
       </c>
       <c r="E396" s="41" t="n"/>
@@ -15138,7 +14845,6 @@
       <c r="N414" s="51" t="n"/>
       <c r="O414" s="52" t="n"/>
     </row>
-    <row r="415"/>
     <row r="416" ht="24" customHeight="1" s="48">
       <c r="A416" s="43" t="inlineStr">
         <is>
@@ -15149,7 +14855,7 @@
       <c r="C416" s="42" t="n"/>
       <c r="D416" s="40" t="inlineStr">
         <is>
-          <t>TT-PAR-A01-06</t>
+          <t>TT-PAR-A01-07</t>
         </is>
       </c>
       <c r="E416" s="41" t="n"/>
@@ -15174,7 +14880,7 @@
       <c r="C417" s="42" t="n"/>
       <c r="D417" s="40" t="inlineStr">
         <is>
-          <t>PR-PAR-A01-19</t>
+          <t>PR-PAR-A01-22</t>
         </is>
       </c>
       <c r="E417" s="41" t="n"/>
@@ -15199,7 +14905,7 @@
       <c r="C418" s="42" t="n"/>
       <c r="D418" s="40" t="inlineStr">
         <is>
-          <t>UI-PAR-003-03</t>
+          <t>UI-PAR-003-04</t>
         </is>
       </c>
       <c r="E418" s="41" t="n"/>
@@ -15224,7 +14930,7 @@
       <c r="C419" s="42" t="n"/>
       <c r="D419" s="40" t="inlineStr">
         <is>
-          <t>격자 기반 분석 실행</t>
+          <t>구역 추천 실행</t>
         </is>
       </c>
       <c r="E419" s="41" t="n"/>
@@ -15341,7 +15047,6 @@
       <c r="N437" s="51" t="n"/>
       <c r="O437" s="52" t="n"/>
     </row>
-    <row r="438"/>
     <row r="439" ht="24" customHeight="1" s="48">
       <c r="A439" s="43" t="inlineStr">
         <is>
@@ -15352,7 +15057,7 @@
       <c r="C439" s="42" t="n"/>
       <c r="D439" s="40" t="inlineStr">
         <is>
-          <t>TT-PAR-A01-06</t>
+          <t>TT-PAR-A01-07</t>
         </is>
       </c>
       <c r="E439" s="41" t="n"/>
@@ -15377,7 +15082,7 @@
       <c r="C440" s="42" t="n"/>
       <c r="D440" s="40" t="inlineStr">
         <is>
-          <t>PR-PAR-A01-20</t>
+          <t>PR-PAR-A01-23</t>
         </is>
       </c>
       <c r="E440" s="41" t="n"/>
@@ -15402,7 +15107,7 @@
       <c r="C441" s="42" t="n"/>
       <c r="D441" s="40" t="inlineStr">
         <is>
-          <t>UI-PAR-003-03</t>
+          <t>UI-PAR-003-04</t>
         </is>
       </c>
       <c r="E441" s="41" t="n"/>
@@ -15427,7 +15132,7 @@
       <c r="C442" s="42" t="n"/>
       <c r="D442" s="40" t="inlineStr">
         <is>
-          <t>격자 클릭 상세 팝업</t>
+          <t>추천 구역 마커 표출</t>
         </is>
       </c>
       <c r="E442" s="41" t="n"/>
@@ -15544,7 +15249,6 @@
       <c r="N460" s="51" t="n"/>
       <c r="O460" s="52" t="n"/>
     </row>
-    <row r="461"/>
     <row r="462" ht="24" customHeight="1" s="48">
       <c r="A462" s="43" t="inlineStr">
         <is>
@@ -15555,7 +15259,7 @@
       <c r="C462" s="42" t="n"/>
       <c r="D462" s="40" t="inlineStr">
         <is>
-          <t>TT-PAR-A01-06</t>
+          <t>TT-PAR-A01-07</t>
         </is>
       </c>
       <c r="E462" s="41" t="n"/>
@@ -15580,7 +15284,7 @@
       <c r="C463" s="42" t="n"/>
       <c r="D463" s="40" t="inlineStr">
         <is>
-          <t>PR-PAR-A01-21</t>
+          <t>PR-PAR-A01-24</t>
         </is>
       </c>
       <c r="E463" s="41" t="n"/>
@@ -15605,7 +15309,7 @@
       <c r="C464" s="42" t="n"/>
       <c r="D464" s="40" t="inlineStr">
         <is>
-          <t>UI-PAR-003-03</t>
+          <t>UI-PAR-003-04</t>
         </is>
       </c>
       <c r="E464" s="41" t="n"/>
@@ -15630,7 +15334,7 @@
       <c r="C465" s="42" t="n"/>
       <c r="D465" s="40" t="inlineStr">
         <is>
-          <t>분석결과요약·민원집중구역 표출</t>
+          <t>추천 구역 순위 산정</t>
         </is>
       </c>
       <c r="E465" s="41" t="n"/>
@@ -15747,7 +15451,6 @@
       <c r="N483" s="51" t="n"/>
       <c r="O483" s="52" t="n"/>
     </row>
-    <row r="484"/>
     <row r="485" ht="24" customHeight="1" s="48">
       <c r="A485" s="43" t="inlineStr">
         <is>
@@ -15758,7 +15461,7 @@
       <c r="C485" s="42" t="n"/>
       <c r="D485" s="40" t="inlineStr">
         <is>
-          <t>TT-PAR-A01-07</t>
+          <t>TT-PAR-A01-08</t>
         </is>
       </c>
       <c r="E485" s="41" t="n"/>
@@ -15783,7 +15486,7 @@
       <c r="C486" s="42" t="n"/>
       <c r="D486" s="40" t="inlineStr">
         <is>
-          <t>PR-PAR-A01-22</t>
+          <t>PR-PAR-A01-25</t>
         </is>
       </c>
       <c r="E486" s="41" t="n"/>
@@ -15808,7 +15511,7 @@
       <c r="C487" s="42" t="n"/>
       <c r="D487" s="40" t="inlineStr">
         <is>
-          <t>UI-PAR-003-04</t>
+          <t>UI-PAR-003-05</t>
         </is>
       </c>
       <c r="E487" s="41" t="n"/>
@@ -15833,7 +15536,7 @@
       <c r="C488" s="42" t="n"/>
       <c r="D488" s="40" t="inlineStr">
         <is>
-          <t>구역 추천 실행</t>
+          <t>종합 지표 기반 우선순위 자동 산정</t>
         </is>
       </c>
       <c r="E488" s="41" t="n"/>
@@ -15950,7 +15653,6 @@
       <c r="N506" s="51" t="n"/>
       <c r="O506" s="52" t="n"/>
     </row>
-    <row r="507"/>
     <row r="508" ht="24" customHeight="1" s="48">
       <c r="A508" s="43" t="inlineStr">
         <is>
@@ -15961,7 +15663,7 @@
       <c r="C508" s="42" t="n"/>
       <c r="D508" s="40" t="inlineStr">
         <is>
-          <t>TT-PAR-A01-07</t>
+          <t>TT-PAR-A01-08</t>
         </is>
       </c>
       <c r="E508" s="41" t="n"/>
@@ -15986,7 +15688,7 @@
       <c r="C509" s="42" t="n"/>
       <c r="D509" s="40" t="inlineStr">
         <is>
-          <t>PR-PAR-A01-23</t>
+          <t>PR-PAR-A01-26</t>
         </is>
       </c>
       <c r="E509" s="41" t="n"/>
@@ -16011,7 +15713,7 @@
       <c r="C510" s="42" t="n"/>
       <c r="D510" s="40" t="inlineStr">
         <is>
-          <t>UI-PAR-003-04</t>
+          <t>UI-PAR-003-05</t>
         </is>
       </c>
       <c r="E510" s="41" t="n"/>
@@ -16036,7 +15738,7 @@
       <c r="C511" s="42" t="n"/>
       <c r="D511" s="40" t="inlineStr">
         <is>
-          <t>추천 구역 마커 표출</t>
+          <t>지도 마커 표출 및 상세 팝업</t>
         </is>
       </c>
       <c r="E511" s="41" t="n"/>
@@ -16153,7 +15855,6 @@
       <c r="N529" s="51" t="n"/>
       <c r="O529" s="52" t="n"/>
     </row>
-    <row r="530"/>
     <row r="531" ht="24" customHeight="1" s="48">
       <c r="A531" s="43" t="inlineStr">
         <is>
@@ -16164,7 +15865,7 @@
       <c r="C531" s="42" t="n"/>
       <c r="D531" s="40" t="inlineStr">
         <is>
-          <t>TT-PAR-A01-07</t>
+          <t>TT-PAR-A01-08</t>
         </is>
       </c>
       <c r="E531" s="41" t="n"/>
@@ -16189,7 +15890,7 @@
       <c r="C532" s="42" t="n"/>
       <c r="D532" s="40" t="inlineStr">
         <is>
-          <t>PR-PAR-A01-24</t>
+          <t>PR-PAR-A01-27</t>
         </is>
       </c>
       <c r="E532" s="41" t="n"/>
@@ -16214,7 +15915,7 @@
       <c r="C533" s="42" t="n"/>
       <c r="D533" s="40" t="inlineStr">
         <is>
-          <t>UI-PAR-003-04</t>
+          <t>UI-PAR-003-05</t>
         </is>
       </c>
       <c r="E533" s="41" t="n"/>
@@ -16239,7 +15940,7 @@
       <c r="C534" s="42" t="n"/>
       <c r="D534" s="40" t="inlineStr">
         <is>
-          <t>추천 구역 순위 산정</t>
+          <t>요약 카드·순위 리스트 정합성</t>
         </is>
       </c>
       <c r="E534" s="41" t="n"/>
@@ -16356,7 +16057,6 @@
       <c r="N552" s="51" t="n"/>
       <c r="O552" s="52" t="n"/>
     </row>
-    <row r="553"/>
     <row r="554" ht="24" customHeight="1" s="48">
       <c r="A554" s="43" t="inlineStr">
         <is>
@@ -16367,7 +16067,7 @@
       <c r="C554" s="42" t="n"/>
       <c r="D554" s="40" t="inlineStr">
         <is>
-          <t>TT-PAR-A01-08</t>
+          <t>TT-PAR-A01-09</t>
         </is>
       </c>
       <c r="E554" s="41" t="n"/>
@@ -16392,7 +16092,7 @@
       <c r="C555" s="42" t="n"/>
       <c r="D555" s="40" t="inlineStr">
         <is>
-          <t>PR-PAR-A01-25</t>
+          <t>PR-PAR-A01-28</t>
         </is>
       </c>
       <c r="E555" s="41" t="n"/>
@@ -16417,7 +16117,7 @@
       <c r="C556" s="42" t="n"/>
       <c r="D556" s="40" t="inlineStr">
         <is>
-          <t>UI-PAR-003-05</t>
+          <t>UI-PAR-004-03</t>
         </is>
       </c>
       <c r="E556" s="41" t="n"/>
@@ -16442,7 +16142,7 @@
       <c r="C557" s="42" t="n"/>
       <c r="D557" s="40" t="inlineStr">
         <is>
-          <t>종합 지표 기반 우선순위 자동 산정</t>
+          <t>알림 기준 설정 저장</t>
         </is>
       </c>
       <c r="E557" s="41" t="n"/>
@@ -16559,7 +16259,6 @@
       <c r="N575" s="51" t="n"/>
       <c r="O575" s="52" t="n"/>
     </row>
-    <row r="576"/>
     <row r="577" ht="24" customHeight="1" s="48">
       <c r="A577" s="43" t="inlineStr">
         <is>
@@ -16570,7 +16269,7 @@
       <c r="C577" s="42" t="n"/>
       <c r="D577" s="40" t="inlineStr">
         <is>
-          <t>TT-PAR-A01-08</t>
+          <t>TT-PAR-A01-09</t>
         </is>
       </c>
       <c r="E577" s="41" t="n"/>
@@ -16595,7 +16294,7 @@
       <c r="C578" s="42" t="n"/>
       <c r="D578" s="40" t="inlineStr">
         <is>
-          <t>PR-PAR-A01-26</t>
+          <t>PR-PAR-A01-29</t>
         </is>
       </c>
       <c r="E578" s="41" t="n"/>
@@ -16620,7 +16319,7 @@
       <c r="C579" s="42" t="n"/>
       <c r="D579" s="40" t="inlineStr">
         <is>
-          <t>UI-PAR-003-05</t>
+          <t>UI-PAR-004-03</t>
         </is>
       </c>
       <c r="E579" s="41" t="n"/>
@@ -16645,7 +16344,7 @@
       <c r="C580" s="42" t="n"/>
       <c r="D580" s="40" t="inlineStr">
         <is>
-          <t>지도 마커 표출 및 상세 팝업</t>
+          <t>수신자 등록 및 활성화 관리</t>
         </is>
       </c>
       <c r="E580" s="41" t="n"/>
@@ -16762,7 +16461,6 @@
       <c r="N598" s="51" t="n"/>
       <c r="O598" s="52" t="n"/>
     </row>
-    <row r="599"/>
     <row r="600" ht="24" customHeight="1" s="48">
       <c r="A600" s="43" t="inlineStr">
         <is>
@@ -16773,7 +16471,7 @@
       <c r="C600" s="42" t="n"/>
       <c r="D600" s="40" t="inlineStr">
         <is>
-          <t>TT-PAR-A01-08</t>
+          <t>TT-PAR-A01-09</t>
         </is>
       </c>
       <c r="E600" s="41" t="n"/>
@@ -16798,7 +16496,7 @@
       <c r="C601" s="42" t="n"/>
       <c r="D601" s="40" t="inlineStr">
         <is>
-          <t>PR-PAR-A01-27</t>
+          <t>PR-PAR-A01-30</t>
         </is>
       </c>
       <c r="E601" s="41" t="n"/>
@@ -16823,7 +16521,7 @@
       <c r="C602" s="42" t="n"/>
       <c r="D602" s="40" t="inlineStr">
         <is>
-          <t>UI-PAR-003-05</t>
+          <t>UI-PAR-004-02</t>
         </is>
       </c>
       <c r="E602" s="41" t="n"/>
@@ -16848,7 +16546,7 @@
       <c r="C603" s="42" t="n"/>
       <c r="D603" s="40" t="inlineStr">
         <is>
-          <t>요약 카드·순위 리스트 정합성</t>
+          <t>기준 충족 시 알림 자동 발생</t>
         </is>
       </c>
       <c r="E603" s="41" t="n"/>
@@ -16965,7 +16663,6 @@
       <c r="N621" s="51" t="n"/>
       <c r="O621" s="52" t="n"/>
     </row>
-    <row r="622"/>
     <row r="623" ht="24" customHeight="1" s="48">
       <c r="A623" s="43" t="inlineStr">
         <is>
@@ -17001,7 +16698,7 @@
       <c r="C624" s="42" t="n"/>
       <c r="D624" s="40" t="inlineStr">
         <is>
-          <t>PR-PAR-A01-28</t>
+          <t>PR-PAR-A01-31</t>
         </is>
       </c>
       <c r="E624" s="41" t="n"/>
@@ -17026,7 +16723,7 @@
       <c r="C625" s="42" t="n"/>
       <c r="D625" s="40" t="inlineStr">
         <is>
-          <t>UI-PAR-004-03</t>
+          <t>UI-PAR-004-02</t>
         </is>
       </c>
       <c r="E625" s="41" t="n"/>
@@ -17051,7 +16748,7 @@
       <c r="C626" s="42" t="n"/>
       <c r="D626" s="40" t="inlineStr">
         <is>
-          <t>알림 기준 설정 저장</t>
+          <t>알림 이력 조회</t>
         </is>
       </c>
       <c r="E626" s="41" t="n"/>
@@ -17168,7 +16865,6 @@
       <c r="N644" s="51" t="n"/>
       <c r="O644" s="52" t="n"/>
     </row>
-    <row r="645"/>
     <row r="646" ht="24" customHeight="1" s="48">
       <c r="A646" s="43" t="inlineStr">
         <is>
@@ -17179,7 +16875,7 @@
       <c r="C646" s="42" t="n"/>
       <c r="D646" s="40" t="inlineStr">
         <is>
-          <t>TT-PAR-A01-09</t>
+          <t>TT-PAR-A01-10</t>
         </is>
       </c>
       <c r="E646" s="41" t="n"/>
@@ -17204,7 +16900,7 @@
       <c r="C647" s="42" t="n"/>
       <c r="D647" s="40" t="inlineStr">
         <is>
-          <t>PR-PAR-A01-29</t>
+          <t>PR-PAR-A01-32</t>
         </is>
       </c>
       <c r="E647" s="41" t="n"/>
@@ -17229,7 +16925,7 @@
       <c r="C648" s="42" t="n"/>
       <c r="D648" s="40" t="inlineStr">
         <is>
-          <t>UI-PAR-004-03</t>
+          <t>UI-PAR-004-01</t>
         </is>
       </c>
       <c r="E648" s="41" t="n"/>
@@ -17254,7 +16950,7 @@
       <c r="C649" s="42" t="n"/>
       <c r="D649" s="40" t="inlineStr">
         <is>
-          <t>수신자 등록 및 활성화 관리</t>
+          <t>배포주기·배포일자 설정</t>
         </is>
       </c>
       <c r="E649" s="41" t="n"/>
@@ -17371,7 +17067,6 @@
       <c r="N667" s="51" t="n"/>
       <c r="O667" s="52" t="n"/>
     </row>
-    <row r="668"/>
     <row r="669" ht="24" customHeight="1" s="48">
       <c r="A669" s="43" t="inlineStr">
         <is>
@@ -17382,7 +17077,7 @@
       <c r="C669" s="42" t="n"/>
       <c r="D669" s="40" t="inlineStr">
         <is>
-          <t>TT-PAR-A01-09</t>
+          <t>TT-PAR-A01-10</t>
         </is>
       </c>
       <c r="E669" s="41" t="n"/>
@@ -17407,7 +17102,7 @@
       <c r="C670" s="42" t="n"/>
       <c r="D670" s="40" t="inlineStr">
         <is>
-          <t>PR-PAR-A01-30</t>
+          <t>PR-PAR-A01-33</t>
         </is>
       </c>
       <c r="E670" s="41" t="n"/>
@@ -17432,7 +17127,7 @@
       <c r="C671" s="42" t="n"/>
       <c r="D671" s="40" t="inlineStr">
         <is>
-          <t>UI-PAR-004-02</t>
+          <t>UI-PAR-004-01</t>
         </is>
       </c>
       <c r="E671" s="41" t="n"/>
@@ -17457,7 +17152,7 @@
       <c r="C672" s="42" t="n"/>
       <c r="D672" s="40" t="inlineStr">
         <is>
-          <t>기준 충족 시 알림 자동 발생</t>
+          <t>배포일자 도래 시 자동 생성</t>
         </is>
       </c>
       <c r="E672" s="41" t="n"/>
@@ -17574,7 +17269,6 @@
       <c r="N690" s="51" t="n"/>
       <c r="O690" s="52" t="n"/>
     </row>
-    <row r="691"/>
     <row r="692" ht="24" customHeight="1" s="48">
       <c r="A692" s="43" t="inlineStr">
         <is>
@@ -17585,7 +17279,7 @@
       <c r="C692" s="42" t="n"/>
       <c r="D692" s="40" t="inlineStr">
         <is>
-          <t>TT-PAR-A01-09</t>
+          <t>TT-PAR-A01-10</t>
         </is>
       </c>
       <c r="E692" s="41" t="n"/>
@@ -17610,7 +17304,7 @@
       <c r="C693" s="42" t="n"/>
       <c r="D693" s="40" t="inlineStr">
         <is>
-          <t>PR-PAR-A01-31</t>
+          <t>PR-PAR-A01-34</t>
         </is>
       </c>
       <c r="E693" s="41" t="n"/>
@@ -17635,7 +17329,7 @@
       <c r="C694" s="42" t="n"/>
       <c r="D694" s="40" t="inlineStr">
         <is>
-          <t>UI-PAR-004-02</t>
+          <t>UI-PAR-004-01</t>
         </is>
       </c>
       <c r="E694" s="41" t="n"/>
@@ -17660,7 +17354,7 @@
       <c r="C695" s="42" t="n"/>
       <c r="D695" s="40" t="inlineStr">
         <is>
-          <t>알림 이력 조회</t>
+          <t>미리보기 및 다운로드</t>
         </is>
       </c>
       <c r="E695" s="41" t="n"/>
@@ -17777,7 +17471,6 @@
       <c r="N713" s="51" t="n"/>
       <c r="O713" s="52" t="n"/>
     </row>
-    <row r="714"/>
     <row r="715" ht="24" customHeight="1" s="48">
       <c r="A715" s="43" t="inlineStr">
         <is>
@@ -17788,7 +17481,7 @@
       <c r="C715" s="42" t="n"/>
       <c r="D715" s="40" t="inlineStr">
         <is>
-          <t>TT-PAR-A01-10</t>
+          <t>TT-PAR-A01-11</t>
         </is>
       </c>
       <c r="E715" s="41" t="n"/>
@@ -17813,7 +17506,7 @@
       <c r="C716" s="42" t="n"/>
       <c r="D716" s="40" t="inlineStr">
         <is>
-          <t>PR-PAR-A01-32</t>
+          <t>PR-PAR-A01-35</t>
         </is>
       </c>
       <c r="E716" s="41" t="n"/>
@@ -17838,7 +17531,7 @@
       <c r="C717" s="42" t="n"/>
       <c r="D717" s="40" t="inlineStr">
         <is>
-          <t>UI-PAR-004-01</t>
+          <t>UI-PAR-005</t>
         </is>
       </c>
       <c r="E717" s="41" t="n"/>
@@ -17863,7 +17556,7 @@
       <c r="C718" s="42" t="n"/>
       <c r="D718" s="40" t="inlineStr">
         <is>
-          <t>배포주기·배포일자 설정</t>
+          <t>AI 어시스턴트 행정 지원(자연어 검색·조례 인용·민원 요약)</t>
         </is>
       </c>
       <c r="E718" s="41" t="n"/>
@@ -17980,7 +17673,6 @@
       <c r="N736" s="51" t="n"/>
       <c r="O736" s="52" t="n"/>
     </row>
-    <row r="737"/>
     <row r="738" ht="24" customHeight="1" s="48">
       <c r="A738" s="43" t="inlineStr">
         <is>
@@ -17991,7 +17683,7 @@
       <c r="C738" s="42" t="n"/>
       <c r="D738" s="40" t="inlineStr">
         <is>
-          <t>TT-PAR-A01-10</t>
+          <t>TT-PAR-A01-12</t>
         </is>
       </c>
       <c r="E738" s="41" t="n"/>
@@ -18016,7 +17708,7 @@
       <c r="C739" s="42" t="n"/>
       <c r="D739" s="40" t="inlineStr">
         <is>
-          <t>PR-PAR-A01-33</t>
+          <t>PR-PAR-A01-37</t>
         </is>
       </c>
       <c r="E739" s="41" t="n"/>
@@ -18041,7 +17733,7 @@
       <c r="C740" s="42" t="n"/>
       <c r="D740" s="40" t="inlineStr">
         <is>
-          <t>UI-PAR-004-01</t>
+          <t>UI-PAR-005</t>
         </is>
       </c>
       <c r="E740" s="41" t="n"/>
@@ -18066,7 +17758,7 @@
       <c r="C741" s="42" t="n"/>
       <c r="D741" s="40" t="inlineStr">
         <is>
-          <t>배포일자 도래 시 자동 생성</t>
+          <t>데이터 융합 통합분석</t>
         </is>
       </c>
       <c r="E741" s="41" t="n"/>
@@ -18183,7 +17875,6 @@
       <c r="N759" s="51" t="n"/>
       <c r="O759" s="52" t="n"/>
     </row>
-    <row r="760"/>
     <row r="761" ht="24" customHeight="1" s="48">
       <c r="A761" s="43" t="inlineStr">
         <is>
@@ -18194,7 +17885,7 @@
       <c r="C761" s="42" t="n"/>
       <c r="D761" s="40" t="inlineStr">
         <is>
-          <t>TT-PAR-A01-10</t>
+          <t>TT-PAR-A01-13</t>
         </is>
       </c>
       <c r="E761" s="41" t="n"/>
@@ -18219,7 +17910,7 @@
       <c r="C762" s="42" t="n"/>
       <c r="D762" s="40" t="inlineStr">
         <is>
-          <t>PR-PAR-A01-34</t>
+          <t>PR-PAR-A01-39</t>
         </is>
       </c>
       <c r="E762" s="41" t="n"/>
@@ -18244,7 +17935,7 @@
       <c r="C763" s="42" t="n"/>
       <c r="D763" s="40" t="inlineStr">
         <is>
-          <t>UI-PAR-004-01</t>
+          <t>공통(설정)</t>
         </is>
       </c>
       <c r="E763" s="41" t="n"/>
@@ -18269,7 +17960,7 @@
       <c r="C764" s="42" t="n"/>
       <c r="D764" s="40" t="inlineStr">
         <is>
-          <t>미리보기 및 다운로드</t>
+          <t>타 지자체 확산 적용 구조 검증</t>
         </is>
       </c>
       <c r="E764" s="41" t="n"/>
@@ -18386,1374 +18077,334 @@
       <c r="N782" s="51" t="n"/>
       <c r="O782" s="52" t="n"/>
     </row>
-    <row r="783"/>
-    <row r="784" ht="24" customHeight="1" s="48">
-      <c r="A784" s="43" t="inlineStr">
-        <is>
-          <t>통합테스트 아이디</t>
-        </is>
-      </c>
-      <c r="B784" s="41" t="n"/>
-      <c r="C784" s="42" t="n"/>
-      <c r="D784" s="40" t="inlineStr">
-        <is>
-          <t>TT-PAR-A01-11</t>
-        </is>
-      </c>
-      <c r="E784" s="41" t="n"/>
-      <c r="F784" s="41" t="n"/>
-      <c r="G784" s="41" t="n"/>
-      <c r="H784" s="41" t="n"/>
-      <c r="I784" s="41" t="n"/>
-      <c r="J784" s="41" t="n"/>
-      <c r="K784" s="41" t="n"/>
-      <c r="L784" s="41" t="n"/>
-      <c r="M784" s="41" t="n"/>
-      <c r="N784" s="41" t="n"/>
-      <c r="O784" s="42" t="n"/>
-    </row>
-    <row r="785" ht="24" customHeight="1" s="48">
-      <c r="A785" s="43" t="inlineStr">
-        <is>
-          <t>프로그램 ID</t>
-        </is>
-      </c>
-      <c r="B785" s="41" t="n"/>
-      <c r="C785" s="42" t="n"/>
-      <c r="D785" s="40" t="inlineStr">
-        <is>
-          <t>PR-PAR-A01-35</t>
-        </is>
-      </c>
-      <c r="E785" s="41" t="n"/>
-      <c r="F785" s="41" t="n"/>
-      <c r="G785" s="41" t="n"/>
-      <c r="H785" s="41" t="n"/>
-      <c r="I785" s="41" t="n"/>
-      <c r="J785" s="41" t="n"/>
-      <c r="K785" s="41" t="n"/>
-      <c r="L785" s="41" t="n"/>
-      <c r="M785" s="41" t="n"/>
-      <c r="N785" s="41" t="n"/>
-      <c r="O785" s="42" t="n"/>
-    </row>
-    <row r="786" ht="24" customHeight="1" s="48">
-      <c r="A786" s="43" t="inlineStr">
-        <is>
-          <t>화면 ID</t>
-        </is>
-      </c>
-      <c r="B786" s="41" t="n"/>
-      <c r="C786" s="42" t="n"/>
-      <c r="D786" s="40" t="inlineStr">
-        <is>
-          <t>UI-PAR-005</t>
-        </is>
-      </c>
-      <c r="E786" s="41" t="n"/>
-      <c r="F786" s="41" t="n"/>
-      <c r="G786" s="41" t="n"/>
-      <c r="H786" s="41" t="n"/>
-      <c r="I786" s="41" t="n"/>
-      <c r="J786" s="41" t="n"/>
-      <c r="K786" s="41" t="n"/>
-      <c r="L786" s="41" t="n"/>
-      <c r="M786" s="41" t="n"/>
-      <c r="N786" s="41" t="n"/>
-      <c r="O786" s="42" t="n"/>
-    </row>
-    <row r="787" ht="24" customHeight="1" s="48">
-      <c r="A787" s="43" t="inlineStr">
-        <is>
-          <t>시나리오명</t>
-        </is>
-      </c>
-      <c r="B787" s="41" t="n"/>
-      <c r="C787" s="42" t="n"/>
-      <c r="D787" s="40" t="inlineStr">
-        <is>
-          <t>AI 어시스턴트 행정 지원(자연어 검색·조례 인용·민원 요약)</t>
-        </is>
-      </c>
-      <c r="E787" s="41" t="n"/>
-      <c r="F787" s="41" t="n"/>
-      <c r="G787" s="41" t="n"/>
-      <c r="H787" s="41" t="n"/>
-      <c r="I787" s="41" t="n"/>
-      <c r="J787" s="41" t="n"/>
-      <c r="K787" s="41" t="n"/>
-      <c r="L787" s="41" t="n"/>
-      <c r="M787" s="41" t="n"/>
-      <c r="N787" s="41" t="n"/>
-      <c r="O787" s="42" t="n"/>
-    </row>
-    <row r="788">
-      <c r="A788" s="44" t="inlineStr">
-        <is>
-          <t>[ 테스트 결과 화면 캡쳐 ]</t>
-        </is>
-      </c>
-      <c r="B788" s="45" t="n"/>
-      <c r="C788" s="45" t="n"/>
-      <c r="D788" s="45" t="n"/>
-      <c r="E788" s="45" t="n"/>
-      <c r="F788" s="45" t="n"/>
-      <c r="G788" s="45" t="n"/>
-      <c r="H788" s="45" t="n"/>
-      <c r="I788" s="45" t="n"/>
-      <c r="J788" s="45" t="n"/>
-      <c r="K788" s="45" t="n"/>
-      <c r="L788" s="45" t="n"/>
-      <c r="M788" s="45" t="n"/>
-      <c r="N788" s="45" t="n"/>
-      <c r="O788" s="46" t="n"/>
-    </row>
-    <row r="789">
-      <c r="A789" s="47" t="n"/>
-      <c r="O789" s="49" t="n"/>
-    </row>
-    <row r="790">
-      <c r="A790" s="47" t="n"/>
-      <c r="O790" s="49" t="n"/>
-    </row>
-    <row r="791">
-      <c r="A791" s="47" t="n"/>
-      <c r="O791" s="49" t="n"/>
-    </row>
-    <row r="792">
-      <c r="A792" s="47" t="n"/>
-      <c r="O792" s="49" t="n"/>
-    </row>
-    <row r="793">
-      <c r="A793" s="47" t="n"/>
-      <c r="O793" s="49" t="n"/>
-    </row>
-    <row r="794">
-      <c r="A794" s="47" t="n"/>
-      <c r="O794" s="49" t="n"/>
-    </row>
-    <row r="795">
-      <c r="A795" s="47" t="n"/>
-      <c r="O795" s="49" t="n"/>
-    </row>
-    <row r="796">
-      <c r="A796" s="47" t="n"/>
-      <c r="O796" s="49" t="n"/>
-    </row>
-    <row r="797">
-      <c r="A797" s="47" t="n"/>
-      <c r="O797" s="49" t="n"/>
-    </row>
-    <row r="798">
-      <c r="A798" s="47" t="n"/>
-      <c r="O798" s="49" t="n"/>
-    </row>
-    <row r="799">
-      <c r="A799" s="47" t="n"/>
-      <c r="O799" s="49" t="n"/>
-    </row>
-    <row r="800">
-      <c r="A800" s="47" t="n"/>
-      <c r="O800" s="49" t="n"/>
-    </row>
-    <row r="801">
-      <c r="A801" s="47" t="n"/>
-      <c r="O801" s="49" t="n"/>
-    </row>
-    <row r="802">
-      <c r="A802" s="47" t="n"/>
-      <c r="O802" s="49" t="n"/>
-    </row>
-    <row r="803">
-      <c r="A803" s="47" t="n"/>
-      <c r="O803" s="49" t="n"/>
-    </row>
-    <row r="804">
-      <c r="A804" s="47" t="n"/>
-      <c r="O804" s="49" t="n"/>
-    </row>
-    <row r="805">
-      <c r="A805" s="50" t="n"/>
-      <c r="B805" s="51" t="n"/>
-      <c r="C805" s="51" t="n"/>
-      <c r="D805" s="51" t="n"/>
-      <c r="E805" s="51" t="n"/>
-      <c r="F805" s="51" t="n"/>
-      <c r="G805" s="51" t="n"/>
-      <c r="H805" s="51" t="n"/>
-      <c r="I805" s="51" t="n"/>
-      <c r="J805" s="51" t="n"/>
-      <c r="K805" s="51" t="n"/>
-      <c r="L805" s="51" t="n"/>
-      <c r="M805" s="51" t="n"/>
-      <c r="N805" s="51" t="n"/>
-      <c r="O805" s="52" t="n"/>
-    </row>
-    <row r="806"/>
-    <row r="807" ht="24" customHeight="1" s="48">
-      <c r="A807" s="43" t="inlineStr">
-        <is>
-          <t>통합테스트 아이디</t>
-        </is>
-      </c>
-      <c r="B807" s="41" t="n"/>
-      <c r="C807" s="42" t="n"/>
-      <c r="D807" s="40" t="inlineStr">
-        <is>
-          <t>TT-PAR-A01-12</t>
-        </is>
-      </c>
-      <c r="E807" s="41" t="n"/>
-      <c r="F807" s="41" t="n"/>
-      <c r="G807" s="41" t="n"/>
-      <c r="H807" s="41" t="n"/>
-      <c r="I807" s="41" t="n"/>
-      <c r="J807" s="41" t="n"/>
-      <c r="K807" s="41" t="n"/>
-      <c r="L807" s="41" t="n"/>
-      <c r="M807" s="41" t="n"/>
-      <c r="N807" s="41" t="n"/>
-      <c r="O807" s="42" t="n"/>
-    </row>
-    <row r="808" ht="24" customHeight="1" s="48">
-      <c r="A808" s="43" t="inlineStr">
-        <is>
-          <t>프로그램 ID</t>
-        </is>
-      </c>
-      <c r="B808" s="41" t="n"/>
-      <c r="C808" s="42" t="n"/>
-      <c r="D808" s="40" t="inlineStr">
-        <is>
-          <t>PR-PAR-A01-36</t>
-        </is>
-      </c>
-      <c r="E808" s="41" t="n"/>
-      <c r="F808" s="41" t="n"/>
-      <c r="G808" s="41" t="n"/>
-      <c r="H808" s="41" t="n"/>
-      <c r="I808" s="41" t="n"/>
-      <c r="J808" s="41" t="n"/>
-      <c r="K808" s="41" t="n"/>
-      <c r="L808" s="41" t="n"/>
-      <c r="M808" s="41" t="n"/>
-      <c r="N808" s="41" t="n"/>
-      <c r="O808" s="42" t="n"/>
-    </row>
-    <row r="809" ht="24" customHeight="1" s="48">
-      <c r="A809" s="43" t="inlineStr">
-        <is>
-          <t>화면 ID</t>
-        </is>
-      </c>
-      <c r="B809" s="41" t="n"/>
-      <c r="C809" s="42" t="n"/>
-      <c r="D809" s="40" t="inlineStr">
-        <is>
-          <t>UI-PAR-005</t>
-        </is>
-      </c>
-      <c r="E809" s="41" t="n"/>
-      <c r="F809" s="41" t="n"/>
-      <c r="G809" s="41" t="n"/>
-      <c r="H809" s="41" t="n"/>
-      <c r="I809" s="41" t="n"/>
-      <c r="J809" s="41" t="n"/>
-      <c r="K809" s="41" t="n"/>
-      <c r="L809" s="41" t="n"/>
-      <c r="M809" s="41" t="n"/>
-      <c r="N809" s="41" t="n"/>
-      <c r="O809" s="42" t="n"/>
-    </row>
-    <row r="810" ht="24" customHeight="1" s="48">
-      <c r="A810" s="43" t="inlineStr">
-        <is>
-          <t>시나리오명</t>
-        </is>
-      </c>
-      <c r="B810" s="41" t="n"/>
-      <c r="C810" s="42" t="n"/>
-      <c r="D810" s="40" t="inlineStr">
-        <is>
-          <t>비정형 행정문서 자동 수집·정형화(AI RPA/OCR)</t>
-        </is>
-      </c>
-      <c r="E810" s="41" t="n"/>
-      <c r="F810" s="41" t="n"/>
-      <c r="G810" s="41" t="n"/>
-      <c r="H810" s="41" t="n"/>
-      <c r="I810" s="41" t="n"/>
-      <c r="J810" s="41" t="n"/>
-      <c r="K810" s="41" t="n"/>
-      <c r="L810" s="41" t="n"/>
-      <c r="M810" s="41" t="n"/>
-      <c r="N810" s="41" t="n"/>
-      <c r="O810" s="42" t="n"/>
-    </row>
-    <row r="811">
-      <c r="A811" s="44" t="inlineStr">
-        <is>
-          <t>[ 테스트 결과 화면 캡쳐 ]</t>
-        </is>
-      </c>
-      <c r="B811" s="45" t="n"/>
-      <c r="C811" s="45" t="n"/>
-      <c r="D811" s="45" t="n"/>
-      <c r="E811" s="45" t="n"/>
-      <c r="F811" s="45" t="n"/>
-      <c r="G811" s="45" t="n"/>
-      <c r="H811" s="45" t="n"/>
-      <c r="I811" s="45" t="n"/>
-      <c r="J811" s="45" t="n"/>
-      <c r="K811" s="45" t="n"/>
-      <c r="L811" s="45" t="n"/>
-      <c r="M811" s="45" t="n"/>
-      <c r="N811" s="45" t="n"/>
-      <c r="O811" s="46" t="n"/>
-    </row>
-    <row r="812">
-      <c r="A812" s="47" t="n"/>
-      <c r="O812" s="49" t="n"/>
-    </row>
-    <row r="813">
-      <c r="A813" s="47" t="n"/>
-      <c r="O813" s="49" t="n"/>
-    </row>
-    <row r="814">
-      <c r="A814" s="47" t="n"/>
-      <c r="O814" s="49" t="n"/>
-    </row>
-    <row r="815">
-      <c r="A815" s="47" t="n"/>
-      <c r="O815" s="49" t="n"/>
-    </row>
-    <row r="816">
-      <c r="A816" s="47" t="n"/>
-      <c r="O816" s="49" t="n"/>
-    </row>
-    <row r="817">
-      <c r="A817" s="47" t="n"/>
-      <c r="O817" s="49" t="n"/>
-    </row>
-    <row r="818">
-      <c r="A818" s="47" t="n"/>
-      <c r="O818" s="49" t="n"/>
-    </row>
-    <row r="819">
-      <c r="A819" s="47" t="n"/>
-      <c r="O819" s="49" t="n"/>
-    </row>
-    <row r="820">
-      <c r="A820" s="47" t="n"/>
-      <c r="O820" s="49" t="n"/>
-    </row>
-    <row r="821">
-      <c r="A821" s="47" t="n"/>
-      <c r="O821" s="49" t="n"/>
-    </row>
-    <row r="822">
-      <c r="A822" s="47" t="n"/>
-      <c r="O822" s="49" t="n"/>
-    </row>
-    <row r="823">
-      <c r="A823" s="47" t="n"/>
-      <c r="O823" s="49" t="n"/>
-    </row>
-    <row r="824">
-      <c r="A824" s="47" t="n"/>
-      <c r="O824" s="49" t="n"/>
-    </row>
-    <row r="825">
-      <c r="A825" s="47" t="n"/>
-      <c r="O825" s="49" t="n"/>
-    </row>
-    <row r="826">
-      <c r="A826" s="47" t="n"/>
-      <c r="O826" s="49" t="n"/>
-    </row>
-    <row r="827">
-      <c r="A827" s="47" t="n"/>
-      <c r="O827" s="49" t="n"/>
-    </row>
-    <row r="828">
-      <c r="A828" s="50" t="n"/>
-      <c r="B828" s="51" t="n"/>
-      <c r="C828" s="51" t="n"/>
-      <c r="D828" s="51" t="n"/>
-      <c r="E828" s="51" t="n"/>
-      <c r="F828" s="51" t="n"/>
-      <c r="G828" s="51" t="n"/>
-      <c r="H828" s="51" t="n"/>
-      <c r="I828" s="51" t="n"/>
-      <c r="J828" s="51" t="n"/>
-      <c r="K828" s="51" t="n"/>
-      <c r="L828" s="51" t="n"/>
-      <c r="M828" s="51" t="n"/>
-      <c r="N828" s="51" t="n"/>
-      <c r="O828" s="52" t="n"/>
-    </row>
-    <row r="829"/>
-    <row r="830" ht="24" customHeight="1" s="48">
-      <c r="A830" s="43" t="inlineStr">
-        <is>
-          <t>통합테스트 아이디</t>
-        </is>
-      </c>
-      <c r="B830" s="41" t="n"/>
-      <c r="C830" s="42" t="n"/>
-      <c r="D830" s="40" t="inlineStr">
-        <is>
-          <t>TT-PAR-A01-13</t>
-        </is>
-      </c>
-      <c r="E830" s="41" t="n"/>
-      <c r="F830" s="41" t="n"/>
-      <c r="G830" s="41" t="n"/>
-      <c r="H830" s="41" t="n"/>
-      <c r="I830" s="41" t="n"/>
-      <c r="J830" s="41" t="n"/>
-      <c r="K830" s="41" t="n"/>
-      <c r="L830" s="41" t="n"/>
-      <c r="M830" s="41" t="n"/>
-      <c r="N830" s="41" t="n"/>
-      <c r="O830" s="42" t="n"/>
-    </row>
-    <row r="831" ht="24" customHeight="1" s="48">
-      <c r="A831" s="43" t="inlineStr">
-        <is>
-          <t>프로그램 ID</t>
-        </is>
-      </c>
-      <c r="B831" s="41" t="n"/>
-      <c r="C831" s="42" t="n"/>
-      <c r="D831" s="40" t="inlineStr">
-        <is>
-          <t>PR-PAR-A01-37</t>
-        </is>
-      </c>
-      <c r="E831" s="41" t="n"/>
-      <c r="F831" s="41" t="n"/>
-      <c r="G831" s="41" t="n"/>
-      <c r="H831" s="41" t="n"/>
-      <c r="I831" s="41" t="n"/>
-      <c r="J831" s="41" t="n"/>
-      <c r="K831" s="41" t="n"/>
-      <c r="L831" s="41" t="n"/>
-      <c r="M831" s="41" t="n"/>
-      <c r="N831" s="41" t="n"/>
-      <c r="O831" s="42" t="n"/>
-    </row>
-    <row r="832" ht="24" customHeight="1" s="48">
-      <c r="A832" s="43" t="inlineStr">
-        <is>
-          <t>화면 ID</t>
-        </is>
-      </c>
-      <c r="B832" s="41" t="n"/>
-      <c r="C832" s="42" t="n"/>
-      <c r="D832" s="40" t="inlineStr">
-        <is>
-          <t>UI-PAR-005</t>
-        </is>
-      </c>
-      <c r="E832" s="41" t="n"/>
-      <c r="F832" s="41" t="n"/>
-      <c r="G832" s="41" t="n"/>
-      <c r="H832" s="41" t="n"/>
-      <c r="I832" s="41" t="n"/>
-      <c r="J832" s="41" t="n"/>
-      <c r="K832" s="41" t="n"/>
-      <c r="L832" s="41" t="n"/>
-      <c r="M832" s="41" t="n"/>
-      <c r="N832" s="41" t="n"/>
-      <c r="O832" s="42" t="n"/>
-    </row>
-    <row r="833" ht="24" customHeight="1" s="48">
-      <c r="A833" s="43" t="inlineStr">
-        <is>
-          <t>시나리오명</t>
-        </is>
-      </c>
-      <c r="B833" s="41" t="n"/>
-      <c r="C833" s="42" t="n"/>
-      <c r="D833" s="40" t="inlineStr">
-        <is>
-          <t>데이터 융합 통합분석</t>
-        </is>
-      </c>
-      <c r="E833" s="41" t="n"/>
-      <c r="F833" s="41" t="n"/>
-      <c r="G833" s="41" t="n"/>
-      <c r="H833" s="41" t="n"/>
-      <c r="I833" s="41" t="n"/>
-      <c r="J833" s="41" t="n"/>
-      <c r="K833" s="41" t="n"/>
-      <c r="L833" s="41" t="n"/>
-      <c r="M833" s="41" t="n"/>
-      <c r="N833" s="41" t="n"/>
-      <c r="O833" s="42" t="n"/>
-    </row>
-    <row r="834">
-      <c r="A834" s="44" t="inlineStr">
-        <is>
-          <t>[ 테스트 결과 화면 캡쳐 ]</t>
-        </is>
-      </c>
-      <c r="B834" s="45" t="n"/>
-      <c r="C834" s="45" t="n"/>
-      <c r="D834" s="45" t="n"/>
-      <c r="E834" s="45" t="n"/>
-      <c r="F834" s="45" t="n"/>
-      <c r="G834" s="45" t="n"/>
-      <c r="H834" s="45" t="n"/>
-      <c r="I834" s="45" t="n"/>
-      <c r="J834" s="45" t="n"/>
-      <c r="K834" s="45" t="n"/>
-      <c r="L834" s="45" t="n"/>
-      <c r="M834" s="45" t="n"/>
-      <c r="N834" s="45" t="n"/>
-      <c r="O834" s="46" t="n"/>
-    </row>
-    <row r="835">
-      <c r="A835" s="47" t="n"/>
-      <c r="O835" s="49" t="n"/>
-    </row>
-    <row r="836">
-      <c r="A836" s="47" t="n"/>
-      <c r="O836" s="49" t="n"/>
-    </row>
-    <row r="837">
-      <c r="A837" s="47" t="n"/>
-      <c r="O837" s="49" t="n"/>
-    </row>
-    <row r="838">
-      <c r="A838" s="47" t="n"/>
-      <c r="O838" s="49" t="n"/>
-    </row>
-    <row r="839">
-      <c r="A839" s="47" t="n"/>
-      <c r="O839" s="49" t="n"/>
-    </row>
-    <row r="840">
-      <c r="A840" s="47" t="n"/>
-      <c r="O840" s="49" t="n"/>
-    </row>
-    <row r="841">
-      <c r="A841" s="47" t="n"/>
-      <c r="O841" s="49" t="n"/>
-    </row>
-    <row r="842">
-      <c r="A842" s="47" t="n"/>
-      <c r="O842" s="49" t="n"/>
-    </row>
-    <row r="843">
-      <c r="A843" s="47" t="n"/>
-      <c r="O843" s="49" t="n"/>
-    </row>
-    <row r="844">
-      <c r="A844" s="47" t="n"/>
-      <c r="O844" s="49" t="n"/>
-    </row>
-    <row r="845">
-      <c r="A845" s="47" t="n"/>
-      <c r="O845" s="49" t="n"/>
-    </row>
-    <row r="846">
-      <c r="A846" s="47" t="n"/>
-      <c r="O846" s="49" t="n"/>
-    </row>
-    <row r="847">
-      <c r="A847" s="47" t="n"/>
-      <c r="O847" s="49" t="n"/>
-    </row>
-    <row r="848">
-      <c r="A848" s="47" t="n"/>
-      <c r="O848" s="49" t="n"/>
-    </row>
-    <row r="849">
-      <c r="A849" s="47" t="n"/>
-      <c r="O849" s="49" t="n"/>
-    </row>
-    <row r="850">
-      <c r="A850" s="47" t="n"/>
-      <c r="O850" s="49" t="n"/>
-    </row>
-    <row r="851">
-      <c r="A851" s="50" t="n"/>
-      <c r="B851" s="51" t="n"/>
-      <c r="C851" s="51" t="n"/>
-      <c r="D851" s="51" t="n"/>
-      <c r="E851" s="51" t="n"/>
-      <c r="F851" s="51" t="n"/>
-      <c r="G851" s="51" t="n"/>
-      <c r="H851" s="51" t="n"/>
-      <c r="I851" s="51" t="n"/>
-      <c r="J851" s="51" t="n"/>
-      <c r="K851" s="51" t="n"/>
-      <c r="L851" s="51" t="n"/>
-      <c r="M851" s="51" t="n"/>
-      <c r="N851" s="51" t="n"/>
-      <c r="O851" s="52" t="n"/>
-    </row>
-    <row r="852"/>
-    <row r="853" ht="24" customHeight="1" s="48">
-      <c r="A853" s="43" t="inlineStr">
-        <is>
-          <t>통합테스트 아이디</t>
-        </is>
-      </c>
-      <c r="B853" s="41" t="n"/>
-      <c r="C853" s="42" t="n"/>
-      <c r="D853" s="40" t="inlineStr">
-        <is>
-          <t>TT-PAR-A01-14</t>
-        </is>
-      </c>
-      <c r="E853" s="41" t="n"/>
-      <c r="F853" s="41" t="n"/>
-      <c r="G853" s="41" t="n"/>
-      <c r="H853" s="41" t="n"/>
-      <c r="I853" s="41" t="n"/>
-      <c r="J853" s="41" t="n"/>
-      <c r="K853" s="41" t="n"/>
-      <c r="L853" s="41" t="n"/>
-      <c r="M853" s="41" t="n"/>
-      <c r="N853" s="41" t="n"/>
-      <c r="O853" s="42" t="n"/>
-    </row>
-    <row r="854" ht="24" customHeight="1" s="48">
-      <c r="A854" s="43" t="inlineStr">
-        <is>
-          <t>프로그램 ID</t>
-        </is>
-      </c>
-      <c r="B854" s="41" t="n"/>
-      <c r="C854" s="42" t="n"/>
-      <c r="D854" s="40" t="inlineStr">
-        <is>
-          <t>PR-PAR-A01-38</t>
-        </is>
-      </c>
-      <c r="E854" s="41" t="n"/>
-      <c r="F854" s="41" t="n"/>
-      <c r="G854" s="41" t="n"/>
-      <c r="H854" s="41" t="n"/>
-      <c r="I854" s="41" t="n"/>
-      <c r="J854" s="41" t="n"/>
-      <c r="K854" s="41" t="n"/>
-      <c r="L854" s="41" t="n"/>
-      <c r="M854" s="41" t="n"/>
-      <c r="N854" s="41" t="n"/>
-      <c r="O854" s="42" t="n"/>
-    </row>
-    <row r="855" ht="24" customHeight="1" s="48">
-      <c r="A855" s="43" t="inlineStr">
-        <is>
-          <t>화면 ID</t>
-        </is>
-      </c>
-      <c r="B855" s="41" t="n"/>
-      <c r="C855" s="42" t="n"/>
-      <c r="D855" s="40" t="inlineStr">
-        <is>
-          <t>공통(배치)</t>
-        </is>
-      </c>
-      <c r="E855" s="41" t="n"/>
-      <c r="F855" s="41" t="n"/>
-      <c r="G855" s="41" t="n"/>
-      <c r="H855" s="41" t="n"/>
-      <c r="I855" s="41" t="n"/>
-      <c r="J855" s="41" t="n"/>
-      <c r="K855" s="41" t="n"/>
-      <c r="L855" s="41" t="n"/>
-      <c r="M855" s="41" t="n"/>
-      <c r="N855" s="41" t="n"/>
-      <c r="O855" s="42" t="n"/>
-    </row>
-    <row r="856" ht="24" customHeight="1" s="48">
-      <c r="A856" s="43" t="inlineStr">
-        <is>
-          <t>시나리오명</t>
-        </is>
-      </c>
-      <c r="B856" s="41" t="n"/>
-      <c r="C856" s="42" t="n"/>
-      <c r="D856" s="40" t="inlineStr">
-        <is>
-          <t>분석 모델 재학습 및 고도화</t>
-        </is>
-      </c>
-      <c r="E856" s="41" t="n"/>
-      <c r="F856" s="41" t="n"/>
-      <c r="G856" s="41" t="n"/>
-      <c r="H856" s="41" t="n"/>
-      <c r="I856" s="41" t="n"/>
-      <c r="J856" s="41" t="n"/>
-      <c r="K856" s="41" t="n"/>
-      <c r="L856" s="41" t="n"/>
-      <c r="M856" s="41" t="n"/>
-      <c r="N856" s="41" t="n"/>
-      <c r="O856" s="42" t="n"/>
-    </row>
-    <row r="857">
-      <c r="A857" s="44" t="inlineStr">
-        <is>
-          <t>[ 테스트 결과 화면 캡쳐 ]</t>
-        </is>
-      </c>
-      <c r="B857" s="45" t="n"/>
-      <c r="C857" s="45" t="n"/>
-      <c r="D857" s="45" t="n"/>
-      <c r="E857" s="45" t="n"/>
-      <c r="F857" s="45" t="n"/>
-      <c r="G857" s="45" t="n"/>
-      <c r="H857" s="45" t="n"/>
-      <c r="I857" s="45" t="n"/>
-      <c r="J857" s="45" t="n"/>
-      <c r="K857" s="45" t="n"/>
-      <c r="L857" s="45" t="n"/>
-      <c r="M857" s="45" t="n"/>
-      <c r="N857" s="45" t="n"/>
-      <c r="O857" s="46" t="n"/>
-    </row>
-    <row r="858">
-      <c r="A858" s="47" t="n"/>
-      <c r="O858" s="49" t="n"/>
-    </row>
-    <row r="859">
-      <c r="A859" s="47" t="n"/>
-      <c r="O859" s="49" t="n"/>
-    </row>
-    <row r="860">
-      <c r="A860" s="47" t="n"/>
-      <c r="O860" s="49" t="n"/>
-    </row>
-    <row r="861">
-      <c r="A861" s="47" t="n"/>
-      <c r="O861" s="49" t="n"/>
-    </row>
-    <row r="862">
-      <c r="A862" s="47" t="n"/>
-      <c r="O862" s="49" t="n"/>
-    </row>
-    <row r="863">
-      <c r="A863" s="47" t="n"/>
-      <c r="O863" s="49" t="n"/>
-    </row>
-    <row r="864">
-      <c r="A864" s="47" t="n"/>
-      <c r="O864" s="49" t="n"/>
-    </row>
-    <row r="865">
-      <c r="A865" s="47" t="n"/>
-      <c r="O865" s="49" t="n"/>
-    </row>
-    <row r="866">
-      <c r="A866" s="47" t="n"/>
-      <c r="O866" s="49" t="n"/>
-    </row>
-    <row r="867">
-      <c r="A867" s="47" t="n"/>
-      <c r="O867" s="49" t="n"/>
-    </row>
-    <row r="868">
-      <c r="A868" s="47" t="n"/>
-      <c r="O868" s="49" t="n"/>
-    </row>
-    <row r="869">
-      <c r="A869" s="47" t="n"/>
-      <c r="O869" s="49" t="n"/>
-    </row>
-    <row r="870">
-      <c r="A870" s="47" t="n"/>
-      <c r="O870" s="49" t="n"/>
-    </row>
-    <row r="871">
-      <c r="A871" s="47" t="n"/>
-      <c r="O871" s="49" t="n"/>
-    </row>
-    <row r="872">
-      <c r="A872" s="47" t="n"/>
-      <c r="O872" s="49" t="n"/>
-    </row>
-    <row r="873">
-      <c r="A873" s="47" t="n"/>
-      <c r="O873" s="49" t="n"/>
-    </row>
-    <row r="874">
-      <c r="A874" s="50" t="n"/>
-      <c r="B874" s="51" t="n"/>
-      <c r="C874" s="51" t="n"/>
-      <c r="D874" s="51" t="n"/>
-      <c r="E874" s="51" t="n"/>
-      <c r="F874" s="51" t="n"/>
-      <c r="G874" s="51" t="n"/>
-      <c r="H874" s="51" t="n"/>
-      <c r="I874" s="51" t="n"/>
-      <c r="J874" s="51" t="n"/>
-      <c r="K874" s="51" t="n"/>
-      <c r="L874" s="51" t="n"/>
-      <c r="M874" s="51" t="n"/>
-      <c r="N874" s="51" t="n"/>
-      <c r="O874" s="52" t="n"/>
-    </row>
-    <row r="875"/>
-    <row r="876" ht="24" customHeight="1" s="48">
-      <c r="A876" s="43" t="inlineStr">
-        <is>
-          <t>통합테스트 아이디</t>
-        </is>
-      </c>
-      <c r="B876" s="41" t="n"/>
-      <c r="C876" s="42" t="n"/>
-      <c r="D876" s="40" t="inlineStr">
-        <is>
-          <t>TT-PAR-A01-15</t>
-        </is>
-      </c>
-      <c r="E876" s="41" t="n"/>
-      <c r="F876" s="41" t="n"/>
-      <c r="G876" s="41" t="n"/>
-      <c r="H876" s="41" t="n"/>
-      <c r="I876" s="41" t="n"/>
-      <c r="J876" s="41" t="n"/>
-      <c r="K876" s="41" t="n"/>
-      <c r="L876" s="41" t="n"/>
-      <c r="M876" s="41" t="n"/>
-      <c r="N876" s="41" t="n"/>
-      <c r="O876" s="42" t="n"/>
-    </row>
-    <row r="877" ht="24" customHeight="1" s="48">
-      <c r="A877" s="43" t="inlineStr">
-        <is>
-          <t>프로그램 ID</t>
-        </is>
-      </c>
-      <c r="B877" s="41" t="n"/>
-      <c r="C877" s="42" t="n"/>
-      <c r="D877" s="40" t="inlineStr">
-        <is>
-          <t>PR-PAR-A01-39</t>
-        </is>
-      </c>
-      <c r="E877" s="41" t="n"/>
-      <c r="F877" s="41" t="n"/>
-      <c r="G877" s="41" t="n"/>
-      <c r="H877" s="41" t="n"/>
-      <c r="I877" s="41" t="n"/>
-      <c r="J877" s="41" t="n"/>
-      <c r="K877" s="41" t="n"/>
-      <c r="L877" s="41" t="n"/>
-      <c r="M877" s="41" t="n"/>
-      <c r="N877" s="41" t="n"/>
-      <c r="O877" s="42" t="n"/>
-    </row>
-    <row r="878" ht="24" customHeight="1" s="48">
-      <c r="A878" s="43" t="inlineStr">
-        <is>
-          <t>화면 ID</t>
-        </is>
-      </c>
-      <c r="B878" s="41" t="n"/>
-      <c r="C878" s="42" t="n"/>
-      <c r="D878" s="40" t="inlineStr">
-        <is>
-          <t>공통(설정)</t>
-        </is>
-      </c>
-      <c r="E878" s="41" t="n"/>
-      <c r="F878" s="41" t="n"/>
-      <c r="G878" s="41" t="n"/>
-      <c r="H878" s="41" t="n"/>
-      <c r="I878" s="41" t="n"/>
-      <c r="J878" s="41" t="n"/>
-      <c r="K878" s="41" t="n"/>
-      <c r="L878" s="41" t="n"/>
-      <c r="M878" s="41" t="n"/>
-      <c r="N878" s="41" t="n"/>
-      <c r="O878" s="42" t="n"/>
-    </row>
-    <row r="879" ht="24" customHeight="1" s="48">
-      <c r="A879" s="43" t="inlineStr">
-        <is>
-          <t>시나리오명</t>
-        </is>
-      </c>
-      <c r="B879" s="41" t="n"/>
-      <c r="C879" s="42" t="n"/>
-      <c r="D879" s="40" t="inlineStr">
-        <is>
-          <t>타 지자체 확산 적용 구조 검증</t>
-        </is>
-      </c>
-      <c r="E879" s="41" t="n"/>
-      <c r="F879" s="41" t="n"/>
-      <c r="G879" s="41" t="n"/>
-      <c r="H879" s="41" t="n"/>
-      <c r="I879" s="41" t="n"/>
-      <c r="J879" s="41" t="n"/>
-      <c r="K879" s="41" t="n"/>
-      <c r="L879" s="41" t="n"/>
-      <c r="M879" s="41" t="n"/>
-      <c r="N879" s="41" t="n"/>
-      <c r="O879" s="42" t="n"/>
-    </row>
-    <row r="880">
-      <c r="A880" s="44" t="inlineStr">
-        <is>
-          <t>[ 테스트 결과 화면 캡쳐 ]</t>
-        </is>
-      </c>
-      <c r="B880" s="45" t="n"/>
-      <c r="C880" s="45" t="n"/>
-      <c r="D880" s="45" t="n"/>
-      <c r="E880" s="45" t="n"/>
-      <c r="F880" s="45" t="n"/>
-      <c r="G880" s="45" t="n"/>
-      <c r="H880" s="45" t="n"/>
-      <c r="I880" s="45" t="n"/>
-      <c r="J880" s="45" t="n"/>
-      <c r="K880" s="45" t="n"/>
-      <c r="L880" s="45" t="n"/>
-      <c r="M880" s="45" t="n"/>
-      <c r="N880" s="45" t="n"/>
-      <c r="O880" s="46" t="n"/>
-    </row>
-    <row r="881">
-      <c r="A881" s="47" t="n"/>
-      <c r="O881" s="49" t="n"/>
-    </row>
-    <row r="882">
-      <c r="A882" s="47" t="n"/>
-      <c r="O882" s="49" t="n"/>
-    </row>
-    <row r="883">
-      <c r="A883" s="47" t="n"/>
-      <c r="O883" s="49" t="n"/>
-    </row>
-    <row r="884">
-      <c r="A884" s="47" t="n"/>
-      <c r="O884" s="49" t="n"/>
-    </row>
-    <row r="885">
-      <c r="A885" s="47" t="n"/>
-      <c r="O885" s="49" t="n"/>
-    </row>
-    <row r="886">
-      <c r="A886" s="47" t="n"/>
-      <c r="O886" s="49" t="n"/>
-    </row>
-    <row r="887">
-      <c r="A887" s="47" t="n"/>
-      <c r="O887" s="49" t="n"/>
-    </row>
-    <row r="888">
-      <c r="A888" s="47" t="n"/>
-      <c r="O888" s="49" t="n"/>
-    </row>
-    <row r="889">
-      <c r="A889" s="47" t="n"/>
-      <c r="O889" s="49" t="n"/>
-    </row>
-    <row r="890">
-      <c r="A890" s="47" t="n"/>
-      <c r="O890" s="49" t="n"/>
-    </row>
-    <row r="891">
-      <c r="A891" s="47" t="n"/>
-      <c r="O891" s="49" t="n"/>
-    </row>
-    <row r="892">
-      <c r="A892" s="47" t="n"/>
-      <c r="O892" s="49" t="n"/>
-    </row>
-    <row r="893">
-      <c r="A893" s="47" t="n"/>
-      <c r="O893" s="49" t="n"/>
-    </row>
-    <row r="894">
-      <c r="A894" s="47" t="n"/>
-      <c r="O894" s="49" t="n"/>
-    </row>
-    <row r="895">
-      <c r="A895" s="47" t="n"/>
-      <c r="O895" s="49" t="n"/>
-    </row>
-    <row r="896">
-      <c r="A896" s="47" t="n"/>
-      <c r="O896" s="49" t="n"/>
-    </row>
-    <row r="897">
-      <c r="A897" s="50" t="n"/>
-      <c r="B897" s="51" t="n"/>
-      <c r="C897" s="51" t="n"/>
-      <c r="D897" s="51" t="n"/>
-      <c r="E897" s="51" t="n"/>
-      <c r="F897" s="51" t="n"/>
-      <c r="G897" s="51" t="n"/>
-      <c r="H897" s="51" t="n"/>
-      <c r="I897" s="51" t="n"/>
-      <c r="J897" s="51" t="n"/>
-      <c r="K897" s="51" t="n"/>
-      <c r="L897" s="51" t="n"/>
-      <c r="M897" s="51" t="n"/>
-      <c r="N897" s="51" t="n"/>
-      <c r="O897" s="52" t="n"/>
-    </row>
+    <row r="784" ht="24" customHeight="1" s="48"/>
+    <row r="785" ht="24" customHeight="1" s="48"/>
+    <row r="786" ht="24" customHeight="1" s="48"/>
+    <row r="787" ht="24" customHeight="1" s="48"/>
+    <row r="807" ht="24" customHeight="1" s="48"/>
+    <row r="808" ht="24" customHeight="1" s="48"/>
+    <row r="809" ht="24" customHeight="1" s="48"/>
+    <row r="810" ht="24" customHeight="1" s="48"/>
+    <row r="830" ht="24" customHeight="1" s="48"/>
+    <row r="831" ht="24" customHeight="1" s="48"/>
+    <row r="832" ht="24" customHeight="1" s="48"/>
+    <row r="833" ht="24" customHeight="1" s="48"/>
+    <row r="853" ht="24" customHeight="1" s="48"/>
+    <row r="854" ht="24" customHeight="1" s="48"/>
+    <row r="855" ht="24" customHeight="1" s="48"/>
+    <row r="856" ht="24" customHeight="1" s="48"/>
+    <row r="876" ht="24" customHeight="1" s="48"/>
+    <row r="877" ht="24" customHeight="1" s="48"/>
+    <row r="878" ht="24" customHeight="1" s="48"/>
+    <row r="879" ht="24" customHeight="1" s="48"/>
   </sheetData>
-  <mergeCells count="351">
+  <mergeCells count="306">
     <mergeCell ref="D2:O2"/>
+    <mergeCell ref="D601:O601"/>
     <mergeCell ref="A255:C255"/>
+    <mergeCell ref="A233:C233"/>
     <mergeCell ref="A326:C326"/>
+    <mergeCell ref="D278:O278"/>
+    <mergeCell ref="A673:O690"/>
     <mergeCell ref="D189:O189"/>
     <mergeCell ref="A557:C557"/>
-    <mergeCell ref="D877:O877"/>
-    <mergeCell ref="A855:C855"/>
+    <mergeCell ref="A531:C531"/>
+    <mergeCell ref="D465:O465"/>
+    <mergeCell ref="D763:O763"/>
     <mergeCell ref="D716:O716"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="A235:C235"/>
+    <mergeCell ref="A210:C210"/>
+    <mergeCell ref="D166:O166"/>
+    <mergeCell ref="A533:C533"/>
+    <mergeCell ref="D464:O464"/>
+    <mergeCell ref="A302:C302"/>
+    <mergeCell ref="D578:O578"/>
+    <mergeCell ref="D626:O626"/>
+    <mergeCell ref="A71:C71"/>
     <mergeCell ref="D416:O416"/>
-    <mergeCell ref="A784:C784"/>
-    <mergeCell ref="A715:C715"/>
-    <mergeCell ref="A351:O368"/>
-    <mergeCell ref="A761:C761"/>
-    <mergeCell ref="D142:O142"/>
-    <mergeCell ref="A510:C510"/>
-    <mergeCell ref="D807:O807"/>
-    <mergeCell ref="D442:O442"/>
-    <mergeCell ref="A49:C49"/>
-    <mergeCell ref="D119:O119"/>
-    <mergeCell ref="A370:C370"/>
-    <mergeCell ref="D419:O419"/>
-    <mergeCell ref="A121:O138"/>
-    <mergeCell ref="A118:C118"/>
-    <mergeCell ref="A670:C670"/>
-    <mergeCell ref="A535:O552"/>
-    <mergeCell ref="D3:O3"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="D74:O74"/>
-    <mergeCell ref="D372:O372"/>
-    <mergeCell ref="A512:O529"/>
-    <mergeCell ref="D117:O117"/>
-    <mergeCell ref="D188:O188"/>
-    <mergeCell ref="A786:C786"/>
-    <mergeCell ref="D5:O5"/>
-    <mergeCell ref="A258:C258"/>
-    <mergeCell ref="D303:O303"/>
-    <mergeCell ref="D417:O417"/>
-    <mergeCell ref="A785:C785"/>
-    <mergeCell ref="D830:O830"/>
-    <mergeCell ref="A73:C73"/>
-    <mergeCell ref="D603:O603"/>
-    <mergeCell ref="A787:C787"/>
-    <mergeCell ref="A466:O483"/>
-    <mergeCell ref="A167:O184"/>
-    <mergeCell ref="A98:O115"/>
-    <mergeCell ref="A578:C578"/>
-    <mergeCell ref="D210:O210"/>
-    <mergeCell ref="A50:C50"/>
-    <mergeCell ref="A876:C876"/>
-    <mergeCell ref="D209:O209"/>
-    <mergeCell ref="A188:C188"/>
-    <mergeCell ref="D301:O301"/>
-    <mergeCell ref="A878:C878"/>
-    <mergeCell ref="A853:C853"/>
-    <mergeCell ref="D211:O211"/>
-    <mergeCell ref="D511:O511"/>
-    <mergeCell ref="A558:O575"/>
-    <mergeCell ref="A259:O276"/>
-    <mergeCell ref="A856:C856"/>
-    <mergeCell ref="D140:O140"/>
-    <mergeCell ref="D740:O740"/>
-    <mergeCell ref="A328:O345"/>
-    <mergeCell ref="D832:O832"/>
-    <mergeCell ref="D440:O440"/>
-    <mergeCell ref="A808:C808"/>
-    <mergeCell ref="D738:O738"/>
-    <mergeCell ref="A74:C74"/>
-    <mergeCell ref="D141:O141"/>
-    <mergeCell ref="D72:O72"/>
-    <mergeCell ref="D235:O235"/>
-    <mergeCell ref="A140:C140"/>
-    <mergeCell ref="A788:O805"/>
-    <mergeCell ref="D393:O393"/>
-    <mergeCell ref="D624:O624"/>
-    <mergeCell ref="A719:O736"/>
-    <mergeCell ref="A279:C279"/>
-    <mergeCell ref="D26:O26"/>
-    <mergeCell ref="A692:C692"/>
-    <mergeCell ref="A350:C350"/>
-    <mergeCell ref="D324:O324"/>
-    <mergeCell ref="A879:C879"/>
-    <mergeCell ref="A420:O437"/>
-    <mergeCell ref="A94:C94"/>
-    <mergeCell ref="A281:C281"/>
-    <mergeCell ref="A694:C694"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="D166:O166"/>
-    <mergeCell ref="D464:O464"/>
-    <mergeCell ref="A71:C71"/>
     <mergeCell ref="D439:O439"/>
+    <mergeCell ref="D28:O28"/>
+    <mergeCell ref="D326:O326"/>
     <mergeCell ref="A234:C234"/>
+    <mergeCell ref="A75:O92"/>
     <mergeCell ref="D764:O764"/>
+    <mergeCell ref="D165:O165"/>
     <mergeCell ref="D143:O143"/>
     <mergeCell ref="D118:O118"/>
     <mergeCell ref="A371:C371"/>
     <mergeCell ref="D441:O441"/>
+    <mergeCell ref="A351:O368"/>
+    <mergeCell ref="A715:C715"/>
+    <mergeCell ref="D394:O394"/>
+    <mergeCell ref="D279:O279"/>
+    <mergeCell ref="A761:C761"/>
+    <mergeCell ref="D692:O692"/>
+    <mergeCell ref="D232:O232"/>
+    <mergeCell ref="A327:C327"/>
     <mergeCell ref="A165:C165"/>
-    <mergeCell ref="D232:O232"/>
+    <mergeCell ref="D142:O142"/>
+    <mergeCell ref="A510:C510"/>
+    <mergeCell ref="D418:O418"/>
+    <mergeCell ref="D94:O94"/>
     <mergeCell ref="D741:O741"/>
+    <mergeCell ref="D623:O623"/>
+    <mergeCell ref="D694:O694"/>
+    <mergeCell ref="A144:O161"/>
     <mergeCell ref="D532:O532"/>
+    <mergeCell ref="D442:O442"/>
     <mergeCell ref="A489:O506"/>
+    <mergeCell ref="A29:O46"/>
+    <mergeCell ref="A49:C49"/>
     <mergeCell ref="A669:C669"/>
-    <mergeCell ref="D96:O96"/>
-    <mergeCell ref="D27:O27"/>
-    <mergeCell ref="D325:O325"/>
-    <mergeCell ref="D396:O396"/>
-    <mergeCell ref="A120:C120"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="A301:C301"/>
-    <mergeCell ref="A95:C95"/>
-    <mergeCell ref="A393:C393"/>
-    <mergeCell ref="A464:C464"/>
-    <mergeCell ref="D327:O327"/>
-    <mergeCell ref="A695:C695"/>
-    <mergeCell ref="D625:O625"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A303:C303"/>
-    <mergeCell ref="A601:C601"/>
-    <mergeCell ref="A97:C97"/>
-    <mergeCell ref="A395:C395"/>
-    <mergeCell ref="A693:C693"/>
-    <mergeCell ref="A96:C96"/>
-    <mergeCell ref="D487:O487"/>
-    <mergeCell ref="D280:O280"/>
-    <mergeCell ref="D488:O488"/>
-    <mergeCell ref="D233:O233"/>
-    <mergeCell ref="D580:O580"/>
-    <mergeCell ref="D350:O350"/>
-    <mergeCell ref="A212:C212"/>
-    <mergeCell ref="A187:C187"/>
-    <mergeCell ref="D257:O257"/>
-    <mergeCell ref="A485:C485"/>
-    <mergeCell ref="D533:O533"/>
-    <mergeCell ref="A189:C189"/>
-    <mergeCell ref="A487:C487"/>
-    <mergeCell ref="D557:O557"/>
-    <mergeCell ref="A278:C278"/>
-    <mergeCell ref="D371:O371"/>
-    <mergeCell ref="D485:O485"/>
-    <mergeCell ref="A581:O598"/>
-    <mergeCell ref="A857:O874"/>
-    <mergeCell ref="D164:O164"/>
-    <mergeCell ref="D462:O462"/>
-    <mergeCell ref="A830:C830"/>
-    <mergeCell ref="A603:C603"/>
-    <mergeCell ref="A650:O667"/>
-    <mergeCell ref="A832:C832"/>
-    <mergeCell ref="A304:C304"/>
-    <mergeCell ref="D762:O762"/>
-    <mergeCell ref="A396:C396"/>
-    <mergeCell ref="D463:O463"/>
-    <mergeCell ref="D555:O555"/>
-    <mergeCell ref="A164:C164"/>
-    <mergeCell ref="A556:C556"/>
-    <mergeCell ref="D48:O48"/>
-    <mergeCell ref="D554:O554"/>
-    <mergeCell ref="D348:O348"/>
-    <mergeCell ref="A716:C716"/>
-    <mergeCell ref="D646:O646"/>
-    <mergeCell ref="D717:O717"/>
-    <mergeCell ref="A324:C324"/>
-    <mergeCell ref="D347:O347"/>
-    <mergeCell ref="A416:C416"/>
-    <mergeCell ref="D648:O648"/>
-    <mergeCell ref="A117:C117"/>
-    <mergeCell ref="D51:O51"/>
-    <mergeCell ref="D349:O349"/>
-    <mergeCell ref="D647:O647"/>
-    <mergeCell ref="A48:C48"/>
-    <mergeCell ref="A142:C142"/>
-    <mergeCell ref="A604:O621"/>
-    <mergeCell ref="A696:O713"/>
-    <mergeCell ref="D672:O672"/>
-    <mergeCell ref="A442:C442"/>
-    <mergeCell ref="D509:O509"/>
-    <mergeCell ref="D601:O601"/>
-    <mergeCell ref="A673:O690"/>
-    <mergeCell ref="A233:C233"/>
-    <mergeCell ref="D278:O278"/>
-    <mergeCell ref="A531:C531"/>
-    <mergeCell ref="D465:O465"/>
-    <mergeCell ref="D763:O763"/>
-    <mergeCell ref="A235:C235"/>
-    <mergeCell ref="A210:C210"/>
-    <mergeCell ref="A533:C533"/>
-    <mergeCell ref="D578:O578"/>
-    <mergeCell ref="A831:C831"/>
-    <mergeCell ref="D876:O876"/>
-    <mergeCell ref="A75:O92"/>
-    <mergeCell ref="A833:C833"/>
-    <mergeCell ref="D418:O418"/>
-    <mergeCell ref="A144:O161"/>
+    <mergeCell ref="D119:O119"/>
     <mergeCell ref="D718:O718"/>
     <mergeCell ref="A325:C325"/>
     <mergeCell ref="A119:C119"/>
     <mergeCell ref="A417:C417"/>
     <mergeCell ref="D186:O186"/>
     <mergeCell ref="A488:C488"/>
+    <mergeCell ref="A370:C370"/>
     <mergeCell ref="D649:O649"/>
+    <mergeCell ref="D96:O96"/>
+    <mergeCell ref="A718:C718"/>
     <mergeCell ref="A256:C256"/>
+    <mergeCell ref="D419:O419"/>
+    <mergeCell ref="A627:O644"/>
     <mergeCell ref="A625:C625"/>
+    <mergeCell ref="A121:O138"/>
     <mergeCell ref="A419:C419"/>
+    <mergeCell ref="D577:O577"/>
+    <mergeCell ref="A118:C118"/>
     <mergeCell ref="A717:C717"/>
+    <mergeCell ref="D49:O49"/>
+    <mergeCell ref="A670:C670"/>
+    <mergeCell ref="D120:O120"/>
+    <mergeCell ref="D27:O27"/>
+    <mergeCell ref="D325:O325"/>
+    <mergeCell ref="D396:O396"/>
     <mergeCell ref="A418:C418"/>
+    <mergeCell ref="A120:C120"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="D163:O163"/>
+    <mergeCell ref="A602:C602"/>
+    <mergeCell ref="A301:C301"/>
+    <mergeCell ref="D234:O234"/>
+    <mergeCell ref="A95:C95"/>
     <mergeCell ref="D715:O715"/>
+    <mergeCell ref="A393:C393"/>
+    <mergeCell ref="A464:C464"/>
+    <mergeCell ref="A535:O552"/>
+    <mergeCell ref="A695:C695"/>
+    <mergeCell ref="D327:O327"/>
+    <mergeCell ref="D625:O625"/>
     <mergeCell ref="A305:O322"/>
-    <mergeCell ref="D809:O809"/>
-    <mergeCell ref="D212:O212"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A303:C303"/>
+    <mergeCell ref="A601:C601"/>
+    <mergeCell ref="A508:C508"/>
     <mergeCell ref="A397:O414"/>
     <mergeCell ref="D510:O510"/>
+    <mergeCell ref="A97:C97"/>
+    <mergeCell ref="A395:C395"/>
+    <mergeCell ref="A579:C579"/>
     <mergeCell ref="D304:O304"/>
+    <mergeCell ref="D212:O212"/>
+    <mergeCell ref="A373:C373"/>
+    <mergeCell ref="A671:C671"/>
+    <mergeCell ref="D3:O3"/>
+    <mergeCell ref="A236:O253"/>
+    <mergeCell ref="D74:O74"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="A209:C209"/>
+    <mergeCell ref="A96:C96"/>
+    <mergeCell ref="D25:O25"/>
+    <mergeCell ref="A512:O529"/>
     <mergeCell ref="D602:O602"/>
-    <mergeCell ref="A236:O253"/>
-    <mergeCell ref="A209:C209"/>
+    <mergeCell ref="D117:O117"/>
+    <mergeCell ref="D372:O372"/>
+    <mergeCell ref="D188:O188"/>
     <mergeCell ref="A280:C280"/>
     <mergeCell ref="A372:C372"/>
-    <mergeCell ref="D810:O810"/>
+    <mergeCell ref="A213:O230"/>
+    <mergeCell ref="D5:O5"/>
+    <mergeCell ref="D669:O669"/>
+    <mergeCell ref="D303:O303"/>
     <mergeCell ref="A211:C211"/>
+    <mergeCell ref="D487:O487"/>
+    <mergeCell ref="A534:C534"/>
+    <mergeCell ref="A509:C509"/>
+    <mergeCell ref="D579:O579"/>
     <mergeCell ref="D256:O256"/>
-    <mergeCell ref="A509:C509"/>
-    <mergeCell ref="A534:C534"/>
-    <mergeCell ref="D579:O579"/>
+    <mergeCell ref="A258:C258"/>
+    <mergeCell ref="D417:O417"/>
     <mergeCell ref="A186:C186"/>
     <mergeCell ref="A257:C257"/>
     <mergeCell ref="D370:O370"/>
     <mergeCell ref="A672:C672"/>
+    <mergeCell ref="A73:C73"/>
+    <mergeCell ref="A51:C51"/>
     <mergeCell ref="A555:C555"/>
-    <mergeCell ref="A51:C51"/>
+    <mergeCell ref="A462:C462"/>
+    <mergeCell ref="D280:O280"/>
     <mergeCell ref="A349:C349"/>
+    <mergeCell ref="D603:O603"/>
     <mergeCell ref="A511:C511"/>
-    <mergeCell ref="A809:C809"/>
-    <mergeCell ref="D879:O879"/>
+    <mergeCell ref="A190:O207"/>
     <mergeCell ref="A486:C486"/>
+    <mergeCell ref="A466:O483"/>
+    <mergeCell ref="D488:O488"/>
+    <mergeCell ref="D233:O233"/>
+    <mergeCell ref="A762:C762"/>
+    <mergeCell ref="D693:O693"/>
     <mergeCell ref="A649:C649"/>
-    <mergeCell ref="D693:O693"/>
-    <mergeCell ref="D670:O670"/>
-    <mergeCell ref="D486:O486"/>
-    <mergeCell ref="D784:O784"/>
-    <mergeCell ref="A440:C440"/>
-    <mergeCell ref="A738:C738"/>
-    <mergeCell ref="D534:O534"/>
-    <mergeCell ref="A141:C141"/>
-    <mergeCell ref="D71:O71"/>
-    <mergeCell ref="A439:C439"/>
-    <mergeCell ref="D373:O373"/>
-    <mergeCell ref="A72:C72"/>
-    <mergeCell ref="D785:O785"/>
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="D73:O73"/>
-    <mergeCell ref="D787:O787"/>
-    <mergeCell ref="A834:O851"/>
-    <mergeCell ref="A580:C580"/>
-    <mergeCell ref="A765:O782"/>
-    <mergeCell ref="D739:O739"/>
-    <mergeCell ref="A52:O69"/>
-    <mergeCell ref="D854:O854"/>
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="A577:C577"/>
-    <mergeCell ref="D671:O671"/>
-    <mergeCell ref="D4:O4"/>
-    <mergeCell ref="D531:O531"/>
-    <mergeCell ref="A764:C764"/>
-    <mergeCell ref="A143:C143"/>
-    <mergeCell ref="D831:O831"/>
-    <mergeCell ref="A441:C441"/>
-    <mergeCell ref="A739:C739"/>
-    <mergeCell ref="D508:O508"/>
-    <mergeCell ref="A810:C810"/>
-    <mergeCell ref="A232:C232"/>
-    <mergeCell ref="D302:O302"/>
-    <mergeCell ref="D600:O600"/>
-    <mergeCell ref="A741:C741"/>
-    <mergeCell ref="D808:O808"/>
-    <mergeCell ref="A532:C532"/>
-    <mergeCell ref="A807:C807"/>
-    <mergeCell ref="D626:O626"/>
-    <mergeCell ref="A302:C302"/>
-    <mergeCell ref="D28:O28"/>
-    <mergeCell ref="D326:O326"/>
-    <mergeCell ref="D165:O165"/>
-    <mergeCell ref="A327:C327"/>
-    <mergeCell ref="D394:O394"/>
-    <mergeCell ref="D279:O279"/>
-    <mergeCell ref="D692:O692"/>
-    <mergeCell ref="D94:O94"/>
-    <mergeCell ref="D623:O623"/>
-    <mergeCell ref="D694:O694"/>
-    <mergeCell ref="A29:O46"/>
-    <mergeCell ref="D833:O833"/>
-    <mergeCell ref="A627:O644"/>
-    <mergeCell ref="D577:O577"/>
-    <mergeCell ref="D49:O49"/>
-    <mergeCell ref="D120:O120"/>
-    <mergeCell ref="D163:O163"/>
-    <mergeCell ref="A602:C602"/>
-    <mergeCell ref="D234:O234"/>
-    <mergeCell ref="A508:C508"/>
-    <mergeCell ref="A579:C579"/>
-    <mergeCell ref="A877:C877"/>
-    <mergeCell ref="A373:C373"/>
-    <mergeCell ref="A671:C671"/>
-    <mergeCell ref="D25:O25"/>
-    <mergeCell ref="A213:O230"/>
-    <mergeCell ref="D669:O669"/>
-    <mergeCell ref="D855:O855"/>
-    <mergeCell ref="A462:C462"/>
-    <mergeCell ref="A880:O897"/>
-    <mergeCell ref="A190:O207"/>
-    <mergeCell ref="A762:C762"/>
-    <mergeCell ref="D856:O856"/>
+    <mergeCell ref="A167:O184"/>
+    <mergeCell ref="A212:C212"/>
+    <mergeCell ref="A187:C187"/>
+    <mergeCell ref="D580:O580"/>
+    <mergeCell ref="D257:O257"/>
+    <mergeCell ref="A485:C485"/>
     <mergeCell ref="A25:C25"/>
     <mergeCell ref="D95:O95"/>
     <mergeCell ref="A463:C463"/>
     <mergeCell ref="D695:O695"/>
     <mergeCell ref="A626:C626"/>
+    <mergeCell ref="A98:O115"/>
+    <mergeCell ref="D533:O533"/>
     <mergeCell ref="A742:O759"/>
+    <mergeCell ref="A189:C189"/>
     <mergeCell ref="A163:C163"/>
+    <mergeCell ref="A487:C487"/>
+    <mergeCell ref="D557:O557"/>
+    <mergeCell ref="A578:C578"/>
     <mergeCell ref="A394:C394"/>
+    <mergeCell ref="A50:C50"/>
+    <mergeCell ref="D395:O395"/>
+    <mergeCell ref="D210:O210"/>
+    <mergeCell ref="D486:O486"/>
+    <mergeCell ref="D670:O670"/>
+    <mergeCell ref="A2:C2"/>
     <mergeCell ref="D97:O97"/>
     <mergeCell ref="A465:C465"/>
-    <mergeCell ref="D395:O395"/>
     <mergeCell ref="A763:C763"/>
-    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A693:C693"/>
+    <mergeCell ref="A440:C440"/>
+    <mergeCell ref="D371:O371"/>
+    <mergeCell ref="D209:O209"/>
+    <mergeCell ref="A278:C278"/>
+    <mergeCell ref="A738:C738"/>
+    <mergeCell ref="D534:O534"/>
+    <mergeCell ref="A188:C188"/>
+    <mergeCell ref="D301:O301"/>
+    <mergeCell ref="D485:O485"/>
+    <mergeCell ref="A141:C141"/>
+    <mergeCell ref="A439:C439"/>
+    <mergeCell ref="D71:O71"/>
     <mergeCell ref="D255:O255"/>
+    <mergeCell ref="A581:O598"/>
+    <mergeCell ref="D373:O373"/>
     <mergeCell ref="A740:C740"/>
-    <mergeCell ref="D853:O853"/>
+    <mergeCell ref="D211:O211"/>
+    <mergeCell ref="A72:C72"/>
     <mergeCell ref="A443:O460"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="D73:O73"/>
     <mergeCell ref="A554:C554"/>
+    <mergeCell ref="D164:O164"/>
     <mergeCell ref="A348:C348"/>
+    <mergeCell ref="D462:O462"/>
     <mergeCell ref="A282:O299"/>
     <mergeCell ref="A646:C646"/>
-    <mergeCell ref="D786:O786"/>
+    <mergeCell ref="D511:O511"/>
     <mergeCell ref="A374:O391"/>
-    <mergeCell ref="D878:O878"/>
+    <mergeCell ref="A558:O575"/>
+    <mergeCell ref="A603:C603"/>
     <mergeCell ref="A347:C347"/>
+    <mergeCell ref="A650:O667"/>
     <mergeCell ref="D50:O50"/>
-    <mergeCell ref="A854:C854"/>
+    <mergeCell ref="A259:O276"/>
     <mergeCell ref="A648:C648"/>
+    <mergeCell ref="D762:O762"/>
+    <mergeCell ref="A304:C304"/>
     <mergeCell ref="D187:O187"/>
+    <mergeCell ref="A396:C396"/>
     <mergeCell ref="A623:C623"/>
+    <mergeCell ref="A580:C580"/>
+    <mergeCell ref="D463:O463"/>
+    <mergeCell ref="A765:O782"/>
     <mergeCell ref="A647:C647"/>
+    <mergeCell ref="D555:O555"/>
+    <mergeCell ref="D739:O739"/>
+    <mergeCell ref="D140:O140"/>
+    <mergeCell ref="D740:O740"/>
+    <mergeCell ref="A52:O69"/>
     <mergeCell ref="D281:O281"/>
+    <mergeCell ref="A328:O345"/>
     <mergeCell ref="A624:C624"/>
-    <mergeCell ref="A811:O828"/>
+    <mergeCell ref="A164:C164"/>
+    <mergeCell ref="D440:O440"/>
+    <mergeCell ref="D738:O738"/>
+    <mergeCell ref="A74:C74"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="D141:O141"/>
+    <mergeCell ref="A556:C556"/>
+    <mergeCell ref="D48:O48"/>
+    <mergeCell ref="A577:C577"/>
+    <mergeCell ref="D72:O72"/>
+    <mergeCell ref="D671:O671"/>
+    <mergeCell ref="D554:O554"/>
     <mergeCell ref="A6:O23"/>
+    <mergeCell ref="D235:O235"/>
+    <mergeCell ref="A716:C716"/>
+    <mergeCell ref="D348:O348"/>
+    <mergeCell ref="D646:O646"/>
+    <mergeCell ref="D4:O4"/>
+    <mergeCell ref="D717:O717"/>
+    <mergeCell ref="A140:C140"/>
+    <mergeCell ref="A324:C324"/>
+    <mergeCell ref="D347:O347"/>
     <mergeCell ref="A600:C600"/>
+    <mergeCell ref="D531:O531"/>
+    <mergeCell ref="A416:C416"/>
     <mergeCell ref="D761:O761"/>
+    <mergeCell ref="D648:O648"/>
+    <mergeCell ref="A117:C117"/>
+    <mergeCell ref="D393:O393"/>
+    <mergeCell ref="D624:O624"/>
+    <mergeCell ref="D51:O51"/>
+    <mergeCell ref="D349:O349"/>
+    <mergeCell ref="A764:C764"/>
+    <mergeCell ref="A143:C143"/>
+    <mergeCell ref="D647:O647"/>
+    <mergeCell ref="A441:C441"/>
+    <mergeCell ref="A719:O736"/>
+    <mergeCell ref="D26:O26"/>
+    <mergeCell ref="D508:O508"/>
+    <mergeCell ref="A48:C48"/>
+    <mergeCell ref="A739:C739"/>
+    <mergeCell ref="A279:C279"/>
     <mergeCell ref="A166:C166"/>
+    <mergeCell ref="A350:C350"/>
+    <mergeCell ref="A232:C232"/>
+    <mergeCell ref="D324:O324"/>
+    <mergeCell ref="A692:C692"/>
+    <mergeCell ref="D302:O302"/>
+    <mergeCell ref="D600:O600"/>
+    <mergeCell ref="A420:O437"/>
+    <mergeCell ref="A142:C142"/>
+    <mergeCell ref="A604:O621"/>
+    <mergeCell ref="A94:C94"/>
+    <mergeCell ref="A696:O713"/>
+    <mergeCell ref="A741:C741"/>
+    <mergeCell ref="A281:C281"/>
+    <mergeCell ref="D672:O672"/>
+    <mergeCell ref="A694:C694"/>
+    <mergeCell ref="A532:C532"/>
     <mergeCell ref="D258:O258"/>
+    <mergeCell ref="A442:C442"/>
     <mergeCell ref="D556:O556"/>
-    <mergeCell ref="A718:C718"/>
+    <mergeCell ref="D509:O509"/>
+    <mergeCell ref="D350:O350"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -19765,7 +18416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.875" defaultRowHeight="17.1"/>
   <cols>
     <col width="6" customWidth="1" style="48" min="1" max="1"/>
@@ -19784,7 +18435,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="28" t="inlineStr">
         <is>
@@ -19859,7 +18509,7 @@
     </row>
     <row r="5" ht="60" customHeight="1" s="48">
       <c r="A5" s="29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B5" s="29" t="inlineStr">
         <is>
@@ -19868,17 +18518,17 @@
       </c>
       <c r="C5" s="40" t="inlineStr">
         <is>
-          <t>AI RPA·OCR 기반 비정형 문서 자동 수집·정형화 배치에 대응하는 화면이 화면설계서(JJ_PD_IP_D04)에 없어 화면 ID를 공란 처리함</t>
+          <t>단위테스트(M04)의 설정 화면(UT-SET-01~06)에 대응하는 화면이 화면설계서에 없어 화면 ID를 공란 처리함</t>
         </is>
       </c>
       <c r="D5" s="29" t="inlineStr">
         <is>
-          <t>TT-PAR-A01-13</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E5" s="40" t="inlineStr">
         <is>
-          <t>배치 모니터링 화면 신설 여부 검토 후 화면설계서 반영</t>
+          <t>화면설계서에 설정 화면 추가 또는 테스트 항목 조정</t>
         </is>
       </c>
       <c r="F5" s="29" t="inlineStr">
@@ -19894,31 +18544,31 @@
     </row>
     <row r="6" ht="60" customHeight="1" s="48">
       <c r="A6" s="29" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B6" s="29" t="inlineStr">
         <is>
-          <t>설계 미반영</t>
+          <t>테스트 환경</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>단위테스트(M04)의 설정 화면(UT-SET-01~06)에 대응하는 화면이 화면설계서에 없어 화면 ID를 공란 처리함</t>
+          <t>테스트데이터를 권한 유형으로만 기재함. 실증 환경에서 권한별 계정 발급 후 테스트 수행 필요</t>
         </is>
       </c>
       <c r="D6" s="29" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>전체</t>
         </is>
       </c>
       <c r="E6" s="40" t="inlineStr">
         <is>
-          <t>화면설계서에 설정 화면 추가 또는 테스트 항목 조정</t>
+          <t>실증 착수 시 권한별 계정 발급 후 테스트 수행</t>
         </is>
       </c>
       <c r="F6" s="29" t="inlineStr">
         <is>
-          <t>검토중</t>
+          <t>대기</t>
         </is>
       </c>
       <c r="G6" s="29" t="inlineStr">
@@ -19929,16 +18579,16 @@
     </row>
     <row r="7" ht="60" customHeight="1" s="48">
       <c r="A7" s="29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B7" s="29" t="inlineStr">
         <is>
-          <t>테스트 환경</t>
+          <t>미수행</t>
         </is>
       </c>
       <c r="C7" s="40" t="inlineStr">
         <is>
-          <t>테스트데이터를 권한 유형으로만 기재함. 실증 환경에서 권한별 계정 발급 후 테스트 수행 필요</t>
+          <t>통합테스트 미수행 상태로 결과서의 1차·2차 상태·점검자·점검일이 공란임</t>
         </is>
       </c>
       <c r="D7" s="29" t="inlineStr">
@@ -19948,7 +18598,7 @@
       </c>
       <c r="E7" s="40" t="inlineStr">
         <is>
-          <t>실증 착수 시 권한별 계정 발급 후 테스트 수행</t>
+          <t>통합테스트 수행 후 결과 기입</t>
         </is>
       </c>
       <c r="F7" s="29" t="inlineStr">
@@ -19962,41 +18612,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="60" customHeight="1" s="48">
-      <c r="A8" s="29" t="n">
-        <v>5</v>
-      </c>
-      <c r="B8" s="29" t="inlineStr">
-        <is>
-          <t>미수행</t>
-        </is>
-      </c>
-      <c r="C8" s="40" t="inlineStr">
-        <is>
-          <t>통합테스트 미수행 상태로 결과서의 1차·2차 상태·점검자·점검일이 공란임</t>
-        </is>
-      </c>
-      <c r="D8" s="29" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="E8" s="40" t="inlineStr">
-        <is>
-          <t>통합테스트 수행 후 결과 기입</t>
-        </is>
-      </c>
-      <c r="F8" s="29" t="inlineStr">
-        <is>
-          <t>대기</t>
-        </is>
-      </c>
-      <c r="G8" s="29" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-    </row>
+    <row r="8" ht="60" customHeight="1" s="48"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
